--- a/AAII_Financials/Quarterly/HTHIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HTHIY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
   <si>
     <t>HTHIY</t>
   </si>
@@ -656,415 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>17513500</v>
+        <v>15219500</v>
       </c>
       <c r="E8" s="3">
-        <v>15421300</v>
+        <v>17777300</v>
       </c>
       <c r="F8" s="3">
-        <v>18408400</v>
+        <v>15653600</v>
       </c>
       <c r="G8" s="3">
-        <v>17875000</v>
+        <v>18685700</v>
       </c>
       <c r="H8" s="3">
-        <v>18903800</v>
+        <v>18144200</v>
       </c>
       <c r="I8" s="3">
-        <v>17063600</v>
+        <v>19188500</v>
       </c>
       <c r="J8" s="3">
+        <v>17320600</v>
+      </c>
+      <c r="K8" s="3">
         <v>19375100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17271200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17774300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17400700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19498900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16264900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>16871400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13599200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>21347400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>19339200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>20114600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>18618500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>25924400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>21628300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>21607900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>19688000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>24359100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>20770000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>20681700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>18881600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>23443000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>19208300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>19720700</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>13163600</v>
+        <v>10951800</v>
       </c>
       <c r="E9" s="3">
-        <v>11606900</v>
+        <v>13361800</v>
       </c>
       <c r="F9" s="3">
-        <v>13732500</v>
+        <v>11781700</v>
       </c>
       <c r="G9" s="3">
-        <v>13428500</v>
+        <v>13939300</v>
       </c>
       <c r="H9" s="3">
-        <v>14257500</v>
+        <v>13630700</v>
       </c>
       <c r="I9" s="3">
-        <v>12976800</v>
+        <v>14472200</v>
       </c>
       <c r="J9" s="3">
+        <v>13172300</v>
+      </c>
+      <c r="K9" s="3">
         <v>14433800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12948800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13386900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13161400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14759900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12099600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12635200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10060500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>15555900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>14178700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14579000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13633700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>19379600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>15751100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>15728800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>14420300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>17804700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>15290000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>15148400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>13830300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>17433900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>14170500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>14505800</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4349900</v>
+        <v>4267600</v>
       </c>
       <c r="E10" s="3">
-        <v>3814400</v>
+        <v>4415500</v>
       </c>
       <c r="F10" s="3">
-        <v>4676000</v>
+        <v>3871800</v>
       </c>
       <c r="G10" s="3">
-        <v>4446500</v>
+        <v>4746400</v>
       </c>
       <c r="H10" s="3">
-        <v>4646300</v>
+        <v>4513500</v>
       </c>
       <c r="I10" s="3">
-        <v>4086700</v>
+        <v>4716300</v>
       </c>
       <c r="J10" s="3">
+        <v>4148300</v>
+      </c>
+      <c r="K10" s="3">
         <v>4941300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4322400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4387400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4239200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4739000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4165300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4236200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3538700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5791400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5160500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5535500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4984800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>6544800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5877200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5879200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5267700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>6554300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5479900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>5533300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5051300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>6009100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5037800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5214900</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1097,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1189,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1281,59 +1298,62 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-50000</v>
+        <v>-543800</v>
       </c>
       <c r="E14" s="3">
-        <v>54600</v>
+        <v>-50800</v>
       </c>
       <c r="F14" s="3">
-        <v>-1091300</v>
+        <v>55400</v>
       </c>
       <c r="G14" s="3">
-        <v>44800</v>
+        <v>-1107700</v>
       </c>
       <c r="H14" s="3">
-        <v>-13500</v>
+        <v>45500</v>
       </c>
       <c r="I14" s="3">
-        <v>27900</v>
+        <v>-13700</v>
       </c>
       <c r="J14" s="3">
+        <v>28300</v>
+      </c>
+      <c r="K14" s="3">
         <v>176000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>55000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-428000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-245700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-853500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>256500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>325700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-2389500</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
@@ -1373,8 +1393,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1465,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1496,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>16169200</v>
+        <v>13326200</v>
       </c>
       <c r="E17" s="3">
-        <v>14609000</v>
+        <v>16412700</v>
       </c>
       <c r="F17" s="3">
-        <v>15852100</v>
+        <v>14829100</v>
       </c>
       <c r="G17" s="3">
-        <v>16572800</v>
+        <v>16090800</v>
       </c>
       <c r="H17" s="3">
-        <v>17541900</v>
+        <v>16822400</v>
       </c>
       <c r="I17" s="3">
-        <v>16284400</v>
+        <v>17806000</v>
       </c>
       <c r="J17" s="3">
+        <v>16529600</v>
+      </c>
+      <c r="K17" s="3">
         <v>17866000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16128100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16051500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16195900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17381500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15523600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16243500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10711800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>19442200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>17987000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18526400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>17479100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>23806000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>19835200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>19783000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>18341400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>22188700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>19221300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>19132200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>17689700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>21707800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>18186600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>18780900</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1344400</v>
+        <v>1893300</v>
       </c>
       <c r="E18" s="3">
-        <v>812300</v>
+        <v>1364600</v>
       </c>
       <c r="F18" s="3">
-        <v>2556300</v>
+        <v>824500</v>
       </c>
       <c r="G18" s="3">
-        <v>1302200</v>
+        <v>2594800</v>
       </c>
       <c r="H18" s="3">
-        <v>1362000</v>
+        <v>1321800</v>
       </c>
       <c r="I18" s="3">
-        <v>779200</v>
+        <v>1382500</v>
       </c>
       <c r="J18" s="3">
+        <v>791000</v>
+      </c>
+      <c r="K18" s="3">
         <v>1509100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1143100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1722800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1204700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2117400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>741300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>628000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2887400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1905200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1352200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1588200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1139400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2118400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1793100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1824900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1346700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2170300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1548600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1549500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1191800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1735100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1021800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>939800</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1714,468 +1747,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>159600</v>
+        <v>380800</v>
       </c>
       <c r="E20" s="3">
-        <v>71600</v>
+        <v>162000</v>
       </c>
       <c r="F20" s="3">
-        <v>-38900</v>
+        <v>72600</v>
       </c>
       <c r="G20" s="3">
-        <v>-50200</v>
+        <v>-39500</v>
       </c>
       <c r="H20" s="3">
-        <v>83700</v>
+        <v>-51000</v>
       </c>
       <c r="I20" s="3">
-        <v>-209000</v>
+        <v>84900</v>
       </c>
       <c r="J20" s="3">
+        <v>-212100</v>
+      </c>
+      <c r="K20" s="3">
         <v>175400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>91000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>150500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>69100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>373000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>149700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-235800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>47600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-725600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3452500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-545700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>577900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-53600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2174600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-175700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>335400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-583700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>82700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-132600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>132400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-702400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>286900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2338300</v>
+        <v>2971700</v>
       </c>
       <c r="E21" s="3">
-        <v>1689600</v>
+        <v>2373500</v>
       </c>
       <c r="F21" s="3">
-        <v>3316400</v>
+        <v>1715100</v>
       </c>
       <c r="G21" s="3">
-        <v>2072500</v>
+        <v>3366400</v>
       </c>
       <c r="H21" s="3">
-        <v>2379500</v>
+        <v>2103700</v>
       </c>
       <c r="I21" s="3">
-        <v>1511600</v>
+        <v>2415300</v>
       </c>
       <c r="J21" s="3">
+        <v>1534400</v>
+      </c>
+      <c r="K21" s="3">
         <v>2630100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2160100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2825900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2236100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3486900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1809100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1384600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3774700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2207500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1110500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2001500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2665100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2999300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>481600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2478000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2501800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2422700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2464400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2253700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2112600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1868900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2102600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1987900</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>132400</v>
+        <v>116900</v>
       </c>
       <c r="E22" s="3">
-        <v>117000</v>
+        <v>134400</v>
       </c>
       <c r="F22" s="3">
-        <v>106100</v>
+        <v>118800</v>
       </c>
       <c r="G22" s="3">
-        <v>92200</v>
+        <v>107700</v>
       </c>
       <c r="H22" s="3">
-        <v>80900</v>
+        <v>93600</v>
       </c>
       <c r="I22" s="3">
-        <v>61600</v>
+        <v>82100</v>
       </c>
       <c r="J22" s="3">
+        <v>62500</v>
+      </c>
+      <c r="K22" s="3">
         <v>50500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>44600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>47300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>47400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>40900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>50200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>45100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>37200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>50600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>57400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>58200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>51300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>49200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>54300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>47100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>41700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>45400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>48500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>47200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>44600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>38100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>42000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>41800</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1371600</v>
+        <v>2157100</v>
       </c>
       <c r="E23" s="3">
-        <v>766800</v>
+        <v>1392300</v>
       </c>
       <c r="F23" s="3">
-        <v>2411300</v>
+        <v>778400</v>
       </c>
       <c r="G23" s="3">
-        <v>1159800</v>
+        <v>2447600</v>
       </c>
       <c r="H23" s="3">
-        <v>1364800</v>
+        <v>1177300</v>
       </c>
       <c r="I23" s="3">
-        <v>508700</v>
+        <v>1385300</v>
       </c>
       <c r="J23" s="3">
+        <v>516300</v>
+      </c>
+      <c r="K23" s="3">
         <v>1634000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1189500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1825900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1226400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2449500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>840800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>347000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2897700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1129000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2157700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>984300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1665900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2015600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-435700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1602100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1640400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1541300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1582800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1369600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1279600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>994600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1266600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>926100</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>371200</v>
+        <v>511500</v>
       </c>
       <c r="E24" s="3">
-        <v>224500</v>
+        <v>376800</v>
       </c>
       <c r="F24" s="3">
-        <v>-45600</v>
+        <v>227900</v>
       </c>
       <c r="G24" s="3">
-        <v>276600</v>
+        <v>-46200</v>
       </c>
       <c r="H24" s="3">
-        <v>343600</v>
+        <v>280800</v>
       </c>
       <c r="I24" s="3">
-        <v>196300</v>
+        <v>348700</v>
       </c>
       <c r="J24" s="3">
+        <v>199200</v>
+      </c>
+      <c r="K24" s="3">
         <v>580700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>174000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>185900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>219800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1000000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>347100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>186800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>962900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>762200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1147100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>454200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>377600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>469000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>422800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>407300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>444600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>137800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>394200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>340500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>318200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>339400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>295300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>179000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2266,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1000400</v>
+        <v>1645700</v>
       </c>
       <c r="E26" s="3">
-        <v>542300</v>
+        <v>1015500</v>
       </c>
       <c r="F26" s="3">
-        <v>2456900</v>
+        <v>550500</v>
       </c>
       <c r="G26" s="3">
-        <v>883200</v>
+        <v>2493900</v>
       </c>
       <c r="H26" s="3">
-        <v>1021200</v>
+        <v>896500</v>
       </c>
       <c r="I26" s="3">
-        <v>312400</v>
+        <v>1036600</v>
       </c>
       <c r="J26" s="3">
+        <v>317100</v>
+      </c>
+      <c r="K26" s="3">
         <v>1053300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1015600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1640000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1006600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1449500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>493700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>160200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1934800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>366800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1010700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>530100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1288300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1546600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-858600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1194900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1195800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1403500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1188600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1029200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>961500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>655200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>971300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>747200</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>923500</v>
+        <v>1590600</v>
       </c>
       <c r="E27" s="3">
-        <v>464900</v>
+        <v>937400</v>
       </c>
       <c r="F27" s="3">
-        <v>2369800</v>
+        <v>471900</v>
       </c>
       <c r="G27" s="3">
-        <v>794900</v>
+        <v>2405500</v>
       </c>
       <c r="H27" s="3">
-        <v>898800</v>
+        <v>806900</v>
       </c>
       <c r="I27" s="3">
-        <v>246700</v>
+        <v>912300</v>
       </c>
       <c r="J27" s="3">
+        <v>250400</v>
+      </c>
+      <c r="K27" s="3">
         <v>881000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>881700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1443500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>898400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1373600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>418700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>217000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1907200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>291100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1218500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>637600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1105700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1390100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1038100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>907000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>903300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1089500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>873200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>784200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>679200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>399800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>697700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>509700</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2542,28 +2600,31 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2584,58 +2645,61 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-2900</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-5200</v>
-      </c>
-      <c r="S29" s="3">
-        <v>-3600</v>
       </c>
       <c r="T29" s="3">
         <v>-3600</v>
       </c>
       <c r="U29" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="V29" s="3">
         <v>-3700</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-45500</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-3800</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-91800</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>53400</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-145700</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>12400</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-10900</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-600</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-45100</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-7900</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2726,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2818,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-159600</v>
+        <v>-380800</v>
       </c>
       <c r="E32" s="3">
-        <v>-71600</v>
+        <v>-162000</v>
       </c>
       <c r="F32" s="3">
-        <v>38900</v>
+        <v>-72600</v>
       </c>
       <c r="G32" s="3">
-        <v>50200</v>
+        <v>39500</v>
       </c>
       <c r="H32" s="3">
-        <v>-83700</v>
+        <v>51000</v>
       </c>
       <c r="I32" s="3">
-        <v>209000</v>
+        <v>-84900</v>
       </c>
       <c r="J32" s="3">
+        <v>212100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-175400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-91000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-150500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-69100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-373000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-149700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>235800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-47600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>725600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3452500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>545700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-577900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>53600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2174600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>175700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-335400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>583700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-82700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>132600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-132400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>702400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-286900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-28100</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>923500</v>
+        <v>1590600</v>
       </c>
       <c r="E33" s="3">
-        <v>464900</v>
+        <v>937400</v>
       </c>
       <c r="F33" s="3">
-        <v>2369800</v>
+        <v>471900</v>
       </c>
       <c r="G33" s="3">
-        <v>794900</v>
+        <v>2405500</v>
       </c>
       <c r="H33" s="3">
-        <v>898800</v>
+        <v>806900</v>
       </c>
       <c r="I33" s="3">
-        <v>246700</v>
+        <v>912300</v>
       </c>
       <c r="J33" s="3">
+        <v>250400</v>
+      </c>
+      <c r="K33" s="3">
         <v>881000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>881700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1443500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>898400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1373600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>418700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>214300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1904300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>285900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1222100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>634000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1102000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1344600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1041900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>815200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>956700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>943800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>885600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>773300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>678600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>354800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>689800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3094,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>923500</v>
+        <v>1590600</v>
       </c>
       <c r="E35" s="3">
-        <v>464900</v>
+        <v>937400</v>
       </c>
       <c r="F35" s="3">
-        <v>2369800</v>
+        <v>471900</v>
       </c>
       <c r="G35" s="3">
-        <v>794900</v>
+        <v>2405500</v>
       </c>
       <c r="H35" s="3">
-        <v>898800</v>
+        <v>806900</v>
       </c>
       <c r="I35" s="3">
-        <v>246700</v>
+        <v>912300</v>
       </c>
       <c r="J35" s="3">
+        <v>250400</v>
+      </c>
+      <c r="K35" s="3">
         <v>881000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>881700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1443500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>898400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1373600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>418700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>214300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1904300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>285900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1222100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>634000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1102000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1344600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1041900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>815200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>956700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>943800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>885600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>773300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>678600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>354800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>689800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3317,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3351,183 +3437,187 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6014800</v>
+        <v>5825400</v>
       </c>
       <c r="E41" s="3">
-        <v>6145000</v>
+        <v>6105300</v>
       </c>
       <c r="F41" s="3">
-        <v>5533000</v>
+        <v>6237500</v>
       </c>
       <c r="G41" s="3">
-        <v>5575000</v>
+        <v>5616300</v>
       </c>
       <c r="H41" s="3">
-        <v>5750300</v>
+        <v>5659000</v>
       </c>
       <c r="I41" s="3">
-        <v>7166500</v>
+        <v>5836900</v>
       </c>
       <c r="J41" s="3">
+        <v>7274400</v>
+      </c>
+      <c r="K41" s="3">
         <v>6433000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6802700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6351800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8540600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7202600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6723400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5919500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>15789700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7156600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6326500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7735200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7635500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7761000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6690600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7669800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7402900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6309600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7334400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6944300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>7349700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6787700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6771500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7553100</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2155700</v>
+        <v>1972900</v>
       </c>
       <c r="E42" s="3">
-        <v>2671000</v>
+        <v>2188200</v>
       </c>
       <c r="F42" s="3">
-        <v>2303500</v>
+        <v>2711200</v>
       </c>
       <c r="G42" s="3">
-        <v>1809100</v>
+        <v>2338200</v>
       </c>
       <c r="H42" s="3">
-        <v>2211100</v>
+        <v>1836300</v>
       </c>
       <c r="I42" s="3">
-        <v>2739000</v>
+        <v>2244400</v>
       </c>
       <c r="J42" s="3">
+        <v>2780300</v>
+      </c>
+      <c r="K42" s="3">
         <v>2498700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2058500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2439100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2416300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2326600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2238300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2240900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2179300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2466400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2925600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2532000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2600300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2731800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>3037900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2792200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3453500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>3374800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2939900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2708500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>3501600</v>
-      </c>
-      <c r="AD42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE42" s="3" t="s">
         <v>8</v>
@@ -3535,652 +3625,676 @@
       <c r="AF42" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>19886400</v>
+        <v>18338200</v>
       </c>
       <c r="E43" s="3">
-        <v>18200600</v>
+        <v>20185900</v>
       </c>
       <c r="F43" s="3">
-        <v>19089900</v>
+        <v>18474700</v>
       </c>
       <c r="G43" s="3">
-        <v>17056900</v>
+        <v>19377400</v>
       </c>
       <c r="H43" s="3">
-        <v>18592700</v>
+        <v>17313800</v>
       </c>
       <c r="I43" s="3">
-        <v>18353000</v>
+        <v>18872700</v>
       </c>
       <c r="J43" s="3">
+        <v>18629400</v>
+      </c>
+      <c r="K43" s="3">
         <v>19774900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>18424400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>18472800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>18322300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>19387400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>17315500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>17898000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>14873600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>19912400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>19995800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>19820500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>19347400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>23063400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>20887500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>20792200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>19477900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>22612800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>20017900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>21216900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>19871600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>21957800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>19728100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>25974400</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>12376800</v>
+        <v>10788200</v>
       </c>
       <c r="E44" s="3">
-        <v>12146500</v>
+        <v>12563200</v>
       </c>
       <c r="F44" s="3">
-        <v>10930700</v>
+        <v>12329500</v>
       </c>
       <c r="G44" s="3">
-        <v>11704300</v>
+        <v>11095300</v>
       </c>
       <c r="H44" s="3">
-        <v>13186600</v>
+        <v>11880600</v>
       </c>
       <c r="I44" s="3">
-        <v>15470300</v>
+        <v>13385200</v>
       </c>
       <c r="J44" s="3">
+        <v>15703200</v>
+      </c>
+      <c r="K44" s="3">
         <v>13561700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>13883600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13376400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>13211400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>11722600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>12228700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>12212600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>12348200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>12412700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>14707900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>13615300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>13569800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>13038500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>14975900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>13820200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>13141900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>12432100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>14097600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>12782800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>12369500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>10873800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>12655400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>11737600</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2278200</v>
+        <v>2395700</v>
       </c>
       <c r="E45" s="3">
-        <v>2346300</v>
+        <v>2312500</v>
       </c>
       <c r="F45" s="3">
-        <v>1508300</v>
+        <v>2381700</v>
       </c>
       <c r="G45" s="3">
-        <v>9921800</v>
+        <v>1531100</v>
       </c>
       <c r="H45" s="3">
-        <v>1975700</v>
+        <v>10071200</v>
       </c>
       <c r="I45" s="3">
-        <v>2009900</v>
+        <v>2005500</v>
       </c>
       <c r="J45" s="3">
+        <v>2040100</v>
+      </c>
+      <c r="K45" s="3">
         <v>1551800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2556900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2070600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1818300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1498800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1681100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1832800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4113500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4018800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6546100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2042700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2117200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1799400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2361700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2166700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2156900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1842900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2258300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2187200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2212300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4753800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4708100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4654500</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>42711800</v>
+        <v>39320400</v>
       </c>
       <c r="E46" s="3">
-        <v>41509400</v>
+        <v>43355100</v>
       </c>
       <c r="F46" s="3">
-        <v>39365500</v>
+        <v>42134500</v>
       </c>
       <c r="G46" s="3">
-        <v>46067100</v>
+        <v>39958300</v>
       </c>
       <c r="H46" s="3">
-        <v>41716500</v>
+        <v>46760900</v>
       </c>
       <c r="I46" s="3">
-        <v>45738600</v>
+        <v>42344800</v>
       </c>
       <c r="J46" s="3">
+        <v>46427400</v>
+      </c>
+      <c r="K46" s="3">
         <v>43820200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>43726000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>42710700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>44308900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>42138000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>40187000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>40103800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>49304300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>45967000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>50502000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>45745800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>45270100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>48394000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>47953500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>47241100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>45633100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>46572300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>46648100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>45839800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>45304800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>44373100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>43863100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>49919500</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>6888000</v>
+        <v>8575100</v>
       </c>
       <c r="E47" s="3">
-        <v>6889100</v>
+        <v>6991700</v>
       </c>
       <c r="F47" s="3">
-        <v>6477400</v>
+        <v>6992900</v>
       </c>
       <c r="G47" s="3">
-        <v>6381700</v>
+        <v>6575000</v>
       </c>
       <c r="H47" s="3">
-        <v>7414100</v>
+        <v>6477800</v>
       </c>
       <c r="I47" s="3">
-        <v>6831400</v>
+        <v>7525800</v>
       </c>
       <c r="J47" s="3">
+        <v>6934300</v>
+      </c>
+      <c r="K47" s="3">
         <v>6613500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6824000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7105800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7097900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7135600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6667500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7063000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7699800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>8113000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>9074100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>12086600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>11909900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12423900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12268900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12733300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12636400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13196900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>13425300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13164700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>12783700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>12515200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>13097300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>16937400</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>11774700</v>
+        <v>7909900</v>
       </c>
       <c r="E48" s="3">
-        <v>11669800</v>
+        <v>11952000</v>
       </c>
       <c r="F48" s="3">
-        <v>11291100</v>
+        <v>11845600</v>
       </c>
       <c r="G48" s="3">
-        <v>11285700</v>
+        <v>11461200</v>
       </c>
       <c r="H48" s="3">
-        <v>14041500</v>
+        <v>11455600</v>
       </c>
       <c r="I48" s="3">
-        <v>17018500</v>
+        <v>14252900</v>
       </c>
       <c r="J48" s="3">
+        <v>17274800</v>
+      </c>
+      <c r="K48" s="3">
         <v>16459900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16629700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>17237600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17652400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17079000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15682000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16694300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>16517900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19076400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20106600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19703700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19759100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>18803700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>18389900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20003800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19357100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19208400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19232200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>18881700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>18246800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>17725900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>17662900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>20069600</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>24870200</v>
+        <v>22753300</v>
       </c>
       <c r="E49" s="3">
-        <v>24293900</v>
+        <v>25244700</v>
       </c>
       <c r="F49" s="3">
-        <v>22642700</v>
+        <v>24659800</v>
       </c>
       <c r="G49" s="3">
-        <v>22200800</v>
+        <v>22983700</v>
       </c>
       <c r="H49" s="3">
-        <v>24797100</v>
+        <v>22535100</v>
       </c>
       <c r="I49" s="3">
-        <v>24740900</v>
+        <v>25170600</v>
       </c>
       <c r="J49" s="3">
+        <v>25113500</v>
+      </c>
+      <c r="K49" s="3">
         <v>22647900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22308700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>23106900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15617200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15073600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14192100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15141300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9038200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9829500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10478300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8381100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8770800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9225800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9348100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9968300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9621800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9531500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>10139000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>10111900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>8483100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>8153300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>8193600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>8309100</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4271,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4363,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3230600</v>
+        <v>2814800</v>
       </c>
       <c r="E52" s="3">
-        <v>2989500</v>
+        <v>3279300</v>
       </c>
       <c r="F52" s="3">
-        <v>3232700</v>
+        <v>3034500</v>
       </c>
       <c r="G52" s="3">
-        <v>2250600</v>
+        <v>3281400</v>
       </c>
       <c r="H52" s="3">
-        <v>2450000</v>
+        <v>2284500</v>
       </c>
       <c r="I52" s="3">
-        <v>2628300</v>
+        <v>2486900</v>
       </c>
       <c r="J52" s="3">
+        <v>2667900</v>
+      </c>
+      <c r="K52" s="3">
         <v>2671500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2733700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2700300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2786600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2610500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3472000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3696300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4109000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4498100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3502200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3405900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3442200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3664200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3546200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3512500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3057200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2854500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2728600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2784700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2792500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2951400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2691400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9247200</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4547,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>89475400</v>
+        <v>81373400</v>
       </c>
       <c r="E54" s="3">
-        <v>87351600</v>
+        <v>90822900</v>
       </c>
       <c r="F54" s="3">
-        <v>83009400</v>
+        <v>88667200</v>
       </c>
       <c r="G54" s="3">
-        <v>88185900</v>
+        <v>84259500</v>
       </c>
       <c r="H54" s="3">
-        <v>90419200</v>
+        <v>89514000</v>
       </c>
       <c r="I54" s="3">
-        <v>96957800</v>
+        <v>91780900</v>
       </c>
       <c r="J54" s="3">
+        <v>98418000</v>
+      </c>
+      <c r="K54" s="3">
         <v>92213000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>92222000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>92861400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>87463100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>84036700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>80200700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>82698800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>86669200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>87484000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>93663200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>89323100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>89152000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>92511500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>91506600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>93459000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>90305500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>91363700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>92173200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>90782700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>87610900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>85718900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>85508400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>104482800</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4673,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4707,560 +4837,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>10466100</v>
+        <v>9047700</v>
       </c>
       <c r="E57" s="3">
-        <v>10422100</v>
+        <v>10623700</v>
       </c>
       <c r="F57" s="3">
-        <v>10282000</v>
+        <v>10579100</v>
       </c>
       <c r="G57" s="3">
-        <v>9818900</v>
+        <v>10436900</v>
       </c>
       <c r="H57" s="3">
-        <v>11321500</v>
+        <v>9966800</v>
       </c>
       <c r="I57" s="3">
-        <v>11925400</v>
+        <v>11492000</v>
       </c>
       <c r="J57" s="3">
+        <v>12105000</v>
+      </c>
+      <c r="K57" s="3">
         <v>11650800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10957900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10787600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11144000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10748100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9809900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9797100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9368400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>11194600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11828400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>11275400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11927900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>13511800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12785400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>12738900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12718200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>13894300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>13397100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12889700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12346100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12437800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>11908500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>11654900</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6872400</v>
+        <v>3952500</v>
       </c>
       <c r="E58" s="3">
-        <v>7214100</v>
+        <v>6975900</v>
       </c>
       <c r="F58" s="3">
-        <v>6105600</v>
+        <v>7322700</v>
       </c>
       <c r="G58" s="3">
-        <v>11604500</v>
+        <v>6197500</v>
       </c>
       <c r="H58" s="3">
-        <v>8977100</v>
+        <v>11779300</v>
       </c>
       <c r="I58" s="3">
-        <v>12297800</v>
+        <v>9112300</v>
       </c>
       <c r="J58" s="3">
+        <v>12483000</v>
+      </c>
+      <c r="K58" s="3">
         <v>10428400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13041400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12086700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6548900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4899400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9077200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>12284200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>12318200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3652100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6529700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5029300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4536800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2847300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5429700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4508500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4229900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2157200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3742700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3865500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4202800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3429100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3937900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>12512300</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>19684200</v>
+        <v>19683100</v>
       </c>
       <c r="E59" s="3">
-        <v>18659700</v>
+        <v>19980600</v>
       </c>
       <c r="F59" s="3">
-        <v>17915800</v>
+        <v>18940700</v>
       </c>
       <c r="G59" s="3">
-        <v>18961400</v>
+        <v>18185700</v>
       </c>
       <c r="H59" s="3">
-        <v>18278800</v>
+        <v>19247000</v>
       </c>
       <c r="I59" s="3">
-        <v>16765400</v>
+        <v>18554100</v>
       </c>
       <c r="J59" s="3">
+        <v>17017900</v>
+      </c>
+      <c r="K59" s="3">
         <v>16791900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15810000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16046600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>16697900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>16944700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15956700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16120700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17854300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18042600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>19847800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>16505800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>16298200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>18290400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>17134300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>17568000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>16763300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>18258800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>17693700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>17628000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>16719600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>17137200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>16265100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>16240700</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>37022700</v>
+        <v>32683300</v>
       </c>
       <c r="E60" s="3">
-        <v>36295900</v>
+        <v>37580300</v>
       </c>
       <c r="F60" s="3">
-        <v>34303400</v>
+        <v>36842500</v>
       </c>
       <c r="G60" s="3">
-        <v>40384900</v>
+        <v>34820000</v>
       </c>
       <c r="H60" s="3">
-        <v>38577300</v>
+        <v>40993100</v>
       </c>
       <c r="I60" s="3">
-        <v>40988600</v>
+        <v>39158300</v>
       </c>
       <c r="J60" s="3">
+        <v>41605900</v>
+      </c>
+      <c r="K60" s="3">
         <v>38871000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>39809300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>38920800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>34390800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>32592200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>34843800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>38202100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>39540800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>32889300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>38205800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>32810500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>32762900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>34649400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>35349400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>34815400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>33711400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>34310400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>34833500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>34383200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>33268500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>33004000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>32111400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>40407900</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8903200</v>
+        <v>7873300</v>
       </c>
       <c r="E61" s="3">
-        <v>8849000</v>
+        <v>9037300</v>
       </c>
       <c r="F61" s="3">
-        <v>8591100</v>
+        <v>8982300</v>
       </c>
       <c r="G61" s="3">
-        <v>8678900</v>
+        <v>8720500</v>
       </c>
       <c r="H61" s="3">
-        <v>9646700</v>
+        <v>8809600</v>
       </c>
       <c r="I61" s="3">
-        <v>10676400</v>
+        <v>9792000</v>
       </c>
       <c r="J61" s="3">
+        <v>10837200</v>
+      </c>
+      <c r="K61" s="3">
         <v>10333000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11118900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11804800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12061200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12097900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9983800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7275300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8505400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9431100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7705500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7720200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8081000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6808600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7076600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6652500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6755400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7337400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7529400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7629600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7261000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7007400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7631500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>19851800</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4866400</v>
+        <v>4263200</v>
       </c>
       <c r="E62" s="3">
-        <v>4766700</v>
+        <v>4939700</v>
       </c>
       <c r="F62" s="3">
-        <v>4686700</v>
+        <v>4838500</v>
       </c>
       <c r="G62" s="3">
-        <v>4789300</v>
+        <v>4757300</v>
       </c>
       <c r="H62" s="3">
-        <v>5550200</v>
+        <v>4861400</v>
       </c>
       <c r="I62" s="3">
-        <v>7782600</v>
+        <v>5633700</v>
       </c>
       <c r="J62" s="3">
+        <v>7899900</v>
+      </c>
+      <c r="K62" s="3">
         <v>7450000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7621300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7886600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7913300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7737800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8641200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9389500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7054800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7573600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8011800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7935100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7819600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8631100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8503900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8634300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8575800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8930400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>9587400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>9519400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>9427600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>9367200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>9692000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9942400</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5351,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5443,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5535,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>53514400</v>
+        <v>45795300</v>
       </c>
       <c r="E66" s="3">
-        <v>52524100</v>
+        <v>54320300</v>
       </c>
       <c r="F66" s="3">
-        <v>50188800</v>
+        <v>53315100</v>
       </c>
       <c r="G66" s="3">
-        <v>58145400</v>
+        <v>50944700</v>
       </c>
       <c r="H66" s="3">
-        <v>58208000</v>
+        <v>59021100</v>
       </c>
       <c r="I66" s="3">
-        <v>66292900</v>
+        <v>59084600</v>
       </c>
       <c r="J66" s="3">
+        <v>67291300</v>
+      </c>
+      <c r="K66" s="3">
         <v>63383200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>65084500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>65283900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>61047200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>59040900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>58736000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>59983500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>60767600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>59644500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>64242700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>58617400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>59031200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>61157900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>61843400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>61415400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>59788500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>61730400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>63059800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>62347900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>60372500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>59400900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>59920500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>81205500</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5661,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5753,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5845,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5937,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6029,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>25117300</v>
+        <v>25908800</v>
       </c>
       <c r="E72" s="3">
-        <v>24186000</v>
+        <v>25495600</v>
       </c>
       <c r="F72" s="3">
-        <v>24150900</v>
+        <v>24550300</v>
       </c>
       <c r="G72" s="3">
-        <v>21649600</v>
+        <v>24514600</v>
       </c>
       <c r="H72" s="3">
-        <v>22299200</v>
+        <v>21975700</v>
       </c>
       <c r="I72" s="3">
-        <v>21343200</v>
+        <v>22635100</v>
       </c>
       <c r="J72" s="3">
+        <v>21664600</v>
+      </c>
+      <c r="K72" s="3">
         <v>21232900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20987100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>21520400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20473000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19218200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>18264800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>19425200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>21120100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>20229600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>20621300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>22424100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>21711000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>21983700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>20149100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>21201100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>19948300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>19032800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18040300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>17443200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>16664700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>15909000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>15530900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>15048500</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6213,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6305,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6397,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>35961000</v>
+        <v>35578200</v>
       </c>
       <c r="E76" s="3">
-        <v>34827600</v>
+        <v>36502600</v>
       </c>
       <c r="F76" s="3">
-        <v>32820600</v>
+        <v>35352100</v>
       </c>
       <c r="G76" s="3">
-        <v>30040500</v>
+        <v>33314800</v>
       </c>
       <c r="H76" s="3">
-        <v>32211200</v>
+        <v>30492900</v>
       </c>
       <c r="I76" s="3">
-        <v>30664800</v>
+        <v>32696300</v>
       </c>
       <c r="J76" s="3">
+        <v>31126700</v>
+      </c>
+      <c r="K76" s="3">
         <v>28829800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>27137600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>27577500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>26415900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>24995800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21464600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22715300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>25901600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>27839500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>29420500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>30705700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>30120900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>31353600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>29663100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>32043600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>30517000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>29633300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>29113400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>28434800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>27238300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>26318000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>25587900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>23277400</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6581,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>923500</v>
+        <v>1590600</v>
       </c>
       <c r="E81" s="3">
-        <v>464900</v>
+        <v>937400</v>
       </c>
       <c r="F81" s="3">
-        <v>2369800</v>
+        <v>471900</v>
       </c>
       <c r="G81" s="3">
-        <v>794900</v>
+        <v>2405500</v>
       </c>
       <c r="H81" s="3">
-        <v>898800</v>
+        <v>806900</v>
       </c>
       <c r="I81" s="3">
-        <v>246700</v>
+        <v>912300</v>
       </c>
       <c r="J81" s="3">
+        <v>250400</v>
+      </c>
+      <c r="K81" s="3">
         <v>881000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>881700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1443500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>898400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1373600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>418700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>214300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1904300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>285900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1222100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>634000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1102000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1344600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1041900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>815200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>956700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>943800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>885600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>773300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>678600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>354800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>689800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6804,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>834300</v>
+        <v>697700</v>
       </c>
       <c r="E83" s="3">
-        <v>805800</v>
+        <v>846900</v>
       </c>
       <c r="F83" s="3">
-        <v>799000</v>
+        <v>817900</v>
       </c>
       <c r="G83" s="3">
-        <v>820400</v>
+        <v>811100</v>
       </c>
       <c r="H83" s="3">
-        <v>933800</v>
+        <v>832800</v>
       </c>
       <c r="I83" s="3">
-        <v>941400</v>
+        <v>947900</v>
       </c>
       <c r="J83" s="3">
+        <v>955600</v>
+      </c>
+      <c r="K83" s="3">
         <v>945700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>926000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>952600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>962300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>996500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>918100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>992500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>839800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1027900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>989800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>959000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>947800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>934400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>863000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>828800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>819700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>836100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>833100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>836900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>788400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>836200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>793900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1019900</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6988,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7080,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7172,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7264,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7356,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1319800</v>
+        <v>1522800</v>
       </c>
       <c r="E89" s="3">
-        <v>784600</v>
+        <v>1339700</v>
       </c>
       <c r="F89" s="3">
-        <v>2967800</v>
+        <v>796400</v>
       </c>
       <c r="G89" s="3">
-        <v>972300</v>
+        <v>3012500</v>
       </c>
       <c r="H89" s="3">
-        <v>846600</v>
+        <v>987000</v>
       </c>
       <c r="I89" s="3">
-        <v>704900</v>
+        <v>859300</v>
       </c>
       <c r="J89" s="3">
+        <v>715500</v>
+      </c>
+      <c r="K89" s="3">
         <v>3139300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>657400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>175900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1007500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2600100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1553300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>472800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1311900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2229600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>930700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1165500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>722400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3917700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-91000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>721300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1221300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2295800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1760400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1369900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1147500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2221100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>835800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1773600</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7482,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-78532000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-106661000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-89091000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-105408000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-96150000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-108272000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-100755000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-134149000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100626000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-107573000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-488900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-628300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-384800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-471300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-453200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-794100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-595900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-811800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-723700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-857900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-898800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-883000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-934700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-11900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1277100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-889100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2139000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7666,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7758,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-467600</v>
+        <v>-415900</v>
       </c>
       <c r="E94" s="3">
-        <v>-264700</v>
+        <v>-474700</v>
       </c>
       <c r="F94" s="3">
-        <v>1967700</v>
+        <v>-268700</v>
       </c>
       <c r="G94" s="3">
-        <v>-484300</v>
+        <v>1997300</v>
       </c>
       <c r="H94" s="3">
-        <v>-2100</v>
+        <v>-491600</v>
       </c>
       <c r="I94" s="3">
-        <v>-478200</v>
+        <v>-2200</v>
       </c>
       <c r="J94" s="3">
+        <v>-485400</v>
+      </c>
+      <c r="K94" s="3">
         <v>-140400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-524200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6808900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-51800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2178300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-455900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8267800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>3049100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-297800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2595800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-937000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-962900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>121300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-311700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-357900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-944800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1447200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-721200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1173700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-945800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1217900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>141000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1198700</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7884,100 +8117,104 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-500200</v>
+      </c>
+      <c r="E96" s="3">
+        <v>900</v>
+      </c>
+      <c r="F96" s="3">
+        <v>-474200</v>
+      </c>
+      <c r="G96" s="3">
+        <v>700</v>
+      </c>
+      <c r="H96" s="3">
+        <v>-447400</v>
+      </c>
+      <c r="I96" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J96" s="3">
+        <v>-424400</v>
+      </c>
+      <c r="K96" s="3">
+        <v>600</v>
+      </c>
+      <c r="L96" s="3">
+        <v>-399200</v>
+      </c>
+      <c r="M96" s="3">
         <v>800</v>
       </c>
-      <c r="E96" s="3">
-        <v>-467200</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="N96" s="3">
+        <v>-391300</v>
+      </c>
+      <c r="O96" s="3">
         <v>600</v>
       </c>
-      <c r="G96" s="3">
-        <v>-440700</v>
-      </c>
-      <c r="H96" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-418100</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="P96" s="3">
+        <v>-355300</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R96" s="3">
+        <v>-412600</v>
+      </c>
+      <c r="S96" s="3">
         <v>600</v>
       </c>
-      <c r="K96" s="3">
-        <v>-399200</v>
-      </c>
-      <c r="L96" s="3">
-        <v>800</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-391300</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="T96" s="3">
+        <v>-397200</v>
+      </c>
+      <c r="U96" s="3">
+        <v>1500</v>
+      </c>
+      <c r="V96" s="3">
+        <v>-442700</v>
+      </c>
+      <c r="W96" s="3">
+        <v>700</v>
+      </c>
+      <c r="X96" s="3">
+        <v>-365100</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>-351500</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>-305900</v>
+      </c>
+      <c r="AC96" s="3">
         <v>600</v>
       </c>
-      <c r="O96" s="3">
-        <v>-355300</v>
-      </c>
-      <c r="P96" s="3">
-        <v>1100</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-412600</v>
-      </c>
-      <c r="R96" s="3">
-        <v>600</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-397200</v>
-      </c>
-      <c r="T96" s="3">
-        <v>1500</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-442700</v>
-      </c>
-      <c r="V96" s="3">
-        <v>700</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-365100</v>
-      </c>
-      <c r="X96" s="3">
-        <v>700</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-351500</v>
-      </c>
-      <c r="Z96" s="3">
+      <c r="AD96" s="3">
+        <v>-305900</v>
+      </c>
+      <c r="AE96" s="3">
         <v>400</v>
       </c>
-      <c r="AA96" s="3">
-        <v>-305900</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>600</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-305900</v>
-      </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
+        <v>-257400</v>
+      </c>
+      <c r="AG96" s="3">
         <v>400</v>
       </c>
-      <c r="AE96" s="3">
-        <v>-257400</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8068,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8160,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8252,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1106600</v>
+        <v>-1222800</v>
       </c>
       <c r="E100" s="3">
-        <v>-183700</v>
+        <v>-1123300</v>
       </c>
       <c r="F100" s="3">
-        <v>-5857200</v>
+        <v>-186500</v>
       </c>
       <c r="G100" s="3">
-        <v>515400</v>
+        <v>-5945400</v>
       </c>
       <c r="H100" s="3">
-        <v>-2353700</v>
+        <v>523100</v>
       </c>
       <c r="I100" s="3">
-        <v>106300</v>
+        <v>-2389200</v>
       </c>
       <c r="J100" s="3">
+        <v>107900</v>
+      </c>
+      <c r="K100" s="3">
         <v>-3369100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>436900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4584400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>78600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4395900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>9900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-723400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4492600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-740400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>152600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-25700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>668100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3116400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-529700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-258300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>797900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1618500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-748700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-709100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>170400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-864900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2288400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>989900</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>124300</v>
+        <v>-164000</v>
       </c>
       <c r="E101" s="3">
-        <v>275800</v>
+        <v>126200</v>
       </c>
       <c r="F101" s="3">
-        <v>85000</v>
+        <v>279900</v>
       </c>
       <c r="G101" s="3">
-        <v>-384000</v>
+        <v>86300</v>
       </c>
       <c r="H101" s="3">
-        <v>93200</v>
+        <v>-389800</v>
       </c>
       <c r="I101" s="3">
-        <v>400500</v>
+        <v>94600</v>
       </c>
       <c r="J101" s="3">
+        <v>406600</v>
+      </c>
+      <c r="K101" s="3">
         <v>228200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>180400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>22500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>39600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>316900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>46100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>18000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>7000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-152900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>171200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-128000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-189700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>27200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-170600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-16000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-254800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>99500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>107600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>59800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-122100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>530100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-69300</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-130200</v>
+        <v>-280000</v>
       </c>
       <c r="E102" s="3">
-        <v>612000</v>
+        <v>-132200</v>
       </c>
       <c r="F102" s="3">
-        <v>-836700</v>
+        <v>621200</v>
       </c>
       <c r="G102" s="3">
-        <v>619400</v>
+        <v>-849300</v>
       </c>
       <c r="H102" s="3">
-        <v>-1416100</v>
+        <v>628700</v>
       </c>
       <c r="I102" s="3">
-        <v>733400</v>
+        <v>-1437400</v>
       </c>
       <c r="J102" s="3">
+        <v>744500</v>
+      </c>
+      <c r="K102" s="3">
         <v>-141900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>750500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2026200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1073900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>699400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1153400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-8500500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>8860600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1038400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1341400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>74800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>237900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>949900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1103100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>104000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1058400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1024800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>390000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-405400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>431900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>16200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-781600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1495500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HTHIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HTHIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
   <si>
     <t>HTHIY</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>15219500</v>
+        <v>16017400</v>
       </c>
       <c r="E8" s="3">
-        <v>17777300</v>
+        <v>14406600</v>
       </c>
       <c r="F8" s="3">
-        <v>15653600</v>
+        <v>16827800</v>
       </c>
       <c r="G8" s="3">
-        <v>18685700</v>
+        <v>14817500</v>
       </c>
       <c r="H8" s="3">
-        <v>18144200</v>
+        <v>17687600</v>
       </c>
       <c r="I8" s="3">
-        <v>19188500</v>
+        <v>17175100</v>
       </c>
       <c r="J8" s="3">
+        <v>18163600</v>
+      </c>
+      <c r="K8" s="3">
         <v>17320600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19375100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17271200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17774300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17400700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19498900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>16264900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16871400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13599200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>21347400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>19339200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>20114600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>18618500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>25924400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>21628300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>21607900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>19688000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>24359100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>20770000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>20681700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>18881600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>23443000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>19208300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>19720700</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>10951800</v>
+        <v>11428000</v>
       </c>
       <c r="E9" s="3">
-        <v>13361800</v>
+        <v>10366900</v>
       </c>
       <c r="F9" s="3">
-        <v>11781700</v>
+        <v>12648200</v>
       </c>
       <c r="G9" s="3">
-        <v>13939300</v>
+        <v>11152500</v>
       </c>
       <c r="H9" s="3">
-        <v>13630700</v>
+        <v>13194700</v>
       </c>
       <c r="I9" s="3">
-        <v>14472200</v>
+        <v>12902700</v>
       </c>
       <c r="J9" s="3">
+        <v>13699200</v>
+      </c>
+      <c r="K9" s="3">
         <v>13172300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14433800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12948800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13386900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13161400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14759900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12099600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12635200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10060500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>15555900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14178700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14579000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13633700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>19379600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>15751100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>15728800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>14420300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>17804700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>15290000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>15148400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>13830300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>17433900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>14170500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>14505800</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4267600</v>
+        <v>4589400</v>
       </c>
       <c r="E10" s="3">
-        <v>4415500</v>
+        <v>4039700</v>
       </c>
       <c r="F10" s="3">
-        <v>3871800</v>
+        <v>4179600</v>
       </c>
       <c r="G10" s="3">
-        <v>4746400</v>
+        <v>3665000</v>
       </c>
       <c r="H10" s="3">
-        <v>4513500</v>
+        <v>4492900</v>
       </c>
       <c r="I10" s="3">
-        <v>4716300</v>
+        <v>4272400</v>
       </c>
       <c r="J10" s="3">
+        <v>4464400</v>
+      </c>
+      <c r="K10" s="3">
         <v>4148300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4941300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4322400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4387400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4239200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4739000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4165300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4236200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3538700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5791400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5160500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5535500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4984800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>6544800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5877200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5879200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5267700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>6554300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>5479900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5533300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5051300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>6009100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5037800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>5214900</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,62 +1318,65 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>-543800</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
-        <v>-50800</v>
+        <v>-514800</v>
       </c>
       <c r="F14" s="3">
-        <v>55400</v>
+        <v>-48000</v>
       </c>
       <c r="G14" s="3">
-        <v>-1107700</v>
+        <v>52400</v>
       </c>
       <c r="H14" s="3">
-        <v>45500</v>
+        <v>-1048500</v>
       </c>
       <c r="I14" s="3">
-        <v>-13700</v>
+        <v>43100</v>
       </c>
       <c r="J14" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="K14" s="3">
         <v>28300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>176000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>55000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-428000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-245700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-853500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>256500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>325700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-2389500</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
@@ -1396,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13326200</v>
+        <v>14549300</v>
       </c>
       <c r="E17" s="3">
-        <v>16412700</v>
+        <v>12614400</v>
       </c>
       <c r="F17" s="3">
-        <v>14829100</v>
+        <v>15536000</v>
       </c>
       <c r="G17" s="3">
-        <v>16090800</v>
+        <v>14037000</v>
       </c>
       <c r="H17" s="3">
-        <v>16822400</v>
+        <v>15231400</v>
       </c>
       <c r="I17" s="3">
-        <v>17806000</v>
+        <v>15923800</v>
       </c>
       <c r="J17" s="3">
+        <v>16855000</v>
+      </c>
+      <c r="K17" s="3">
         <v>16529600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17866000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16128100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16051500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16195900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17381500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15523600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16243500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10711800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>19442200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>17987000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>18526400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>17479100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>23806000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>19835200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>19783000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>18341400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>22188700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>19221300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>19132200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>17689700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>21707800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>18186600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>18780900</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1893300</v>
+        <v>1468100</v>
       </c>
       <c r="E18" s="3">
-        <v>1364600</v>
+        <v>1792200</v>
       </c>
       <c r="F18" s="3">
-        <v>824500</v>
+        <v>1291700</v>
       </c>
       <c r="G18" s="3">
-        <v>2594800</v>
+        <v>780500</v>
       </c>
       <c r="H18" s="3">
-        <v>1321800</v>
+        <v>2456200</v>
       </c>
       <c r="I18" s="3">
-        <v>1382500</v>
+        <v>1251200</v>
       </c>
       <c r="J18" s="3">
+        <v>1308600</v>
+      </c>
+      <c r="K18" s="3">
         <v>791000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1509100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1143100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1722800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1204700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2117400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>741300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>628000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2887400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1905200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1352200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1588200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1139400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2118400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1793100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1824900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1346700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2170300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1548600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1549500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1191800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1735100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1021800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>939800</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,483 +1781,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>380800</v>
+        <v>-194000</v>
       </c>
       <c r="E20" s="3">
-        <v>162000</v>
+        <v>360400</v>
       </c>
       <c r="F20" s="3">
-        <v>72600</v>
+        <v>153400</v>
       </c>
       <c r="G20" s="3">
-        <v>-39500</v>
+        <v>68800</v>
       </c>
       <c r="H20" s="3">
-        <v>-51000</v>
+        <v>-37400</v>
       </c>
       <c r="I20" s="3">
-        <v>84900</v>
+        <v>-48200</v>
       </c>
       <c r="J20" s="3">
+        <v>80400</v>
+      </c>
+      <c r="K20" s="3">
         <v>-212100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>175400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>91000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>150500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>69100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>373000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>149700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-235800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>47600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-725600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3452500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-545700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>577900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-53600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2174600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-175700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>335400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-583700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>82700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-132600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>132400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-702400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>286900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2971700</v>
+        <v>1918600</v>
       </c>
       <c r="E21" s="3">
-        <v>2373500</v>
+        <v>2813000</v>
       </c>
       <c r="F21" s="3">
-        <v>1715100</v>
+        <v>2246800</v>
       </c>
       <c r="G21" s="3">
-        <v>3366400</v>
+        <v>1623500</v>
       </c>
       <c r="H21" s="3">
-        <v>2103700</v>
+        <v>3186600</v>
       </c>
       <c r="I21" s="3">
-        <v>2415300</v>
+        <v>1991300</v>
       </c>
       <c r="J21" s="3">
+        <v>2286300</v>
+      </c>
+      <c r="K21" s="3">
         <v>1534400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2630100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2160100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2825900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2236100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3486900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1809100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1384600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3774700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2207500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1110500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2001500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2665100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2999300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>481600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2478000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2501800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2422700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2464400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2253700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2112600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1868900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2102600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1987900</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>116900</v>
+        <v>102200</v>
       </c>
       <c r="E22" s="3">
-        <v>134400</v>
+        <v>110700</v>
       </c>
       <c r="F22" s="3">
-        <v>118800</v>
+        <v>127200</v>
       </c>
       <c r="G22" s="3">
-        <v>107700</v>
+        <v>112400</v>
       </c>
       <c r="H22" s="3">
-        <v>93600</v>
+        <v>101900</v>
       </c>
       <c r="I22" s="3">
-        <v>82100</v>
+        <v>88600</v>
       </c>
       <c r="J22" s="3">
+        <v>77700</v>
+      </c>
+      <c r="K22" s="3">
         <v>62500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>50500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>44600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>47300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>47400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>40900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>50200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>45100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>37200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>50600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>57400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>58200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>51300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>49200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>54300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>47100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>41700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>45400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>48500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>47200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>44600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>38100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>42000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>41800</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2157100</v>
+        <v>1172000</v>
       </c>
       <c r="E23" s="3">
-        <v>1392300</v>
+        <v>2041900</v>
       </c>
       <c r="F23" s="3">
-        <v>778400</v>
+        <v>1317900</v>
       </c>
       <c r="G23" s="3">
-        <v>2447600</v>
+        <v>736800</v>
       </c>
       <c r="H23" s="3">
-        <v>1177300</v>
+        <v>2316900</v>
       </c>
       <c r="I23" s="3">
-        <v>1385300</v>
+        <v>1114400</v>
       </c>
       <c r="J23" s="3">
+        <v>1311300</v>
+      </c>
+      <c r="K23" s="3">
         <v>516300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1634000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1189500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1825900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1226400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2449500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>840800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>347000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2897700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1129000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2157700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>984300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1665900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2015600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-435700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1602100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1640400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1541300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1582800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1369600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1279600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>994600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1266600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>926100</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>511500</v>
+        <v>213400</v>
       </c>
       <c r="E24" s="3">
-        <v>376800</v>
+        <v>484100</v>
       </c>
       <c r="F24" s="3">
-        <v>227900</v>
+        <v>356700</v>
       </c>
       <c r="G24" s="3">
-        <v>-46200</v>
+        <v>215700</v>
       </c>
       <c r="H24" s="3">
-        <v>280800</v>
+        <v>-43800</v>
       </c>
       <c r="I24" s="3">
-        <v>348700</v>
+        <v>265800</v>
       </c>
       <c r="J24" s="3">
+        <v>330100</v>
+      </c>
+      <c r="K24" s="3">
         <v>199200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>580700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>174000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>185900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>219800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1000000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>347100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>186800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>962900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>762200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1147100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>454200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>377600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>469000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>422800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>407300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>444600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>137800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>394200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>340500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>318200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>339400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>295300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>179000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1645700</v>
+        <v>958600</v>
       </c>
       <c r="E26" s="3">
-        <v>1015500</v>
+        <v>1557800</v>
       </c>
       <c r="F26" s="3">
-        <v>550500</v>
+        <v>961200</v>
       </c>
       <c r="G26" s="3">
-        <v>2493900</v>
+        <v>521100</v>
       </c>
       <c r="H26" s="3">
-        <v>896500</v>
+        <v>2360700</v>
       </c>
       <c r="I26" s="3">
-        <v>1036600</v>
+        <v>848600</v>
       </c>
       <c r="J26" s="3">
+        <v>981200</v>
+      </c>
+      <c r="K26" s="3">
         <v>317100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1053300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1015600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1640000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1006600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1449500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>493700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>160200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1934800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>366800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1010700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>530100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1288300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1546600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-858600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1194900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1195800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1403500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1188600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1029200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>961500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>655200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>971300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>747200</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1590600</v>
+        <v>923800</v>
       </c>
       <c r="E27" s="3">
-        <v>937400</v>
+        <v>1505600</v>
       </c>
       <c r="F27" s="3">
-        <v>471900</v>
+        <v>887300</v>
       </c>
       <c r="G27" s="3">
-        <v>2405500</v>
+        <v>446700</v>
       </c>
       <c r="H27" s="3">
-        <v>806900</v>
+        <v>2277000</v>
       </c>
       <c r="I27" s="3">
-        <v>912300</v>
+        <v>763800</v>
       </c>
       <c r="J27" s="3">
+        <v>863600</v>
+      </c>
+      <c r="K27" s="3">
         <v>250400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>881000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>881700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1443500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>898400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1373600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>418700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>217000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1907200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>291100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1218500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>637600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1105700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1390100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1038100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>907000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>903300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1089500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>873200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>784200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>679200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>399800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>697700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>509700</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2648,58 +2709,61 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-2700</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-2900</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-5200</v>
-      </c>
-      <c r="T29" s="3">
-        <v>-3600</v>
       </c>
       <c r="U29" s="3">
         <v>-3600</v>
       </c>
       <c r="V29" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="W29" s="3">
         <v>-3700</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-45500</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-91800</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>53400</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-145700</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>12400</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-10900</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-600</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-45100</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-7900</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-380800</v>
+        <v>194000</v>
       </c>
       <c r="E32" s="3">
-        <v>-162000</v>
+        <v>-360400</v>
       </c>
       <c r="F32" s="3">
-        <v>-72600</v>
+        <v>-153400</v>
       </c>
       <c r="G32" s="3">
-        <v>39500</v>
+        <v>-68800</v>
       </c>
       <c r="H32" s="3">
-        <v>51000</v>
+        <v>37400</v>
       </c>
       <c r="I32" s="3">
-        <v>-84900</v>
+        <v>48200</v>
       </c>
       <c r="J32" s="3">
+        <v>-80400</v>
+      </c>
+      <c r="K32" s="3">
         <v>212100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-175400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-91000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-150500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-69100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-373000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-149700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>235800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-47600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>725600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3452500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>545700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-577900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>53600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2174600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>175700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-335400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>583700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-82700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>132600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-132400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>702400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-286900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-28100</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1590600</v>
+        <v>923800</v>
       </c>
       <c r="E33" s="3">
-        <v>937400</v>
+        <v>1505600</v>
       </c>
       <c r="F33" s="3">
-        <v>471900</v>
+        <v>887300</v>
       </c>
       <c r="G33" s="3">
-        <v>2405500</v>
+        <v>446700</v>
       </c>
       <c r="H33" s="3">
-        <v>806900</v>
+        <v>2277000</v>
       </c>
       <c r="I33" s="3">
-        <v>912300</v>
+        <v>763800</v>
       </c>
       <c r="J33" s="3">
+        <v>863600</v>
+      </c>
+      <c r="K33" s="3">
         <v>250400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>881000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>881700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1443500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>898400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1373600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>418700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>214300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1904300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>285900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1222100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>634000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1102000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1344600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1041900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>815200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>956700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>943800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>885600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>773300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>678600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>354800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>689800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1590600</v>
+        <v>923800</v>
       </c>
       <c r="E35" s="3">
-        <v>937400</v>
+        <v>1505600</v>
       </c>
       <c r="F35" s="3">
-        <v>471900</v>
+        <v>887300</v>
       </c>
       <c r="G35" s="3">
-        <v>2405500</v>
+        <v>446700</v>
       </c>
       <c r="H35" s="3">
-        <v>806900</v>
+        <v>2277000</v>
       </c>
       <c r="I35" s="3">
-        <v>912300</v>
+        <v>763800</v>
       </c>
       <c r="J35" s="3">
+        <v>863600</v>
+      </c>
+      <c r="K35" s="3">
         <v>250400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>881000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>881700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1443500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>898400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1373600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>418700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>214300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1904300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>285900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1222100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>634000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1102000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1344600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1041900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>815200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>956700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>943800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>885600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>773300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>678600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>354800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>689800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,189 +3524,193 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5825400</v>
+        <v>4500200</v>
       </c>
       <c r="E41" s="3">
-        <v>6105300</v>
+        <v>5514200</v>
       </c>
       <c r="F41" s="3">
-        <v>6237500</v>
+        <v>5779200</v>
       </c>
       <c r="G41" s="3">
-        <v>5616300</v>
+        <v>5904300</v>
       </c>
       <c r="H41" s="3">
-        <v>5659000</v>
+        <v>5316300</v>
       </c>
       <c r="I41" s="3">
-        <v>5836900</v>
+        <v>5356700</v>
       </c>
       <c r="J41" s="3">
+        <v>5525200</v>
+      </c>
+      <c r="K41" s="3">
         <v>7274400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6433000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6802700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6351800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8540600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7202600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6723400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5919500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>15789700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7156600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6326500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7735200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7635500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7761000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6690600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7669800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7402900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6309600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7334400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6944300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>7349700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6787700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6771500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>7553100</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1972900</v>
+        <v>2113600</v>
       </c>
       <c r="E42" s="3">
-        <v>2188200</v>
+        <v>1867500</v>
       </c>
       <c r="F42" s="3">
-        <v>2711200</v>
+        <v>2071300</v>
       </c>
       <c r="G42" s="3">
-        <v>2338200</v>
+        <v>2566400</v>
       </c>
       <c r="H42" s="3">
-        <v>1836300</v>
+        <v>2213300</v>
       </c>
       <c r="I42" s="3">
-        <v>2244400</v>
+        <v>1738300</v>
       </c>
       <c r="J42" s="3">
+        <v>2124500</v>
+      </c>
+      <c r="K42" s="3">
         <v>2780300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2498700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2058500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2439100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2416300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2326600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2238300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2240900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2179300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2466400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2925600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2532000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2600300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2731800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>3037900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2792200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>3453500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>3374800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2939900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2708500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>3501600</v>
-      </c>
-      <c r="AE42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF42" s="3" t="s">
         <v>8</v>
@@ -3628,673 +3718,697 @@
       <c r="AG42" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>18338200</v>
+        <v>19084600</v>
       </c>
       <c r="E43" s="3">
-        <v>20185900</v>
+        <v>17358700</v>
       </c>
       <c r="F43" s="3">
-        <v>18474700</v>
+        <v>19107700</v>
       </c>
       <c r="G43" s="3">
-        <v>19377400</v>
+        <v>17487900</v>
       </c>
       <c r="H43" s="3">
-        <v>17313800</v>
+        <v>18342400</v>
       </c>
       <c r="I43" s="3">
-        <v>18872700</v>
+        <v>16389000</v>
       </c>
       <c r="J43" s="3">
+        <v>17864700</v>
+      </c>
+      <c r="K43" s="3">
         <v>18629400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>19774900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>18424400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>18472800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>18322300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>19387400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>17315500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>17898000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>14873600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>19912400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>19995800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>19820500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>19347400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>23063400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>20887500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>20792200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>19477900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>22612800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>20017900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>21216900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>19871600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>21957800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>19728100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>25974400</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>10788200</v>
+        <v>9637900</v>
       </c>
       <c r="E44" s="3">
-        <v>12563200</v>
+        <v>10212000</v>
       </c>
       <c r="F44" s="3">
-        <v>12329500</v>
+        <v>11892200</v>
       </c>
       <c r="G44" s="3">
-        <v>11095300</v>
+        <v>11670900</v>
       </c>
       <c r="H44" s="3">
-        <v>11880600</v>
+        <v>10502700</v>
       </c>
       <c r="I44" s="3">
-        <v>13385200</v>
+        <v>11246000</v>
       </c>
       <c r="J44" s="3">
+        <v>12670200</v>
+      </c>
+      <c r="K44" s="3">
         <v>15703200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>13561700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13883600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>13376400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>13211400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>11722600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>12228700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>12212600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>12348200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>12412700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>14707900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>13615300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>13569800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>13038500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>14975900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>13820200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>13141900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>12432100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>14097600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>12782800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>12369500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>10873800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>12655400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>11737600</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2395700</v>
+        <v>2016000</v>
       </c>
       <c r="E45" s="3">
-        <v>2312500</v>
+        <v>2267700</v>
       </c>
       <c r="F45" s="3">
-        <v>2381700</v>
+        <v>2189000</v>
       </c>
       <c r="G45" s="3">
-        <v>1531100</v>
+        <v>2254400</v>
       </c>
       <c r="H45" s="3">
-        <v>10071200</v>
+        <v>1449300</v>
       </c>
       <c r="I45" s="3">
-        <v>2005500</v>
+        <v>9533300</v>
       </c>
       <c r="J45" s="3">
+        <v>1898400</v>
+      </c>
+      <c r="K45" s="3">
         <v>2040100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1551800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2556900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2070600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1818300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1498800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1681100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1832800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4113500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4018800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6546100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2042700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2117200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1799400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2361700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2166700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2156900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1842900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2258300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2187200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2212300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4753800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4708100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4654500</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>39320400</v>
+        <v>37352300</v>
       </c>
       <c r="E46" s="3">
-        <v>43355100</v>
+        <v>37220200</v>
       </c>
       <c r="F46" s="3">
-        <v>42134500</v>
+        <v>41039400</v>
       </c>
       <c r="G46" s="3">
-        <v>39958300</v>
+        <v>39884000</v>
       </c>
       <c r="H46" s="3">
-        <v>46760900</v>
+        <v>37824100</v>
       </c>
       <c r="I46" s="3">
-        <v>42344800</v>
+        <v>44263300</v>
       </c>
       <c r="J46" s="3">
+        <v>40083000</v>
+      </c>
+      <c r="K46" s="3">
         <v>46427400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>43820200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>43726000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>42710700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>44308900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>42138000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>40187000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>40103800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>49304300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>45967000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>50502000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>45745800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>45270100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>48394000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>47953500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>47241100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>45633100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>46572300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>46648100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>45839800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>45304800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>44373100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>43863100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>49919500</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>8575100</v>
+        <v>7251100</v>
       </c>
       <c r="E47" s="3">
-        <v>6991700</v>
+        <v>8117100</v>
       </c>
       <c r="F47" s="3">
-        <v>6992900</v>
+        <v>6618300</v>
       </c>
       <c r="G47" s="3">
-        <v>6575000</v>
+        <v>6619400</v>
       </c>
       <c r="H47" s="3">
-        <v>6477800</v>
+        <v>6223800</v>
       </c>
       <c r="I47" s="3">
-        <v>7525800</v>
+        <v>6131800</v>
       </c>
       <c r="J47" s="3">
+        <v>7123800</v>
+      </c>
+      <c r="K47" s="3">
         <v>6934300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6613500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6824000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7105800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7097900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7135600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6667500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7063000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7699800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8113000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>9074100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12086600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>11909900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12423900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12268900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12733300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12636400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>13196900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13425300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>13164700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>12783700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>12515200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>13097300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>16937400</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>7909900</v>
+        <v>7795400</v>
       </c>
       <c r="E48" s="3">
-        <v>11952000</v>
+        <v>7487400</v>
       </c>
       <c r="F48" s="3">
-        <v>11845600</v>
+        <v>11313700</v>
       </c>
       <c r="G48" s="3">
-        <v>11461200</v>
+        <v>11212900</v>
       </c>
       <c r="H48" s="3">
-        <v>11455600</v>
+        <v>10849000</v>
       </c>
       <c r="I48" s="3">
-        <v>14252900</v>
+        <v>10843800</v>
       </c>
       <c r="J48" s="3">
+        <v>13491700</v>
+      </c>
+      <c r="K48" s="3">
         <v>17274800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16459900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16629700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17237600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17652400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17079000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15682000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>16694300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>16517900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>19076400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20106600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19703700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19759100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>18803700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>18389900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20003800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19357100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19208400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19232200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>18881700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>18246800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>17725900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>17662900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>20069600</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>22753300</v>
+        <v>22651700</v>
       </c>
       <c r="E49" s="3">
-        <v>25244700</v>
+        <v>21538000</v>
       </c>
       <c r="F49" s="3">
-        <v>24659800</v>
+        <v>23896300</v>
       </c>
       <c r="G49" s="3">
-        <v>22983700</v>
+        <v>23342600</v>
       </c>
       <c r="H49" s="3">
-        <v>22535100</v>
+        <v>21756000</v>
       </c>
       <c r="I49" s="3">
-        <v>25170600</v>
+        <v>21331500</v>
       </c>
       <c r="J49" s="3">
+        <v>23826100</v>
+      </c>
+      <c r="K49" s="3">
         <v>25113500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22647900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>22308700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>23106900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15617200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15073600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14192100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>15141300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9038200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9829500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10478300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8381100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8770800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9225800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9348100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9968300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9621800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>9531500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>10139000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>10111900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>8483100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>8153300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>8193600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>8309100</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2814800</v>
+        <v>2921300</v>
       </c>
       <c r="E52" s="3">
-        <v>3279300</v>
+        <v>2664500</v>
       </c>
       <c r="F52" s="3">
-        <v>3034500</v>
+        <v>3104100</v>
       </c>
       <c r="G52" s="3">
-        <v>3281400</v>
+        <v>2872400</v>
       </c>
       <c r="H52" s="3">
-        <v>2284500</v>
+        <v>3106100</v>
       </c>
       <c r="I52" s="3">
-        <v>2486900</v>
+        <v>2162500</v>
       </c>
       <c r="J52" s="3">
+        <v>2354000</v>
+      </c>
+      <c r="K52" s="3">
         <v>2667900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2671500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2733700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2700300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2786600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2610500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3472000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3696300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4109000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4498100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3502200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3405900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3442200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3664200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3546200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3512500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3057200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2854500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2728600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2784700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2792500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2951400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2691400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>9247200</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>81373400</v>
+        <v>77971800</v>
       </c>
       <c r="E54" s="3">
-        <v>90822900</v>
+        <v>77027100</v>
       </c>
       <c r="F54" s="3">
-        <v>88667200</v>
+        <v>85971800</v>
       </c>
       <c r="G54" s="3">
-        <v>84259500</v>
+        <v>83931200</v>
       </c>
       <c r="H54" s="3">
-        <v>89514000</v>
+        <v>79759000</v>
       </c>
       <c r="I54" s="3">
-        <v>91780900</v>
+        <v>84732800</v>
       </c>
       <c r="J54" s="3">
+        <v>86878700</v>
+      </c>
+      <c r="K54" s="3">
         <v>98418000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>92213000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>92222000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>92861400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>87463100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>84036700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>80200700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>82698800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>86669200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>87484000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>93663200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>89323100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>89152000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>92511500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>91506600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>93459000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>90305500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>91363700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>92173200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>90782700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>87610900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>85718900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>85508400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>104482800</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,578 +4968,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>9047700</v>
+        <v>8930100</v>
       </c>
       <c r="E57" s="3">
-        <v>10623700</v>
+        <v>8564400</v>
       </c>
       <c r="F57" s="3">
-        <v>10579100</v>
+        <v>10056300</v>
       </c>
       <c r="G57" s="3">
-        <v>10436900</v>
+        <v>10014000</v>
       </c>
       <c r="H57" s="3">
-        <v>9966800</v>
+        <v>9879400</v>
       </c>
       <c r="I57" s="3">
-        <v>11492000</v>
+        <v>9434500</v>
       </c>
       <c r="J57" s="3">
+        <v>10878200</v>
+      </c>
+      <c r="K57" s="3">
         <v>12105000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11650800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10957900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10787600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11144000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10748100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9809900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9797100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9368400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11194600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>11828400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11275400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11927900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>13511800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>12785400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12738900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12718200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>13894300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>13397100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12889700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12346100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12437800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>11908500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11654900</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3952500</v>
+        <v>1437500</v>
       </c>
       <c r="E58" s="3">
-        <v>6975900</v>
+        <v>3741400</v>
       </c>
       <c r="F58" s="3">
-        <v>7322700</v>
+        <v>6603300</v>
       </c>
       <c r="G58" s="3">
-        <v>6197500</v>
+        <v>6931600</v>
       </c>
       <c r="H58" s="3">
-        <v>11779300</v>
+        <v>5866500</v>
       </c>
       <c r="I58" s="3">
-        <v>9112300</v>
+        <v>11150100</v>
       </c>
       <c r="J58" s="3">
+        <v>8625500</v>
+      </c>
+      <c r="K58" s="3">
         <v>12483000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10428400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13041400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12086700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6548900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4899400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>9077200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>12284200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>12318200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3652100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6529700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5029300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4536800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2847300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5429700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4508500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4229900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2157200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3742700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3865500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4202800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3429100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3937900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>12512300</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>19683100</v>
+        <v>20273000</v>
       </c>
       <c r="E59" s="3">
-        <v>19980600</v>
+        <v>18631800</v>
       </c>
       <c r="F59" s="3">
-        <v>18940700</v>
+        <v>18913400</v>
       </c>
       <c r="G59" s="3">
-        <v>18185700</v>
+        <v>17929000</v>
       </c>
       <c r="H59" s="3">
-        <v>19247000</v>
+        <v>17214300</v>
       </c>
       <c r="I59" s="3">
-        <v>18554100</v>
+        <v>18219000</v>
       </c>
       <c r="J59" s="3">
+        <v>17563000</v>
+      </c>
+      <c r="K59" s="3">
         <v>17017900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16791900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15810000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>16046600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>16697900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16944700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15956700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16120700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>17854300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>18042600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>19847800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>16505800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>16298200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>18290400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>17134300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>17568000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>16763300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>18258800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>17693700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>17628000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>16719600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>17137200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>16265100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>16240700</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>32683300</v>
+        <v>30640600</v>
       </c>
       <c r="E60" s="3">
-        <v>37580300</v>
+        <v>30937600</v>
       </c>
       <c r="F60" s="3">
-        <v>36842500</v>
+        <v>35573000</v>
       </c>
       <c r="G60" s="3">
-        <v>34820000</v>
+        <v>34874700</v>
       </c>
       <c r="H60" s="3">
-        <v>40993100</v>
+        <v>32960200</v>
       </c>
       <c r="I60" s="3">
-        <v>39158300</v>
+        <v>38803600</v>
       </c>
       <c r="J60" s="3">
+        <v>37066800</v>
+      </c>
+      <c r="K60" s="3">
         <v>41605900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>38871000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>39809300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>38920800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>34390800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>32592200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>34843800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>38202100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>39540800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>32889300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>38205800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>32810500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>32762900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>34649400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>35349400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>34815400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>33711400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>34310400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>34833500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>34383200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>33268500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>33004000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>32111400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>40407900</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7873300</v>
+        <v>6091000</v>
       </c>
       <c r="E61" s="3">
-        <v>9037300</v>
+        <v>7452800</v>
       </c>
       <c r="F61" s="3">
-        <v>8982300</v>
+        <v>8554600</v>
       </c>
       <c r="G61" s="3">
-        <v>8720500</v>
+        <v>8502500</v>
       </c>
       <c r="H61" s="3">
-        <v>8809600</v>
+        <v>8254700</v>
       </c>
       <c r="I61" s="3">
-        <v>9792000</v>
+        <v>8339100</v>
       </c>
       <c r="J61" s="3">
+        <v>9269000</v>
+      </c>
+      <c r="K61" s="3">
         <v>10837200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10333000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11118900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11804800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12061200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12097900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9983800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7275300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8505400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9431100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7705500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7720200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8081000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6808600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7076600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6652500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6755400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7337400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7529400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7629600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7261000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7007400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7631500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>19851800</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4263200</v>
+        <v>3855900</v>
       </c>
       <c r="E62" s="3">
-        <v>4939700</v>
+        <v>4035500</v>
       </c>
       <c r="F62" s="3">
-        <v>4838500</v>
+        <v>4675800</v>
       </c>
       <c r="G62" s="3">
-        <v>4757300</v>
+        <v>4580100</v>
       </c>
       <c r="H62" s="3">
-        <v>4861400</v>
+        <v>4503200</v>
       </c>
       <c r="I62" s="3">
-        <v>5633700</v>
+        <v>4601800</v>
       </c>
       <c r="J62" s="3">
+        <v>5332800</v>
+      </c>
+      <c r="K62" s="3">
         <v>7899900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7450000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7621300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7886600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7913300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7737800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8641200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9389500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7054800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7573600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8011800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7935100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7819600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8631100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8503900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8634300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8575800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8930400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>9587400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>9519400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>9427600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>9367200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9692000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9942400</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>45795300</v>
+        <v>41582200</v>
       </c>
       <c r="E66" s="3">
-        <v>54320300</v>
+        <v>43349200</v>
       </c>
       <c r="F66" s="3">
-        <v>53315100</v>
+        <v>51418900</v>
       </c>
       <c r="G66" s="3">
-        <v>50944700</v>
+        <v>50467400</v>
       </c>
       <c r="H66" s="3">
-        <v>59021100</v>
+        <v>48223600</v>
       </c>
       <c r="I66" s="3">
-        <v>59084600</v>
+        <v>55868600</v>
       </c>
       <c r="J66" s="3">
+        <v>55928700</v>
+      </c>
+      <c r="K66" s="3">
         <v>67291300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>63383200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>65084500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>65283900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>61047200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>59040900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>58736000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>59983500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>60767600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>59644500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>64242700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>58617400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>59031200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>61157900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>61843400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>61415400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>59788500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>61730400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>63059800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>62347900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>60372500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>59400900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>59920500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>81205500</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>25908800</v>
+        <v>26060600</v>
       </c>
       <c r="E72" s="3">
-        <v>25495600</v>
+        <v>24525000</v>
       </c>
       <c r="F72" s="3">
-        <v>24550300</v>
+        <v>24133800</v>
       </c>
       <c r="G72" s="3">
-        <v>24514600</v>
+        <v>23239000</v>
       </c>
       <c r="H72" s="3">
-        <v>21975700</v>
+        <v>23205200</v>
       </c>
       <c r="I72" s="3">
-        <v>22635100</v>
+        <v>20801900</v>
       </c>
       <c r="J72" s="3">
+        <v>21426100</v>
+      </c>
+      <c r="K72" s="3">
         <v>21664600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>21232900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20987100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>21520400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>20473000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>19218200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>18264800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>19425200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>21120100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>20229600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>20621300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>22424100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>21711000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>21983700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>20149100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>21201100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>19948300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>19032800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>18040300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>17443200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>16664700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>15909000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>15530900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>15048500</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>35578200</v>
+        <v>36389600</v>
       </c>
       <c r="E76" s="3">
-        <v>36502600</v>
+        <v>33677900</v>
       </c>
       <c r="F76" s="3">
-        <v>35352100</v>
+        <v>34552900</v>
       </c>
       <c r="G76" s="3">
-        <v>33314800</v>
+        <v>33463800</v>
       </c>
       <c r="H76" s="3">
-        <v>30492900</v>
+        <v>31535400</v>
       </c>
       <c r="I76" s="3">
-        <v>32696300</v>
+        <v>28864200</v>
       </c>
       <c r="J76" s="3">
+        <v>30949900</v>
+      </c>
+      <c r="K76" s="3">
         <v>31126700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>28829800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>27137600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>27577500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>26415900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>24995800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>21464600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>22715300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>25901600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>27839500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>29420500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>30705700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>30120900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>31353600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>29663100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>32043600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>30517000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>29633300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>29113400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>28434800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>27238300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>26318000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>25587900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>23277400</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1590600</v>
+        <v>923800</v>
       </c>
       <c r="E81" s="3">
-        <v>937400</v>
+        <v>1505600</v>
       </c>
       <c r="F81" s="3">
-        <v>471900</v>
+        <v>887300</v>
       </c>
       <c r="G81" s="3">
-        <v>2405500</v>
+        <v>446700</v>
       </c>
       <c r="H81" s="3">
-        <v>806900</v>
+        <v>2277000</v>
       </c>
       <c r="I81" s="3">
-        <v>912300</v>
+        <v>763800</v>
       </c>
       <c r="J81" s="3">
+        <v>863600</v>
+      </c>
+      <c r="K81" s="3">
         <v>250400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>881000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>881700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1443500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>898400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1373600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>418700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>214300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1904300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>285900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1222100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>634000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1102000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1344600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1041900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>815200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>956700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>943800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>885600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>773300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>678600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>354800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>689800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>697700</v>
+        <v>644400</v>
       </c>
       <c r="E83" s="3">
-        <v>846900</v>
+        <v>660400</v>
       </c>
       <c r="F83" s="3">
-        <v>817900</v>
+        <v>801600</v>
       </c>
       <c r="G83" s="3">
-        <v>811100</v>
+        <v>774300</v>
       </c>
       <c r="H83" s="3">
-        <v>832800</v>
+        <v>767700</v>
       </c>
       <c r="I83" s="3">
-        <v>947900</v>
+        <v>788300</v>
       </c>
       <c r="J83" s="3">
+        <v>897300</v>
+      </c>
+      <c r="K83" s="3">
         <v>955600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>945700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>926000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>952600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>962300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>996500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>918100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>992500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>839800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1027900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>989800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>959000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>947800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>934400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>863000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>828800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>819700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>836100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>833100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>836900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>788400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>836200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>793900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1019900</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1522800</v>
+        <v>2639700</v>
       </c>
       <c r="E89" s="3">
-        <v>1339700</v>
+        <v>1441500</v>
       </c>
       <c r="F89" s="3">
-        <v>796400</v>
+        <v>1268100</v>
       </c>
       <c r="G89" s="3">
-        <v>3012500</v>
+        <v>753900</v>
       </c>
       <c r="H89" s="3">
-        <v>987000</v>
+        <v>2851600</v>
       </c>
       <c r="I89" s="3">
-        <v>859300</v>
+        <v>934300</v>
       </c>
       <c r="J89" s="3">
+        <v>813400</v>
+      </c>
+      <c r="K89" s="3">
         <v>715500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3139300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>657400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>175900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1007500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2600100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1553300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>472800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1311900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2229600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>930700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1165500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>722400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3917700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-91000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>721300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1221300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2295800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1760400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1369900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1147500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2221100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>835800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1773600</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-110861000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-78532000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-106661000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-89091000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-105408000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-96150000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-108272000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100755000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-134149000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100626000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-107573000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-488900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-628300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-384800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-471300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-453200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-794100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-595900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-811800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-723700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-857900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-898800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-883000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-934700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-11900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1277100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-889100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2139000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-415900</v>
+        <v>258100</v>
       </c>
       <c r="E94" s="3">
-        <v>-474700</v>
+        <v>-393700</v>
       </c>
       <c r="F94" s="3">
-        <v>-268700</v>
+        <v>-449300</v>
       </c>
       <c r="G94" s="3">
-        <v>1997300</v>
+        <v>-254300</v>
       </c>
       <c r="H94" s="3">
-        <v>-491600</v>
+        <v>1890600</v>
       </c>
       <c r="I94" s="3">
-        <v>-2200</v>
+        <v>-465300</v>
       </c>
       <c r="J94" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-485400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-140400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-524200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6808900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-51800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>2178300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-455900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8267800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>3049100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-297800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2595800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-937000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-962900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>121300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-311700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-357900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-944800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1447200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-721200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1173700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-945800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1217900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>141000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1198700</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,103 +8351,107 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-500200</v>
+        <v>600</v>
       </c>
       <c r="E96" s="3">
-        <v>900</v>
+        <v>-473400</v>
       </c>
       <c r="F96" s="3">
-        <v>-474200</v>
+        <v>800</v>
       </c>
       <c r="G96" s="3">
+        <v>-448900</v>
+      </c>
+      <c r="H96" s="3">
+        <v>600</v>
+      </c>
+      <c r="I96" s="3">
+        <v>-423500</v>
+      </c>
+      <c r="J96" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K96" s="3">
+        <v>-424400</v>
+      </c>
+      <c r="L96" s="3">
+        <v>600</v>
+      </c>
+      <c r="M96" s="3">
+        <v>-399200</v>
+      </c>
+      <c r="N96" s="3">
+        <v>800</v>
+      </c>
+      <c r="O96" s="3">
+        <v>-391300</v>
+      </c>
+      <c r="P96" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>-355300</v>
+      </c>
+      <c r="R96" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S96" s="3">
+        <v>-412600</v>
+      </c>
+      <c r="T96" s="3">
+        <v>600</v>
+      </c>
+      <c r="U96" s="3">
+        <v>-397200</v>
+      </c>
+      <c r="V96" s="3">
+        <v>1500</v>
+      </c>
+      <c r="W96" s="3">
+        <v>-442700</v>
+      </c>
+      <c r="X96" s="3">
         <v>700</v>
       </c>
-      <c r="H96" s="3">
-        <v>-447400</v>
-      </c>
-      <c r="I96" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-424400</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="Y96" s="3">
+        <v>-365100</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>-351500</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>-305900</v>
+      </c>
+      <c r="AD96" s="3">
         <v>600</v>
       </c>
-      <c r="L96" s="3">
-        <v>-399200</v>
-      </c>
-      <c r="M96" s="3">
-        <v>800</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-391300</v>
-      </c>
-      <c r="O96" s="3">
-        <v>600</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-355300</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>1100</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-412600</v>
-      </c>
-      <c r="S96" s="3">
-        <v>600</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-397200</v>
-      </c>
-      <c r="U96" s="3">
-        <v>1500</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-442700</v>
-      </c>
-      <c r="W96" s="3">
-        <v>700</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-365100</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>700</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-351500</v>
-      </c>
-      <c r="AA96" s="3">
+      <c r="AE96" s="3">
+        <v>-305900</v>
+      </c>
+      <c r="AF96" s="3">
         <v>400</v>
       </c>
-      <c r="AB96" s="3">
-        <v>-305900</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>600</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-305900</v>
-      </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
+        <v>-257400</v>
+      </c>
+      <c r="AH96" s="3">
         <v>400</v>
       </c>
-      <c r="AF96" s="3">
-        <v>-257400</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1222800</v>
+        <v>-4141600</v>
       </c>
       <c r="E100" s="3">
-        <v>-1123300</v>
+        <v>-1157500</v>
       </c>
       <c r="F100" s="3">
-        <v>-186500</v>
+        <v>-1063300</v>
       </c>
       <c r="G100" s="3">
-        <v>-5945400</v>
+        <v>-176500</v>
       </c>
       <c r="H100" s="3">
-        <v>523100</v>
+        <v>-5627900</v>
       </c>
       <c r="I100" s="3">
-        <v>-2389200</v>
+        <v>495200</v>
       </c>
       <c r="J100" s="3">
+        <v>-2261600</v>
+      </c>
+      <c r="K100" s="3">
         <v>107900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3369100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>436900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>4584400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>78600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4395900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>9900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-723400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4492600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-740400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>152600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-25700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>668100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3116400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-529700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-258300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>797900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1618500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-748700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-709100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>170400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-864900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2288400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>989900</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-164000</v>
+        <v>229700</v>
       </c>
       <c r="E101" s="3">
-        <v>126200</v>
+        <v>-155200</v>
       </c>
       <c r="F101" s="3">
-        <v>279900</v>
+        <v>119400</v>
       </c>
       <c r="G101" s="3">
-        <v>86300</v>
+        <v>265000</v>
       </c>
       <c r="H101" s="3">
-        <v>-389800</v>
+        <v>81700</v>
       </c>
       <c r="I101" s="3">
-        <v>94600</v>
+        <v>-369000</v>
       </c>
       <c r="J101" s="3">
+        <v>89500</v>
+      </c>
+      <c r="K101" s="3">
         <v>406600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>228200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>180400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>22500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>39600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>316900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>46100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>18000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>7000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-152900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>171200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-128000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-189700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>27200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-170600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-254800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>99500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>107600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>59800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-122100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>530100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-69300</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-280000</v>
+        <v>-1014000</v>
       </c>
       <c r="E102" s="3">
-        <v>-132200</v>
+        <v>-265000</v>
       </c>
       <c r="F102" s="3">
-        <v>621200</v>
+        <v>-125100</v>
       </c>
       <c r="G102" s="3">
-        <v>-849300</v>
+        <v>588000</v>
       </c>
       <c r="H102" s="3">
-        <v>628700</v>
+        <v>-804000</v>
       </c>
       <c r="I102" s="3">
-        <v>-1437400</v>
+        <v>595100</v>
       </c>
       <c r="J102" s="3">
+        <v>-1360700</v>
+      </c>
+      <c r="K102" s="3">
         <v>744500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-141900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>750500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2026200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1073900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>699400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1153400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8500500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8860600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1038400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1341400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>74800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>237900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>949900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1103100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>104000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1058400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1024800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>390000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-405400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>431900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>16200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-781600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1495500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HTHIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HTHIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>HTHIY</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>16017400</v>
+        <v>15701100</v>
       </c>
       <c r="E8" s="3">
-        <v>14406600</v>
+        <v>17825000</v>
       </c>
       <c r="F8" s="3">
-        <v>16827800</v>
+        <v>16032400</v>
       </c>
       <c r="G8" s="3">
-        <v>14817500</v>
+        <v>18726800</v>
       </c>
       <c r="H8" s="3">
-        <v>17687600</v>
+        <v>16489700</v>
       </c>
       <c r="I8" s="3">
-        <v>17175100</v>
+        <v>19683700</v>
       </c>
       <c r="J8" s="3">
+        <v>19113300</v>
+      </c>
+      <c r="K8" s="3">
         <v>18163600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17320600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19375100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17271200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17774300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17400700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19498900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16264900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16871400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>13599200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>21347400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>19339200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>20114600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>18618500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>25924400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>21628300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>21607900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>19688000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>24359100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>20770000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>20681700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>18881600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>23443000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>19208300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>19720700</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>11428000</v>
+        <v>11155500</v>
       </c>
       <c r="E9" s="3">
-        <v>10366900</v>
+        <v>12717700</v>
       </c>
       <c r="F9" s="3">
-        <v>12648200</v>
+        <v>11536800</v>
       </c>
       <c r="G9" s="3">
-        <v>11152500</v>
+        <v>14075500</v>
       </c>
       <c r="H9" s="3">
-        <v>13194700</v>
+        <v>12411000</v>
       </c>
       <c r="I9" s="3">
-        <v>12902700</v>
+        <v>14683800</v>
       </c>
       <c r="J9" s="3">
+        <v>14358800</v>
+      </c>
+      <c r="K9" s="3">
         <v>13699200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13172300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14433800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12948800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13386900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13161400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>14759900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12099600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12635200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10060500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>15555900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14178700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14579000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>13633700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>19379600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>15751100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>15728800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>14420300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>17804700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>15290000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>15148400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>13830300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>17433900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>14170500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>14505800</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4589400</v>
+        <v>4545600</v>
       </c>
       <c r="E10" s="3">
-        <v>4039700</v>
+        <v>5107300</v>
       </c>
       <c r="F10" s="3">
-        <v>4179600</v>
+        <v>4495600</v>
       </c>
       <c r="G10" s="3">
-        <v>3665000</v>
+        <v>4651300</v>
       </c>
       <c r="H10" s="3">
-        <v>4492900</v>
+        <v>4078600</v>
       </c>
       <c r="I10" s="3">
-        <v>4272400</v>
+        <v>4999900</v>
       </c>
       <c r="J10" s="3">
+        <v>4754500</v>
+      </c>
+      <c r="K10" s="3">
         <v>4464400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4148300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4941300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4322400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4387400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4239200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4739000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4165300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4236200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3538700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5791400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5160500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5535500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4984800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>6544800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5877200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5879200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5267700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>6554300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5479900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5533300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5051300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>6009100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>5037800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>5214900</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1330,56 +1350,56 @@
         <v>8</v>
       </c>
       <c r="E14" s="3">
-        <v>-514800</v>
+        <v>252400</v>
       </c>
       <c r="F14" s="3">
-        <v>-48000</v>
+        <v>-572900</v>
       </c>
       <c r="G14" s="3">
-        <v>52400</v>
+        <v>-53500</v>
       </c>
       <c r="H14" s="3">
-        <v>-1048500</v>
+        <v>58300</v>
       </c>
       <c r="I14" s="3">
-        <v>43100</v>
+        <v>-1166800</v>
       </c>
       <c r="J14" s="3">
+        <v>47900</v>
+      </c>
+      <c r="K14" s="3">
         <v>-13000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>28300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>176000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>55000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-428000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-245700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-853500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>256500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>325700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-2389500</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14549300</v>
+        <v>14298000</v>
       </c>
       <c r="E17" s="3">
-        <v>12614400</v>
+        <v>16443600</v>
       </c>
       <c r="F17" s="3">
-        <v>15536000</v>
+        <v>14038000</v>
       </c>
       <c r="G17" s="3">
-        <v>14037000</v>
+        <v>17289300</v>
       </c>
       <c r="H17" s="3">
-        <v>15231400</v>
+        <v>15621100</v>
       </c>
       <c r="I17" s="3">
-        <v>15923800</v>
+        <v>16950300</v>
       </c>
       <c r="J17" s="3">
+        <v>17720900</v>
+      </c>
+      <c r="K17" s="3">
         <v>16855000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16529600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17866000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16128100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16051500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16195900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17381500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15523600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>16243500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10711800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>19442200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>17987000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>18526400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>17479100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>23806000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>19835200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>19783000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>18341400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>22188700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>19221300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>19132200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>17689700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>21707800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>18186600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>18780900</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1468100</v>
+        <v>1403100</v>
       </c>
       <c r="E18" s="3">
-        <v>1792200</v>
+        <v>1381400</v>
       </c>
       <c r="F18" s="3">
-        <v>1291700</v>
+        <v>1994400</v>
       </c>
       <c r="G18" s="3">
-        <v>780500</v>
+        <v>1437500</v>
       </c>
       <c r="H18" s="3">
-        <v>2456200</v>
+        <v>868500</v>
       </c>
       <c r="I18" s="3">
-        <v>1251200</v>
+        <v>2733400</v>
       </c>
       <c r="J18" s="3">
+        <v>1392400</v>
+      </c>
+      <c r="K18" s="3">
         <v>1308600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>791000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1509100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1143100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1722800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1204700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2117400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>741300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>628000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2887400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1905200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1352200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1588200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1139400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2118400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1793100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1824900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1346700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2170300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1548600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1549500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1191800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1735100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1021800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>939800</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,498 +1815,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-194000</v>
+        <v>525100</v>
       </c>
       <c r="E20" s="3">
-        <v>360400</v>
+        <v>36500</v>
       </c>
       <c r="F20" s="3">
-        <v>153400</v>
+        <v>401100</v>
       </c>
       <c r="G20" s="3">
-        <v>68800</v>
+        <v>170700</v>
       </c>
       <c r="H20" s="3">
-        <v>-37400</v>
+        <v>76500</v>
       </c>
       <c r="I20" s="3">
-        <v>-48200</v>
+        <v>-41600</v>
       </c>
       <c r="J20" s="3">
+        <v>-53700</v>
+      </c>
+      <c r="K20" s="3">
         <v>80400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-212100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>175400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>91000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>150500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>69100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>373000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>149700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-235800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>47600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-725600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3452500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-545700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>577900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-53600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2174600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-175700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>335400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-583700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>82700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-132600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>132400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-702400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>286900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1918600</v>
+        <v>2674500</v>
       </c>
       <c r="E21" s="3">
-        <v>2813000</v>
+        <v>2135100</v>
       </c>
       <c r="F21" s="3">
-        <v>2246800</v>
+        <v>3130500</v>
       </c>
       <c r="G21" s="3">
-        <v>1623500</v>
+        <v>2500300</v>
       </c>
       <c r="H21" s="3">
-        <v>3186600</v>
+        <v>1806700</v>
       </c>
       <c r="I21" s="3">
-        <v>1991300</v>
+        <v>3546200</v>
       </c>
       <c r="J21" s="3">
+        <v>2216000</v>
+      </c>
+      <c r="K21" s="3">
         <v>2286300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1534400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2630100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2160100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2825900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2236100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3486900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1809100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1384600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3774700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2207500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1110500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2001500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2665100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2999300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>481600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2478000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2501800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2422700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2464400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2253700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2112600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1868900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2102600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1987900</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>102200</v>
+        <v>136300</v>
       </c>
       <c r="E22" s="3">
-        <v>110700</v>
+        <v>113700</v>
       </c>
       <c r="F22" s="3">
-        <v>127200</v>
+        <v>123100</v>
       </c>
       <c r="G22" s="3">
-        <v>112400</v>
+        <v>141600</v>
       </c>
       <c r="H22" s="3">
-        <v>101900</v>
+        <v>125100</v>
       </c>
       <c r="I22" s="3">
-        <v>88600</v>
+        <v>113400</v>
       </c>
       <c r="J22" s="3">
+        <v>98600</v>
+      </c>
+      <c r="K22" s="3">
         <v>77700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>62500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>50500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>44600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>47300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>47400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>40900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>50200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>45100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>37200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>50600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>57400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>58200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>51300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>49200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>54300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>47100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>41700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>45400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>48500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>47200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>44600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>38100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>42000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>41800</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1172000</v>
+        <v>1791900</v>
       </c>
       <c r="E23" s="3">
-        <v>2041900</v>
+        <v>1304200</v>
       </c>
       <c r="F23" s="3">
-        <v>1317900</v>
+        <v>2272400</v>
       </c>
       <c r="G23" s="3">
-        <v>736800</v>
+        <v>1466700</v>
       </c>
       <c r="H23" s="3">
-        <v>2316900</v>
+        <v>819900</v>
       </c>
       <c r="I23" s="3">
-        <v>1114400</v>
+        <v>2578400</v>
       </c>
       <c r="J23" s="3">
+        <v>1240200</v>
+      </c>
+      <c r="K23" s="3">
         <v>1311300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>516300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1634000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1189500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1825900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1226400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2449500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>840800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>347000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2897700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1129000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2157700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>984300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1665900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2015600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-435700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1602100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1640400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1541300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1582800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1369600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1279600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>994600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1266600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>926100</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>213400</v>
+        <v>465900</v>
       </c>
       <c r="E24" s="3">
-        <v>484100</v>
+        <v>237500</v>
       </c>
       <c r="F24" s="3">
-        <v>356700</v>
+        <v>538800</v>
       </c>
       <c r="G24" s="3">
-        <v>215700</v>
+        <v>396900</v>
       </c>
       <c r="H24" s="3">
-        <v>-43800</v>
+        <v>240100</v>
       </c>
       <c r="I24" s="3">
-        <v>265800</v>
+        <v>-48700</v>
       </c>
       <c r="J24" s="3">
+        <v>295800</v>
+      </c>
+      <c r="K24" s="3">
         <v>330100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>199200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>580700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>174000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>185900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>219800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1000000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>347100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>186800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>962900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>762200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1147100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>454200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>377600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>469000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>422800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>407300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>444600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>137800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>394200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>340500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>318200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>339400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>295300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>179000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>958600</v>
+        <v>1326000</v>
       </c>
       <c r="E26" s="3">
-        <v>1557800</v>
+        <v>1066700</v>
       </c>
       <c r="F26" s="3">
-        <v>961200</v>
+        <v>1733600</v>
       </c>
       <c r="G26" s="3">
-        <v>521100</v>
+        <v>1069700</v>
       </c>
       <c r="H26" s="3">
-        <v>2360700</v>
+        <v>579900</v>
       </c>
       <c r="I26" s="3">
-        <v>848600</v>
+        <v>2627100</v>
       </c>
       <c r="J26" s="3">
+        <v>944400</v>
+      </c>
+      <c r="K26" s="3">
         <v>981200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>317100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1053300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1015600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1640000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1006600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1449500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>493700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>160200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1934800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>366800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1010700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>530100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1288300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1546600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-858600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1194900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1195800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1403500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1188600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1029200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>961500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>655200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>971300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>747200</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>923800</v>
+        <v>1244800</v>
       </c>
       <c r="E27" s="3">
-        <v>1505600</v>
+        <v>1028100</v>
       </c>
       <c r="F27" s="3">
-        <v>887300</v>
+        <v>1675500</v>
       </c>
       <c r="G27" s="3">
-        <v>446700</v>
+        <v>987500</v>
       </c>
       <c r="H27" s="3">
-        <v>2277000</v>
+        <v>497100</v>
       </c>
       <c r="I27" s="3">
-        <v>763800</v>
+        <v>2533900</v>
       </c>
       <c r="J27" s="3">
+        <v>850000</v>
+      </c>
+      <c r="K27" s="3">
         <v>863600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>250400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>881000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>881700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1443500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>898400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1373600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>418700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>217000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1907200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>291100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1218500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>637600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1105700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1390100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1038100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>907000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>903300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1089500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>873200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>784200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>679200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>399800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>697700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>509700</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2712,58 +2773,61 @@
         <v>0</v>
       </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>-2700</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-2900</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-5200</v>
-      </c>
-      <c r="U29" s="3">
-        <v>-3600</v>
       </c>
       <c r="V29" s="3">
         <v>-3600</v>
       </c>
       <c r="W29" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="X29" s="3">
         <v>-3700</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-45500</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-91800</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>53400</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-145700</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>12400</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-10900</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-600</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-45100</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-7900</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>194000</v>
+        <v>-525100</v>
       </c>
       <c r="E32" s="3">
-        <v>-360400</v>
+        <v>-36500</v>
       </c>
       <c r="F32" s="3">
-        <v>-153400</v>
+        <v>-401100</v>
       </c>
       <c r="G32" s="3">
-        <v>-68800</v>
+        <v>-170700</v>
       </c>
       <c r="H32" s="3">
-        <v>37400</v>
+        <v>-76500</v>
       </c>
       <c r="I32" s="3">
-        <v>48200</v>
+        <v>41600</v>
       </c>
       <c r="J32" s="3">
+        <v>53700</v>
+      </c>
+      <c r="K32" s="3">
         <v>-80400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>212100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-175400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-91000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-150500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-69100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-373000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-149700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>235800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-47600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>725600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3452500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>545700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-577900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>53600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2174600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>175700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-335400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>583700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-82700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>132600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-132400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>702400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-286900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-28100</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>923800</v>
+        <v>1244800</v>
       </c>
       <c r="E33" s="3">
-        <v>1505600</v>
+        <v>1028100</v>
       </c>
       <c r="F33" s="3">
-        <v>887300</v>
+        <v>1675500</v>
       </c>
       <c r="G33" s="3">
-        <v>446700</v>
+        <v>987500</v>
       </c>
       <c r="H33" s="3">
-        <v>2277000</v>
+        <v>497100</v>
       </c>
       <c r="I33" s="3">
-        <v>763800</v>
+        <v>2533900</v>
       </c>
       <c r="J33" s="3">
+        <v>850000</v>
+      </c>
+      <c r="K33" s="3">
         <v>863600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>250400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>881000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>881700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1443500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>898400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1373600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>418700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>214300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1904300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>285900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1222100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>634000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1102000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1344600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1041900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>815200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>956700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>943800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>885600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>773300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>678600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>354800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>689800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>923800</v>
+        <v>1244800</v>
       </c>
       <c r="E35" s="3">
-        <v>1505600</v>
+        <v>1028100</v>
       </c>
       <c r="F35" s="3">
-        <v>887300</v>
+        <v>1675500</v>
       </c>
       <c r="G35" s="3">
-        <v>446700</v>
+        <v>987500</v>
       </c>
       <c r="H35" s="3">
-        <v>2277000</v>
+        <v>497100</v>
       </c>
       <c r="I35" s="3">
-        <v>763800</v>
+        <v>2533900</v>
       </c>
       <c r="J35" s="3">
+        <v>850000</v>
+      </c>
+      <c r="K35" s="3">
         <v>863600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>250400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>881000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>881700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1443500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>898400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1373600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>418700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>214300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1904300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>285900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1222100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>634000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1102000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1344600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1041900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>815200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>956700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>943800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>885600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>773300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>678600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>354800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>689800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,195 +3611,199 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4500200</v>
+        <v>6001100</v>
       </c>
       <c r="E41" s="3">
-        <v>5514200</v>
+        <v>5008100</v>
       </c>
       <c r="F41" s="3">
-        <v>5779200</v>
+        <v>6136500</v>
       </c>
       <c r="G41" s="3">
-        <v>5904300</v>
+        <v>6431400</v>
       </c>
       <c r="H41" s="3">
-        <v>5316300</v>
+        <v>6570700</v>
       </c>
       <c r="I41" s="3">
-        <v>5356700</v>
+        <v>5916300</v>
       </c>
       <c r="J41" s="3">
+        <v>5961200</v>
+      </c>
+      <c r="K41" s="3">
         <v>5525200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7274400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6433000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6802700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6351800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8540600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7202600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6723400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5919500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>15789700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7156600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6326500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7735200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7635500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7761000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6690600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7669800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7402900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6309600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>7334400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6944300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>7349700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6787700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6771500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>7553100</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2113600</v>
+        <v>2332100</v>
       </c>
       <c r="E42" s="3">
-        <v>1867500</v>
+        <v>2352100</v>
       </c>
       <c r="F42" s="3">
-        <v>2071300</v>
+        <v>2078200</v>
       </c>
       <c r="G42" s="3">
-        <v>2566400</v>
+        <v>2305000</v>
       </c>
       <c r="H42" s="3">
-        <v>2213300</v>
+        <v>2856000</v>
       </c>
       <c r="I42" s="3">
-        <v>1738300</v>
+        <v>2463100</v>
       </c>
       <c r="J42" s="3">
+        <v>1934400</v>
+      </c>
+      <c r="K42" s="3">
         <v>2124500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2780300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2498700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2058500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2439100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2416300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2326600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2238300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2240900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2179300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2466400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2925600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2532000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2600300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2731800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3037900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2792200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>3453500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>3374800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2939900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2708500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>3501600</v>
-      </c>
-      <c r="AF42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG42" s="3" t="s">
         <v>8</v>
@@ -3721,694 +3811,718 @@
       <c r="AH42" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>19084600</v>
+        <v>22414800</v>
       </c>
       <c r="E43" s="3">
-        <v>17358700</v>
+        <v>21238300</v>
       </c>
       <c r="F43" s="3">
-        <v>19107700</v>
+        <v>19317700</v>
       </c>
       <c r="G43" s="3">
-        <v>17487900</v>
+        <v>21264000</v>
       </c>
       <c r="H43" s="3">
-        <v>18342400</v>
+        <v>19461400</v>
       </c>
       <c r="I43" s="3">
-        <v>16389000</v>
+        <v>20412400</v>
       </c>
       <c r="J43" s="3">
+        <v>18238600</v>
+      </c>
+      <c r="K43" s="3">
         <v>17864700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>18629400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>19774900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>18424400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>18472800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>18322300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>19387400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>17315500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>17898000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>14873600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>19912400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>19995800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>19820500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>19347400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>23063400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>20887500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>20792200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>19477900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>22612800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>20017900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>21216900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>19871600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>21957800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>19728100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>25974400</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>9637900</v>
+        <v>12149900</v>
       </c>
       <c r="E44" s="3">
-        <v>10212000</v>
+        <v>10725600</v>
       </c>
       <c r="F44" s="3">
-        <v>11892200</v>
+        <v>11364500</v>
       </c>
       <c r="G44" s="3">
-        <v>11670900</v>
+        <v>13234200</v>
       </c>
       <c r="H44" s="3">
-        <v>10502700</v>
+        <v>12988000</v>
       </c>
       <c r="I44" s="3">
-        <v>11246000</v>
+        <v>11687900</v>
       </c>
       <c r="J44" s="3">
+        <v>12515200</v>
+      </c>
+      <c r="K44" s="3">
         <v>12670200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>15703200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13561700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>13883600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>13376400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>13211400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>11722600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>12228700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>12212600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>12348200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>12412700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>14707900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>13615300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>13569800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>13038500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>14975900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>13820200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>13141900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>12432100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>14097600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>12782800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>12369500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>10873800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>12655400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>11737600</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2016000</v>
+        <v>2969800</v>
       </c>
       <c r="E45" s="3">
-        <v>2267700</v>
+        <v>2243500</v>
       </c>
       <c r="F45" s="3">
-        <v>2189000</v>
+        <v>2523600</v>
       </c>
       <c r="G45" s="3">
-        <v>2254400</v>
+        <v>2436000</v>
       </c>
       <c r="H45" s="3">
-        <v>1449300</v>
+        <v>2508900</v>
       </c>
       <c r="I45" s="3">
-        <v>9533300</v>
+        <v>1612800</v>
       </c>
       <c r="J45" s="3">
+        <v>10609100</v>
+      </c>
+      <c r="K45" s="3">
         <v>1898400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2040100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1551800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2556900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2070600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1818300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1498800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1681100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1832800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4113500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4018800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6546100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2042700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2117200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1799400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2361700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2166700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2156900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1842900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2258300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2187200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2212300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4753800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4708100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4654500</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>37352300</v>
+        <v>45867700</v>
       </c>
       <c r="E46" s="3">
-        <v>37220200</v>
+        <v>41567600</v>
       </c>
       <c r="F46" s="3">
-        <v>41039400</v>
+        <v>41420600</v>
       </c>
       <c r="G46" s="3">
-        <v>39884000</v>
+        <v>45670800</v>
       </c>
       <c r="H46" s="3">
-        <v>37824100</v>
+        <v>44385000</v>
       </c>
       <c r="I46" s="3">
-        <v>44263300</v>
+        <v>42092600</v>
       </c>
       <c r="J46" s="3">
+        <v>49258500</v>
+      </c>
+      <c r="K46" s="3">
         <v>40083000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>46427400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>43820200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>43726000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>42710700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>44308900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>42138000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>40187000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>40103800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>49304300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>45967000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>50502000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>45745800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>45270100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>48394000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>47953500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>47241100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>45633100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>46572300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>46648100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>45839800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>45304800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>44373100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>43863100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>49919500</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>7251100</v>
+        <v>8479100</v>
       </c>
       <c r="E47" s="3">
-        <v>8117100</v>
+        <v>8069400</v>
       </c>
       <c r="F47" s="3">
-        <v>6618300</v>
+        <v>9033100</v>
       </c>
       <c r="G47" s="3">
-        <v>6619400</v>
+        <v>7365200</v>
       </c>
       <c r="H47" s="3">
-        <v>6223800</v>
+        <v>7366400</v>
       </c>
       <c r="I47" s="3">
-        <v>6131800</v>
+        <v>6926200</v>
       </c>
       <c r="J47" s="3">
+        <v>6823800</v>
+      </c>
+      <c r="K47" s="3">
         <v>7123800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6934300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6613500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6824000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7105800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7097900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7135600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6667500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7063000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7699800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8113000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>9074100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12086600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>11909900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12423900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12268900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12733300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12636400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13196900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>13425300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>13164700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>12783700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>12515200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>13097300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>16937400</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>7795400</v>
+        <v>9096000</v>
       </c>
       <c r="E48" s="3">
-        <v>7487400</v>
+        <v>8675100</v>
       </c>
       <c r="F48" s="3">
-        <v>11313700</v>
+        <v>8332400</v>
       </c>
       <c r="G48" s="3">
-        <v>11212900</v>
+        <v>12590400</v>
       </c>
       <c r="H48" s="3">
-        <v>10849000</v>
+        <v>12478300</v>
       </c>
       <c r="I48" s="3">
-        <v>10843800</v>
+        <v>12073300</v>
       </c>
       <c r="J48" s="3">
+        <v>12067500</v>
+      </c>
+      <c r="K48" s="3">
         <v>13491700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>17274800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16459900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16629700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17237600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17652400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17079000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15682000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>16694300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>16517900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19076400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20106600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19703700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19759100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>18803700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>18389900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20003800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19357100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19208400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19232200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>18881700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>18246800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>17725900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>17662900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>20069600</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>22651700</v>
+        <v>28465900</v>
       </c>
       <c r="E49" s="3">
-        <v>21538000</v>
+        <v>25208000</v>
       </c>
       <c r="F49" s="3">
-        <v>23896300</v>
+        <v>23968600</v>
       </c>
       <c r="G49" s="3">
-        <v>23342600</v>
+        <v>26593100</v>
       </c>
       <c r="H49" s="3">
-        <v>21756000</v>
+        <v>25976900</v>
       </c>
       <c r="I49" s="3">
-        <v>21331500</v>
+        <v>24211300</v>
       </c>
       <c r="J49" s="3">
+        <v>23738800</v>
+      </c>
+      <c r="K49" s="3">
         <v>23826100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>25113500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>22647900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>22308700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>23106900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15617200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15073600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14192100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>15141300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9038200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9829500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10478300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8381100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8770800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9225800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9348100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9968300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>9621800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9531500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>10139000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>10111900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>8483100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>8153300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>8193600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>8309100</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2921300</v>
+        <v>3263900</v>
       </c>
       <c r="E52" s="3">
-        <v>2664500</v>
+        <v>3251000</v>
       </c>
       <c r="F52" s="3">
-        <v>3104100</v>
+        <v>2965200</v>
       </c>
       <c r="G52" s="3">
-        <v>2872400</v>
+        <v>3454400</v>
       </c>
       <c r="H52" s="3">
-        <v>3106100</v>
+        <v>3196600</v>
       </c>
       <c r="I52" s="3">
-        <v>2162500</v>
+        <v>3456700</v>
       </c>
       <c r="J52" s="3">
+        <v>2406600</v>
+      </c>
+      <c r="K52" s="3">
         <v>2354000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2667900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2671500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2733700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2700300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2786600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2610500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3472000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3696300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4109000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4498100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3502200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3405900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3442200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3664200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3546200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3512500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3057200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2854500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2728600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2784700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2792500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2951400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2691400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>9247200</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>77971800</v>
+        <v>95172600</v>
       </c>
       <c r="E54" s="3">
-        <v>77027100</v>
+        <v>86771100</v>
       </c>
       <c r="F54" s="3">
-        <v>85971800</v>
+        <v>85719800</v>
       </c>
       <c r="G54" s="3">
-        <v>83931200</v>
+        <v>95673900</v>
       </c>
       <c r="H54" s="3">
-        <v>79759000</v>
+        <v>93403100</v>
       </c>
       <c r="I54" s="3">
-        <v>84732800</v>
+        <v>88760000</v>
       </c>
       <c r="J54" s="3">
+        <v>94295100</v>
+      </c>
+      <c r="K54" s="3">
         <v>86878700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>98418000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>92213000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>92222000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>92861400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>87463100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>84036700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>80200700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>82698800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>86669200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>87484000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>93663200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>89323100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>89152000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>92511500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>91506600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>93459000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>90305500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>91363700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>92173200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>90782700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>87610900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>85718900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>85508400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>104482800</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,596 +5099,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>8930100</v>
+        <v>10773000</v>
       </c>
       <c r="E57" s="3">
-        <v>8564400</v>
+        <v>9937900</v>
       </c>
       <c r="F57" s="3">
-        <v>10056300</v>
+        <v>9531000</v>
       </c>
       <c r="G57" s="3">
-        <v>10014000</v>
+        <v>11191200</v>
       </c>
       <c r="H57" s="3">
-        <v>9879400</v>
+        <v>11144100</v>
       </c>
       <c r="I57" s="3">
-        <v>9434500</v>
+        <v>10994300</v>
       </c>
       <c r="J57" s="3">
+        <v>10499200</v>
+      </c>
+      <c r="K57" s="3">
         <v>10878200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12105000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11650800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10957900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10787600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11144000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10748100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9809900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9797100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9368400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>11194600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11828400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11275400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11927900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>13511800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12785400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12738900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12718200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>13894300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>13397100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12889700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12346100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>12437800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11908500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>11654900</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1437500</v>
+        <v>4394000</v>
       </c>
       <c r="E58" s="3">
-        <v>3741400</v>
+        <v>1599700</v>
       </c>
       <c r="F58" s="3">
-        <v>6603300</v>
+        <v>4163600</v>
       </c>
       <c r="G58" s="3">
-        <v>6931600</v>
+        <v>7348500</v>
       </c>
       <c r="H58" s="3">
-        <v>5866500</v>
+        <v>7713900</v>
       </c>
       <c r="I58" s="3">
-        <v>11150100</v>
+        <v>6528500</v>
       </c>
       <c r="J58" s="3">
+        <v>12408500</v>
+      </c>
+      <c r="K58" s="3">
         <v>8625500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12483000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10428400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>13041400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12086700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6548900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4899400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>9077200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>12284200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>12318200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3652100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6529700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5029300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4536800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2847300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5429700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4508500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4229900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2157200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3742700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3865500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4202800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3429100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3937900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>12512300</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>20273000</v>
+        <v>24808600</v>
       </c>
       <c r="E59" s="3">
-        <v>18631800</v>
+        <v>22560900</v>
       </c>
       <c r="F59" s="3">
-        <v>18913400</v>
+        <v>20734400</v>
       </c>
       <c r="G59" s="3">
-        <v>17929000</v>
+        <v>21047800</v>
       </c>
       <c r="H59" s="3">
-        <v>17214300</v>
+        <v>19952400</v>
       </c>
       <c r="I59" s="3">
-        <v>18219000</v>
+        <v>19157000</v>
       </c>
       <c r="J59" s="3">
+        <v>20275000</v>
+      </c>
+      <c r="K59" s="3">
         <v>17563000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17017900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16791900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15810000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>16046600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16697900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16944700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15956700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16120700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>17854300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>18042600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>19847800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>16505800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>16298200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>18290400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>17134300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>17568000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>16763300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>18258800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>17693700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>17628000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>16719600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>17137200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>16265100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>16240700</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>30640600</v>
+        <v>39975600</v>
       </c>
       <c r="E60" s="3">
-        <v>30937600</v>
+        <v>34098500</v>
       </c>
       <c r="F60" s="3">
-        <v>35573000</v>
+        <v>34429000</v>
       </c>
       <c r="G60" s="3">
-        <v>34874700</v>
+        <v>39587500</v>
       </c>
       <c r="H60" s="3">
-        <v>32960200</v>
+        <v>38810400</v>
       </c>
       <c r="I60" s="3">
-        <v>38803600</v>
+        <v>36679900</v>
       </c>
       <c r="J60" s="3">
+        <v>43182600</v>
+      </c>
+      <c r="K60" s="3">
         <v>37066800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>41605900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>38871000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>39809300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>38920800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>34390800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>32592200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>34843800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>38202100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>39540800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>32889300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>38205800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>32810500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>32762900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>34649400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>35349400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>34815400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>33711400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>34310400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>34833500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>34383200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>33268500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>33004000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>32111400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>40407900</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6091000</v>
+        <v>7077600</v>
       </c>
       <c r="E61" s="3">
-        <v>7452800</v>
+        <v>6778400</v>
       </c>
       <c r="F61" s="3">
-        <v>8554600</v>
+        <v>8293800</v>
       </c>
       <c r="G61" s="3">
-        <v>8502500</v>
+        <v>9520000</v>
       </c>
       <c r="H61" s="3">
-        <v>8254700</v>
+        <v>9462100</v>
       </c>
       <c r="I61" s="3">
-        <v>8339100</v>
+        <v>9186200</v>
       </c>
       <c r="J61" s="3">
+        <v>9280200</v>
+      </c>
+      <c r="K61" s="3">
         <v>9269000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10837200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10333000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11118900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11804800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12061200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12097900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9983800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7275300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8505400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9431100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7705500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7720200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8081000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6808600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7076600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6652500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6755400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7337400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7529400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7629600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7261000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7007400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7631500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>19851800</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3855900</v>
+        <v>4521500</v>
       </c>
       <c r="E62" s="3">
-        <v>4035500</v>
+        <v>4291000</v>
       </c>
       <c r="F62" s="3">
-        <v>4675800</v>
+        <v>4490900</v>
       </c>
       <c r="G62" s="3">
-        <v>4580100</v>
+        <v>5203500</v>
       </c>
       <c r="H62" s="3">
-        <v>4503200</v>
+        <v>5096900</v>
       </c>
       <c r="I62" s="3">
-        <v>4601800</v>
+        <v>5011400</v>
       </c>
       <c r="J62" s="3">
+        <v>5121100</v>
+      </c>
+      <c r="K62" s="3">
         <v>5332800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7899900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7450000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7621300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7886600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7913300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7737800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8641200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9389500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7054800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7573600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8011800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7935100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7819600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8631100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8503900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8634300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8575800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8930400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>9587400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>9519400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>9427600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9367200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9692000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9942400</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>41582200</v>
+        <v>52629000</v>
       </c>
       <c r="E66" s="3">
-        <v>43349200</v>
+        <v>46274800</v>
       </c>
       <c r="F66" s="3">
-        <v>51418900</v>
+        <v>48241300</v>
       </c>
       <c r="G66" s="3">
-        <v>50467400</v>
+        <v>57221700</v>
       </c>
       <c r="H66" s="3">
-        <v>48223600</v>
+        <v>56162800</v>
       </c>
       <c r="I66" s="3">
-        <v>55868600</v>
+        <v>53665800</v>
       </c>
       <c r="J66" s="3">
+        <v>62173500</v>
+      </c>
+      <c r="K66" s="3">
         <v>55928700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>67291300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>63383200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>65084500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>65283900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>61047200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>59040900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>58736000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>59983500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>60767600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>59644500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>64242700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>58617400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>59031200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>61157900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>61843400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>61415400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>59788500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>61730400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>63059800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>62347900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>60372500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>59400900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>59920500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>81205500</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>26060600</v>
+        <v>29575200</v>
       </c>
       <c r="E72" s="3">
-        <v>24525000</v>
+        <v>29001600</v>
       </c>
       <c r="F72" s="3">
-        <v>24133800</v>
+        <v>27292700</v>
       </c>
       <c r="G72" s="3">
-        <v>23239000</v>
+        <v>26857400</v>
       </c>
       <c r="H72" s="3">
-        <v>23205200</v>
+        <v>25861600</v>
       </c>
       <c r="I72" s="3">
-        <v>20801900</v>
+        <v>25824000</v>
       </c>
       <c r="J72" s="3">
+        <v>23149500</v>
+      </c>
+      <c r="K72" s="3">
         <v>21426100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>21664600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>21232900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20987100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>21520400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>20473000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>19218200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18264800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>19425200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>21120100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>20229600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>20621300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>22424100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>21711000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>21983700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>20149100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>21201100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>19948300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>19032800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>18040300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>17443200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>16664700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>15909000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>15530900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>15048500</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>36389600</v>
+        <v>42543600</v>
       </c>
       <c r="E76" s="3">
-        <v>33677900</v>
+        <v>40496300</v>
       </c>
       <c r="F76" s="3">
-        <v>34552900</v>
+        <v>37478500</v>
       </c>
       <c r="G76" s="3">
-        <v>33463800</v>
+        <v>38452300</v>
       </c>
       <c r="H76" s="3">
-        <v>31535400</v>
+        <v>37240300</v>
       </c>
       <c r="I76" s="3">
-        <v>28864200</v>
+        <v>35094300</v>
       </c>
       <c r="J76" s="3">
+        <v>32121600</v>
+      </c>
+      <c r="K76" s="3">
         <v>30949900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>31126700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>28829800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>27137600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>27577500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>26415900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>24995800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>21464600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>22715300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>25901600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>27839500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>29420500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>30705700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>30120900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>31353600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>29663100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>32043600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>30517000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>29633300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>29113400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>28434800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>27238300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>26318000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>25587900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>23277400</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>923800</v>
+        <v>1244800</v>
       </c>
       <c r="E81" s="3">
-        <v>1505600</v>
+        <v>1028100</v>
       </c>
       <c r="F81" s="3">
-        <v>887300</v>
+        <v>1675500</v>
       </c>
       <c r="G81" s="3">
-        <v>446700</v>
+        <v>987500</v>
       </c>
       <c r="H81" s="3">
-        <v>2277000</v>
+        <v>497100</v>
       </c>
       <c r="I81" s="3">
-        <v>763800</v>
+        <v>2533900</v>
       </c>
       <c r="J81" s="3">
+        <v>850000</v>
+      </c>
+      <c r="K81" s="3">
         <v>863600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>250400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>881000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>881700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1443500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>898400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1373600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>418700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>214300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1904300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>285900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1222100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>634000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1102000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1344600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1041900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>815200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>956700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>943800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>885600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>773300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>678600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>354800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>689800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>644400</v>
+        <v>746300</v>
       </c>
       <c r="E83" s="3">
-        <v>660400</v>
+        <v>717100</v>
       </c>
       <c r="F83" s="3">
-        <v>801600</v>
+        <v>735000</v>
       </c>
       <c r="G83" s="3">
-        <v>774300</v>
+        <v>892100</v>
       </c>
       <c r="H83" s="3">
-        <v>767700</v>
+        <v>861600</v>
       </c>
       <c r="I83" s="3">
-        <v>788300</v>
+        <v>854400</v>
       </c>
       <c r="J83" s="3">
+        <v>877300</v>
+      </c>
+      <c r="K83" s="3">
         <v>897300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>955600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>945700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>926000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>952600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>962300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>996500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>918100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>992500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>839800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1027900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>989800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>959000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>947800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>934400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>863000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>828800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>819700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>836100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>833100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>836900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>788400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>836200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>793900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1019900</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2639700</v>
+        <v>1016200</v>
       </c>
       <c r="E89" s="3">
-        <v>1441500</v>
+        <v>2937600</v>
       </c>
       <c r="F89" s="3">
-        <v>1268100</v>
+        <v>1604200</v>
       </c>
       <c r="G89" s="3">
-        <v>753900</v>
+        <v>1411200</v>
       </c>
       <c r="H89" s="3">
-        <v>2851600</v>
+        <v>838900</v>
       </c>
       <c r="I89" s="3">
-        <v>934300</v>
+        <v>3173400</v>
       </c>
       <c r="J89" s="3">
+        <v>1039700</v>
+      </c>
+      <c r="K89" s="3">
         <v>813400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>715500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3139300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>657400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>175900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1007500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2600100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1553300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>472800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1311900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2229600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>930700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1165500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>722400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3917700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-91000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>721300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1221300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2295800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1760400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1369900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1147500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2221100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>835800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1773600</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-72192000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-110861000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-78532000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-106661000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-89091000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-105408000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-96150000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-108272000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100755000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-134149000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100626000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-107573000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-488900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-628300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-384800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-471300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-453200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-794100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-595900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-811800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-723700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-857900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-898800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-883000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-934700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-11900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1277100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-889100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2139000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>258100</v>
+        <v>-1664200</v>
       </c>
       <c r="E94" s="3">
-        <v>-393700</v>
+        <v>287300</v>
       </c>
       <c r="F94" s="3">
-        <v>-449300</v>
+        <v>-438200</v>
       </c>
       <c r="G94" s="3">
-        <v>-254300</v>
+        <v>-500000</v>
       </c>
       <c r="H94" s="3">
-        <v>1890600</v>
+        <v>-283000</v>
       </c>
       <c r="I94" s="3">
-        <v>-465300</v>
+        <v>2104000</v>
       </c>
       <c r="J94" s="3">
+        <v>-517900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-485400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-140400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-524200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6808900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-51800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>2178300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-455900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-8267800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>3049100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-297800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2595800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-937000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-962900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>121300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-311700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-357900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-944800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1447200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-721200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1173700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-945800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1217900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>141000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1198700</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,106 +8585,110 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-658200</v>
+      </c>
+      <c r="E96" s="3">
+        <v>700</v>
+      </c>
+      <c r="F96" s="3">
+        <v>-526900</v>
+      </c>
+      <c r="G96" s="3">
+        <v>900</v>
+      </c>
+      <c r="H96" s="3">
+        <v>-499600</v>
+      </c>
+      <c r="I96" s="3">
+        <v>700</v>
+      </c>
+      <c r="J96" s="3">
+        <v>-471300</v>
+      </c>
+      <c r="K96" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L96" s="3">
+        <v>-424400</v>
+      </c>
+      <c r="M96" s="3">
         <v>600</v>
       </c>
-      <c r="E96" s="3">
-        <v>-473400</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="N96" s="3">
+        <v>-399200</v>
+      </c>
+      <c r="O96" s="3">
         <v>800</v>
       </c>
-      <c r="G96" s="3">
-        <v>-448900</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="P96" s="3">
+        <v>-391300</v>
+      </c>
+      <c r="Q96" s="3">
         <v>600</v>
       </c>
-      <c r="I96" s="3">
-        <v>-423500</v>
-      </c>
-      <c r="J96" s="3">
-        <v>1600</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-424400</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="R96" s="3">
+        <v>-355300</v>
+      </c>
+      <c r="S96" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T96" s="3">
+        <v>-412600</v>
+      </c>
+      <c r="U96" s="3">
         <v>600</v>
       </c>
-      <c r="M96" s="3">
-        <v>-399200</v>
-      </c>
-      <c r="N96" s="3">
-        <v>800</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-391300</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="V96" s="3">
+        <v>-397200</v>
+      </c>
+      <c r="W96" s="3">
+        <v>1500</v>
+      </c>
+      <c r="X96" s="3">
+        <v>-442700</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>-365100</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>-351500</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>-305900</v>
+      </c>
+      <c r="AE96" s="3">
         <v>600</v>
       </c>
-      <c r="Q96" s="3">
-        <v>-355300</v>
-      </c>
-      <c r="R96" s="3">
-        <v>1100</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-412600</v>
-      </c>
-      <c r="T96" s="3">
-        <v>600</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-397200</v>
-      </c>
-      <c r="V96" s="3">
-        <v>1500</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-442700</v>
-      </c>
-      <c r="X96" s="3">
-        <v>700</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-365100</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>700</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-351500</v>
-      </c>
-      <c r="AB96" s="3">
+      <c r="AF96" s="3">
+        <v>-305900</v>
+      </c>
+      <c r="AG96" s="3">
         <v>400</v>
       </c>
-      <c r="AC96" s="3">
-        <v>-305900</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>600</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-305900</v>
-      </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
+        <v>-257400</v>
+      </c>
+      <c r="AI96" s="3">
         <v>400</v>
       </c>
-      <c r="AG96" s="3">
-        <v>-257400</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-4141600</v>
+        <v>1377000</v>
       </c>
       <c r="E100" s="3">
-        <v>-1157500</v>
+        <v>-4608900</v>
       </c>
       <c r="F100" s="3">
-        <v>-1063300</v>
+        <v>-1288200</v>
       </c>
       <c r="G100" s="3">
-        <v>-176500</v>
+        <v>-1183300</v>
       </c>
       <c r="H100" s="3">
-        <v>-5627900</v>
+        <v>-196400</v>
       </c>
       <c r="I100" s="3">
-        <v>495200</v>
+        <v>-6263000</v>
       </c>
       <c r="J100" s="3">
+        <v>551100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-2261600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>107900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3369100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>436900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4584400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>78600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4395900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>9900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-723400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4492600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-740400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>152600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-25700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>668100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-3116400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-529700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-258300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>797900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1618500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-748700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-709100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>170400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-864900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2288400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>989900</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>229700</v>
+        <v>264000</v>
       </c>
       <c r="E101" s="3">
-        <v>-155200</v>
+        <v>255600</v>
       </c>
       <c r="F101" s="3">
-        <v>119400</v>
+        <v>-172800</v>
       </c>
       <c r="G101" s="3">
-        <v>265000</v>
+        <v>132900</v>
       </c>
       <c r="H101" s="3">
-        <v>81700</v>
+        <v>294900</v>
       </c>
       <c r="I101" s="3">
-        <v>-369000</v>
+        <v>90900</v>
       </c>
       <c r="J101" s="3">
+        <v>-410600</v>
+      </c>
+      <c r="K101" s="3">
         <v>89500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>406600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>228200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>180400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>22500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>39600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>316900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>46100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>18000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>7000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-152900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>171200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-128000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-189700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>27200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-170600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-254800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>99500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>107600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>59800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-122100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>530100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-69300</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1014000</v>
+        <v>993000</v>
       </c>
       <c r="E102" s="3">
-        <v>-265000</v>
+        <v>-1128400</v>
       </c>
       <c r="F102" s="3">
-        <v>-125100</v>
+        <v>-294900</v>
       </c>
       <c r="G102" s="3">
-        <v>588000</v>
+        <v>-139200</v>
       </c>
       <c r="H102" s="3">
-        <v>-804000</v>
+        <v>654400</v>
       </c>
       <c r="I102" s="3">
-        <v>595100</v>
+        <v>-894700</v>
       </c>
       <c r="J102" s="3">
+        <v>662300</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1360700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>744500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-141900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>750500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2026200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1073900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>699400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1153400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-8500500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>8860600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1038400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1341400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>74800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>237900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>949900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1103100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>104000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1058400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1024800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>390000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-405400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>431900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>16200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-781600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1495500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HTHIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HTHIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
   <si>
     <t>HTHIY</t>
   </si>
@@ -656,454 +656,466 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>15701100</v>
-      </c>
-      <c r="E8" s="3">
-        <v>17825000</v>
-      </c>
-      <c r="F8" s="3">
-        <v>16032400</v>
-      </c>
-      <c r="G8" s="3">
-        <v>18726800</v>
-      </c>
-      <c r="H8" s="3">
-        <v>16489700</v>
-      </c>
-      <c r="I8" s="3">
-        <v>19683700</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>19113300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>18163600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17320600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19375100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17271200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17774300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17400700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>19498900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16264900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16871400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>13599200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>21347400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>19339200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>20114600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>18618500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>25924400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>21628300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>21607900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>19688000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>24359100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>20770000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>20681700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>18881600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>23443000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>19208300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>19720700</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>11155500</v>
-      </c>
-      <c r="E9" s="3">
-        <v>12717700</v>
-      </c>
-      <c r="F9" s="3">
-        <v>11536800</v>
-      </c>
-      <c r="G9" s="3">
-        <v>14075500</v>
-      </c>
-      <c r="H9" s="3">
-        <v>12411000</v>
-      </c>
-      <c r="I9" s="3">
-        <v>14683800</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>14358800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13699200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13172300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14433800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12948800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13386900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13161400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>14759900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12099600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12635200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10060500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>15555900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14178700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>14579000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>13633700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>19379600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>15751100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>15728800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>14420300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>17804700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>15290000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>15148400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>13830300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>17433900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>14170500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>14505800</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>4545600</v>
-      </c>
-      <c r="E10" s="3">
-        <v>5107300</v>
-      </c>
-      <c r="F10" s="3">
-        <v>4495600</v>
-      </c>
-      <c r="G10" s="3">
-        <v>4651300</v>
-      </c>
-      <c r="H10" s="3">
-        <v>4078600</v>
-      </c>
-      <c r="I10" s="3">
-        <v>4999900</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>4754500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4464400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4148300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4941300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4322400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4387400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4239200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4739000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4165300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4236200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3538700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5791400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5160500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5535500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4984800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6544800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5877200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5879200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>5267700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>6554300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5479900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5533300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5051300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>6009100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>5037800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>5214900</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1151,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1253,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,67 +1357,70 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>252400</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-572900</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-53500</v>
-      </c>
-      <c r="H14" s="3">
-        <v>58300</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-1166800</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>47900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-13000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>28300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>176000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>55000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-428000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-245700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-853500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>256500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>325700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-2389500</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1442,31 +1461,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1565,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1602,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>14298000</v>
-      </c>
-      <c r="E17" s="3">
-        <v>16443600</v>
-      </c>
-      <c r="F17" s="3">
-        <v>14038000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>17289300</v>
-      </c>
-      <c r="H17" s="3">
-        <v>15621100</v>
-      </c>
-      <c r="I17" s="3">
-        <v>16950300</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>17720900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16855000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16529600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17866000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16128100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16051500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16195900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>17381500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15523600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>16243500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10711800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>19442200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>17987000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>18526400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>17479100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>23806000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>19835200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>19783000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>18341400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>22188700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>19221300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>19132200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>17689700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>21707800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>18186600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>18780900</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>1403100</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1381400</v>
-      </c>
-      <c r="F18" s="3">
-        <v>1994400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1437500</v>
-      </c>
-      <c r="H18" s="3">
-        <v>868500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>2733400</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>1392400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1308600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>791000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1509100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1143100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1722800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1204700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2117400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>741300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>628000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2887400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1905200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1352200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1588200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1139400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2118400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1793100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1824900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1346700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2170300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1548600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1549500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1191800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1735100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1021800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>939800</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1848,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>525100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>36500</v>
-      </c>
-      <c r="F20" s="3">
-        <v>401100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>170700</v>
-      </c>
-      <c r="H20" s="3">
-        <v>76500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-41600</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>-53700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>80400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-212100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>175400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>91000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>150500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>69100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>373000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>149700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-235800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>47600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-725600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3452500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-545700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>577900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-53600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2174600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-175700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>335400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-583700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>82700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-132600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>132400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-702400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>286900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>2674500</v>
-      </c>
-      <c r="E21" s="3">
-        <v>2135100</v>
-      </c>
-      <c r="F21" s="3">
-        <v>3130500</v>
-      </c>
-      <c r="G21" s="3">
-        <v>2500300</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1806700</v>
-      </c>
-      <c r="I21" s="3">
-        <v>3546200</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="3">
         <v>2216000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2286300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1534400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2630100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2160100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2825900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2236100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3486900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1809100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1384600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3774700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2207500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1110500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2001500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2665100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2999300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>481600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2478000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2501800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2422700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2464400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2253700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2112600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1868900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2102600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1987900</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>136300</v>
-      </c>
-      <c r="E22" s="3">
-        <v>113700</v>
-      </c>
-      <c r="F22" s="3">
-        <v>123100</v>
-      </c>
-      <c r="G22" s="3">
-        <v>141600</v>
-      </c>
-      <c r="H22" s="3">
-        <v>125100</v>
-      </c>
-      <c r="I22" s="3">
-        <v>113400</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
         <v>98600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>77700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>62500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>50500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>44600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>47300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>47400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>40900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>50200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>45100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>37200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>50600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>57400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>58200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>51300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>49200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>54300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>47100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>41700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>45400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>48500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>47200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>44600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>38100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>42000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>41800</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>1791900</v>
-      </c>
-      <c r="E23" s="3">
-        <v>1304200</v>
-      </c>
-      <c r="F23" s="3">
-        <v>2272400</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1466700</v>
-      </c>
-      <c r="H23" s="3">
-        <v>819900</v>
-      </c>
-      <c r="I23" s="3">
-        <v>2578400</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>1240200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1311300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>516300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1634000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1189500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1825900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1226400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2449500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>840800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>347000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2897700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1129000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2157700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>984300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1665900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2015600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-435700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1602100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1640400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1541300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1582800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1369600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1279600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>994600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1266600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>926100</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>465900</v>
-      </c>
-      <c r="E24" s="3">
-        <v>237500</v>
-      </c>
-      <c r="F24" s="3">
-        <v>538800</v>
-      </c>
-      <c r="G24" s="3">
-        <v>396900</v>
-      </c>
-      <c r="H24" s="3">
-        <v>240100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-48700</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3">
         <v>295800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>330100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>199200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>580700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>174000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>185900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>219800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1000000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>347100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>186800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>962900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>762200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1147100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>454200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>377600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>469000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>422800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>407300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>444600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>137800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>394200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>340500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>318200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>339400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>295300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>179000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2470,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>1326000</v>
-      </c>
-      <c r="E26" s="3">
-        <v>1066700</v>
-      </c>
-      <c r="F26" s="3">
-        <v>1733600</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1069700</v>
-      </c>
-      <c r="H26" s="3">
-        <v>579900</v>
-      </c>
-      <c r="I26" s="3">
-        <v>2627100</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>944400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>981200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>317100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1053300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1015600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1640000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1006600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1449500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>493700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>160200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1934800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>366800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1010700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>530100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1288300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1546600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-858600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1194900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1195800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1403500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1188600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1029200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>961500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>655200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>971300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>747200</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>1244800</v>
-      </c>
-      <c r="E27" s="3">
-        <v>1028100</v>
-      </c>
-      <c r="F27" s="3">
-        <v>1675500</v>
-      </c>
-      <c r="G27" s="3">
-        <v>987500</v>
-      </c>
-      <c r="H27" s="3">
-        <v>497100</v>
-      </c>
-      <c r="I27" s="3">
-        <v>2533900</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>850000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>863600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>250400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>881000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>881700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1443500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>898400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1373600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>418700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>217000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1907200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>291100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1218500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>637600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1105700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1390100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1038100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>907000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>903300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1089500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>873200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>784200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>679200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>399800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>697700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>509700</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,31 +2782,34 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2776,58 +2836,61 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>-2700</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-2900</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-5200</v>
-      </c>
-      <c r="V29" s="3">
-        <v>-3600</v>
       </c>
       <c r="W29" s="3">
         <v>-3600</v>
       </c>
       <c r="X29" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-45500</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-91800</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>53400</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-145700</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>12400</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-10900</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-600</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-45100</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-7900</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2990,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3094,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-525100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-36500</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-401100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-170700</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-76500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>41600</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>53700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-80400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>212100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-175400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-91000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-150500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-69100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-373000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-149700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>235800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-47600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>725600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3452500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>545700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-577900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>53600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2174600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>175700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-335400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>583700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-82700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>132600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-132400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>702400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-286900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-28100</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>1244800</v>
-      </c>
-      <c r="E33" s="3">
-        <v>1028100</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1675500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>987500</v>
-      </c>
-      <c r="H33" s="3">
-        <v>497100</v>
-      </c>
-      <c r="I33" s="3">
-        <v>2533900</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>850000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>863600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>250400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>881000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>881700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1443500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>898400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1373600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>418700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>214300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1904300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>285900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1222100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>634000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1102000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1344600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1041900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>815200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>956700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>943800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>885600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>773300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>678600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>354800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>689800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3406,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>1244800</v>
-      </c>
-      <c r="E35" s="3">
-        <v>1028100</v>
-      </c>
-      <c r="F35" s="3">
-        <v>1675500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>987500</v>
-      </c>
-      <c r="H35" s="3">
-        <v>497100</v>
-      </c>
-      <c r="I35" s="3">
-        <v>2533900</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>850000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>863600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>250400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>881000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>881700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1443500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>898400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1373600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>418700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>214300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1904300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>285900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1222100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>634000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1102000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1344600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1041900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>815200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>956700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>943800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>885600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>773300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>678600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>354800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>689800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3659,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,917 +3697,945 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6001100</v>
+        <v>5544100</v>
       </c>
       <c r="E41" s="3">
-        <v>5008100</v>
+        <v>5254200</v>
       </c>
       <c r="F41" s="3">
-        <v>6136500</v>
+        <v>4663400</v>
       </c>
       <c r="G41" s="3">
-        <v>6431400</v>
+        <v>6131400</v>
       </c>
       <c r="H41" s="3">
-        <v>6570700</v>
+        <v>6064700</v>
       </c>
       <c r="I41" s="3">
-        <v>5916300</v>
+        <v>6400700</v>
       </c>
       <c r="J41" s="3">
+        <v>6268400</v>
+      </c>
+      <c r="K41" s="3">
         <v>5961200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5525200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7274400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6433000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6802700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6351800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8540600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7202600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6723400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5919500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>15789700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7156600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6326500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7735200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7635500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7761000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6690600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7669800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7402900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6309600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>7334400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6944300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7349700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6787700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6771500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>7553100</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2332100</v>
+        <v>2132100</v>
       </c>
       <c r="E42" s="3">
-        <v>2352100</v>
+        <v>2041900</v>
       </c>
       <c r="F42" s="3">
-        <v>2078200</v>
+        <v>2190200</v>
       </c>
       <c r="G42" s="3">
-        <v>2305000</v>
+        <v>2076500</v>
       </c>
       <c r="H42" s="3">
-        <v>2856000</v>
+        <v>2173600</v>
       </c>
       <c r="I42" s="3">
-        <v>2463100</v>
+        <v>2782200</v>
       </c>
       <c r="J42" s="3">
+        <v>2609700</v>
+      </c>
+      <c r="K42" s="3">
         <v>1934400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2124500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2780300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2498700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2058500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2439100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2416300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2326600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2238300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2240900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2179300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2466400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2925600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2532000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2600300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2731800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>3037900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2792200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>3453500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>3374800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2939900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2708500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>3501600</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH42" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI42" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ42" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>22414800</v>
+        <v>21499500</v>
       </c>
       <c r="E43" s="3">
-        <v>21238300</v>
+        <v>19625100</v>
       </c>
       <c r="F43" s="3">
-        <v>19317700</v>
+        <v>19776600</v>
       </c>
       <c r="G43" s="3">
-        <v>21264000</v>
+        <v>19301700</v>
       </c>
       <c r="H43" s="3">
-        <v>19461400</v>
+        <v>20051500</v>
       </c>
       <c r="I43" s="3">
-        <v>20412400</v>
+        <v>18958000</v>
       </c>
       <c r="J43" s="3">
+        <v>21627200</v>
+      </c>
+      <c r="K43" s="3">
         <v>18238600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>17864700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>18629400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>19774900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>18424400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>18472800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>18322300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>19387400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>17315500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>17898000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>14873600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>19912400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>19995800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>19820500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>19347400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>23063400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>20887500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>20792200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>19477900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>22612800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>20017900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>21216900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>19871600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>21957800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>19728100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>25974400</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>12149900</v>
+        <v>11216400</v>
       </c>
       <c r="E44" s="3">
-        <v>10725600</v>
+        <v>10637800</v>
       </c>
       <c r="F44" s="3">
-        <v>11364500</v>
+        <v>9987400</v>
       </c>
       <c r="G44" s="3">
-        <v>13234200</v>
+        <v>11355000</v>
       </c>
       <c r="H44" s="3">
-        <v>12988000</v>
+        <v>12479600</v>
       </c>
       <c r="I44" s="3">
-        <v>11687900</v>
+        <v>12652100</v>
       </c>
       <c r="J44" s="3">
+        <v>12383500</v>
+      </c>
+      <c r="K44" s="3">
         <v>12515200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12670200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>15703200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>13561700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>13883600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>13376400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>13211400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>11722600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>12228700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>12212600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>12348200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>12412700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>14707900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>13615300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>13569800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>13038500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>14975900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>13820200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>13141900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>12432100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>14097600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>12782800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>12369500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>10873800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>12655400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>11737600</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2969800</v>
+        <v>2523100</v>
       </c>
       <c r="E45" s="3">
-        <v>2243500</v>
+        <v>2600200</v>
       </c>
       <c r="F45" s="3">
-        <v>2523600</v>
+        <v>2089100</v>
       </c>
       <c r="G45" s="3">
-        <v>2436000</v>
+        <v>2521500</v>
       </c>
       <c r="H45" s="3">
-        <v>2508900</v>
+        <v>2297100</v>
       </c>
       <c r="I45" s="3">
-        <v>1612800</v>
+        <v>2444000</v>
       </c>
       <c r="J45" s="3">
+        <v>1708800</v>
+      </c>
+      <c r="K45" s="3">
         <v>10609100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1898400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2040100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1551800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2556900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2070600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1818300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1498800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1681100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1832800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4113500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4018800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6546100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2042700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2117200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1799400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2361700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2166700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2156900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1842900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2258300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2187200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2212300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4753800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4708100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>4654500</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>45867700</v>
+        <v>42915100</v>
       </c>
       <c r="E46" s="3">
-        <v>41567600</v>
+        <v>40159200</v>
       </c>
       <c r="F46" s="3">
-        <v>41420600</v>
+        <v>38706800</v>
       </c>
       <c r="G46" s="3">
-        <v>45670800</v>
+        <v>41386200</v>
       </c>
       <c r="H46" s="3">
-        <v>44385000</v>
+        <v>43066500</v>
       </c>
       <c r="I46" s="3">
-        <v>42092600</v>
+        <v>43236900</v>
       </c>
       <c r="J46" s="3">
+        <v>44597600</v>
+      </c>
+      <c r="K46" s="3">
         <v>49258500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>40083000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>46427400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>43820200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>43726000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>42710700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>44308900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>42138000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>40187000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>40103800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>49304300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>45967000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>50502000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>45745800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>45270100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>48394000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>47953500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>47241100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>45633100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>46572300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>46648100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>45839800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>45304800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>44373100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>43863100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>49919500</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>8479100</v>
+        <v>11077300</v>
       </c>
       <c r="E47" s="3">
-        <v>8069400</v>
+        <v>7423800</v>
       </c>
       <c r="F47" s="3">
-        <v>9033100</v>
+        <v>8654800</v>
       </c>
       <c r="G47" s="3">
-        <v>7365200</v>
+        <v>11988300</v>
       </c>
       <c r="H47" s="3">
-        <v>7366400</v>
+        <v>10202700</v>
       </c>
       <c r="I47" s="3">
-        <v>6926200</v>
+        <v>10289700</v>
       </c>
       <c r="J47" s="3">
+        <v>8957900</v>
+      </c>
+      <c r="K47" s="3">
         <v>6823800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7123800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6934300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6613500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6824000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7105800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7097900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7135600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6667500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7063000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7699800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8113000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>9074100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12086600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>11909900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12423900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12268900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12733300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>12636400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>13196900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>13425300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>13164700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>12783700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>12515200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>13097300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>16937400</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>9096000</v>
+        <v>8514000</v>
       </c>
       <c r="E48" s="3">
-        <v>8675100</v>
+        <v>7963900</v>
       </c>
       <c r="F48" s="3">
-        <v>8332400</v>
+        <v>8078000</v>
       </c>
       <c r="G48" s="3">
-        <v>12590400</v>
+        <v>8325500</v>
       </c>
       <c r="H48" s="3">
-        <v>12478300</v>
+        <v>11872500</v>
       </c>
       <c r="I48" s="3">
-        <v>12073300</v>
+        <v>12155500</v>
       </c>
       <c r="J48" s="3">
+        <v>12791800</v>
+      </c>
+      <c r="K48" s="3">
         <v>12067500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13491700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>17274800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16459900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>16629700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17237600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17652400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17079000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>15682000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>16694300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>16517900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19076400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20106600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19703700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19759100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>18803700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>18389900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20003800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19357100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19208400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>19232200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>18881700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>18246800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>17725900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>17662900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>20069600</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>28465900</v>
+        <v>25224100</v>
       </c>
       <c r="E49" s="3">
-        <v>25208000</v>
+        <v>24923100</v>
       </c>
       <c r="F49" s="3">
-        <v>23968600</v>
+        <v>23473100</v>
       </c>
       <c r="G49" s="3">
-        <v>26593100</v>
+        <v>23948700</v>
       </c>
       <c r="H49" s="3">
-        <v>25976900</v>
+        <v>25076700</v>
       </c>
       <c r="I49" s="3">
-        <v>24211300</v>
+        <v>25305000</v>
       </c>
       <c r="J49" s="3">
+        <v>25652100</v>
+      </c>
+      <c r="K49" s="3">
         <v>23738800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>23826100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>25113500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>22647900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>22308700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>23106900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15617200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>15073600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>14192100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>15141300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9038200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9829500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10478300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8381100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8770800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9225800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9348100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>9968300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9621800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9531500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>10139000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>10111900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>8483100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>8153300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>8193600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>8309100</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4735,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4839,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>3263900</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E52" s="3">
-        <v>3251000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>2965200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>3454400</v>
-      </c>
-      <c r="H52" s="3">
-        <v>3196600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>3456700</v>
-      </c>
-      <c r="J52" s="3">
+        <v>2857700</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" s="3">
         <v>2406600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2354000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2667900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2671500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2733700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2700300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2786600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2610500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3472000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3696300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4109000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4498100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3502200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3405900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3442200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3664200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3546200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3512500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3057200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2854500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2728600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2784700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2792500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2951400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2691400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>9247200</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5047,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>95172600</v>
+        <v>87730500</v>
       </c>
       <c r="E54" s="3">
-        <v>86771100</v>
+        <v>83327700</v>
       </c>
       <c r="F54" s="3">
-        <v>85719800</v>
+        <v>80799200</v>
       </c>
       <c r="G54" s="3">
-        <v>95673900</v>
+        <v>85648700</v>
       </c>
       <c r="H54" s="3">
-        <v>93403100</v>
+        <v>90218400</v>
       </c>
       <c r="I54" s="3">
-        <v>88760000</v>
+        <v>90987100</v>
       </c>
       <c r="J54" s="3">
+        <v>94042300</v>
+      </c>
+      <c r="K54" s="3">
         <v>94295100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>86878700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>98418000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>92213000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>92222000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>92861400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>87463100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>84036700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>80200700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>82698800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>86669200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>87484000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>93663200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>89323100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>89152000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>92511500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>91506600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>93459000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>90305500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>91363700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>92173200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>90782700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>87610900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>85718900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>85508400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>104482800</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5191,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,614 +5229,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>10773000</v>
+        <v>10207600</v>
       </c>
       <c r="E57" s="3">
-        <v>9937900</v>
+        <v>9432200</v>
       </c>
       <c r="F57" s="3">
-        <v>9531000</v>
+        <v>9253900</v>
       </c>
       <c r="G57" s="3">
-        <v>11191200</v>
+        <v>9523100</v>
       </c>
       <c r="H57" s="3">
-        <v>11144100</v>
+        <v>10553000</v>
       </c>
       <c r="I57" s="3">
-        <v>10994300</v>
+        <v>10855800</v>
       </c>
       <c r="J57" s="3">
+        <v>11648600</v>
+      </c>
+      <c r="K57" s="3">
         <v>10499200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10878200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12105000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11650800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10957900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10787600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11144000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10748100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9809900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9797100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9368400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11194600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11828400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11275400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11927900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>13511800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12785400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12738900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12718200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>13894300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>13397100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12889700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>12346100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>12437800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>11908500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>11654900</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4394000</v>
+        <v>3935800</v>
       </c>
       <c r="E58" s="3">
-        <v>1599700</v>
+        <v>3847100</v>
       </c>
       <c r="F58" s="3">
-        <v>4163600</v>
+        <v>1489600</v>
       </c>
       <c r="G58" s="3">
-        <v>7348500</v>
+        <v>4160100</v>
       </c>
       <c r="H58" s="3">
-        <v>7713900</v>
+        <v>6929500</v>
       </c>
       <c r="I58" s="3">
-        <v>6528500</v>
+        <v>7514300</v>
       </c>
       <c r="J58" s="3">
+        <v>6917000</v>
+      </c>
+      <c r="K58" s="3">
         <v>12408500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8625500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12483000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10428400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>13041400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12086700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6548900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4899400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>9077200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>12284200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>12318200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3652100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>6529700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5029300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4536800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2847300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5429700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4508500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4229900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2157200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3742700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3865500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>4202800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3429100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3937900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>12512300</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>24808600</v>
+        <v>18753000</v>
       </c>
       <c r="E59" s="3">
-        <v>22560900</v>
+        <v>18295400</v>
       </c>
       <c r="F59" s="3">
-        <v>20734400</v>
+        <v>16396900</v>
       </c>
       <c r="G59" s="3">
-        <v>21047800</v>
+        <v>16765700</v>
       </c>
       <c r="H59" s="3">
-        <v>19952400</v>
+        <v>15008200</v>
       </c>
       <c r="I59" s="3">
-        <v>19157000</v>
+        <v>15378500</v>
       </c>
       <c r="J59" s="3">
+        <v>14873600</v>
+      </c>
+      <c r="K59" s="3">
         <v>20275000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17563000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17017900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>16791900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15810000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16046600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16697900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16944700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15956700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>16120700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>17854300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>18042600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>19847800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>16505800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>16298200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>18290400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>17134300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>17568000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>16763300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>18258800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>17693700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>17628000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>16719600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>17137200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>16265100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>16240700</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>39975600</v>
+        <v>37169400</v>
       </c>
       <c r="E60" s="3">
-        <v>34098500</v>
+        <v>35000400</v>
       </c>
       <c r="F60" s="3">
-        <v>34429000</v>
+        <v>31751700</v>
       </c>
       <c r="G60" s="3">
-        <v>39587500</v>
+        <v>34400400</v>
       </c>
       <c r="H60" s="3">
-        <v>38810400</v>
+        <v>37330200</v>
       </c>
       <c r="I60" s="3">
-        <v>36679900</v>
+        <v>37806500</v>
       </c>
       <c r="J60" s="3">
+        <v>38862700</v>
+      </c>
+      <c r="K60" s="3">
         <v>43182600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>37066800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>41605900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>38871000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>39809300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>38920800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>34390800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>32592200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>34843800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>38202100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>39540800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>32889300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>38205800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>32810500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>32762900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>34649400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>35349400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>34815400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>33711400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>34310400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>34833500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>34383200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>33268500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>33004000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>32111400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>40407900</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7077600</v>
+        <v>6737400</v>
       </c>
       <c r="E61" s="3">
-        <v>6778400</v>
+        <v>6196700</v>
       </c>
       <c r="F61" s="3">
-        <v>8293800</v>
+        <v>6311900</v>
       </c>
       <c r="G61" s="3">
-        <v>9520000</v>
+        <v>8287000</v>
       </c>
       <c r="H61" s="3">
-        <v>9462100</v>
+        <v>8977200</v>
       </c>
       <c r="I61" s="3">
-        <v>9186200</v>
+        <v>9217300</v>
       </c>
       <c r="J61" s="3">
+        <v>9732900</v>
+      </c>
+      <c r="K61" s="3">
         <v>9280200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9269000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10837200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10333000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11118900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11804800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12061200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12097900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9983800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7275300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8505400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9431100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7705500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7720200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8081000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6808600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7076600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6652500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6755400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7337400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7529400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7629600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7261000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7007400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7631500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>19851800</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4521500</v>
+        <v>2470900</v>
       </c>
       <c r="E62" s="3">
-        <v>4291000</v>
+        <v>2306900</v>
       </c>
       <c r="F62" s="3">
-        <v>4490900</v>
+        <v>1626500</v>
       </c>
       <c r="G62" s="3">
-        <v>5203500</v>
+        <v>2488200</v>
       </c>
       <c r="H62" s="3">
-        <v>5096900</v>
+        <v>2715000</v>
       </c>
       <c r="I62" s="3">
-        <v>5011400</v>
+        <v>2701400</v>
       </c>
       <c r="J62" s="3">
+        <v>1710500</v>
+      </c>
+      <c r="K62" s="3">
         <v>5121100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5332800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7899900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7450000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7621300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7886600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7913300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7737800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>8641200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>9389500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7054800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7573600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8011800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7935100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7819600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8631100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8503900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8634300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8575800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8930400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>9587400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>9519400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9427600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9367200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9692000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9942400</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5955,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6059,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6163,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>52629000</v>
+        <v>48253800</v>
       </c>
       <c r="E66" s="3">
-        <v>46274800</v>
+        <v>45155800</v>
       </c>
       <c r="F66" s="3">
-        <v>48241300</v>
+        <v>42059300</v>
       </c>
       <c r="G66" s="3">
-        <v>57221700</v>
+        <v>47174600</v>
       </c>
       <c r="H66" s="3">
-        <v>56162800</v>
+        <v>51214100</v>
       </c>
       <c r="I66" s="3">
-        <v>53665800</v>
+        <v>51988900</v>
       </c>
       <c r="J66" s="3">
+        <v>53905300</v>
+      </c>
+      <c r="K66" s="3">
         <v>62173500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>55928700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>67291300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>63383200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>65084500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>65283900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>61047200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>59040900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>58736000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>59983500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>60767600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>59644500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>64242700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>58617400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>59031200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>61157900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>61843400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>61415400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>59788500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>61730400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>63059800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>62347900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>60372500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>59400900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>59920500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>81205500</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6307,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6409,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6513,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6617,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6721,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>29575200</v>
+        <v>29895400</v>
       </c>
       <c r="E72" s="3">
-        <v>29001600</v>
+        <v>25894400</v>
       </c>
       <c r="F72" s="3">
-        <v>27292700</v>
+        <v>27005600</v>
       </c>
       <c r="G72" s="3">
-        <v>26857400</v>
+        <v>27270100</v>
       </c>
       <c r="H72" s="3">
-        <v>25861600</v>
+        <v>25325900</v>
       </c>
       <c r="I72" s="3">
-        <v>25824000</v>
+        <v>25192600</v>
       </c>
       <c r="J72" s="3">
+        <v>27360800</v>
+      </c>
+      <c r="K72" s="3">
         <v>23149500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>21426100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>21664600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>21232900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>20987100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>21520400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>20473000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>19218200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>18264800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>19425200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>21120100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>20229600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>20621300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>22424100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>21711000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>21983700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>20149100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>21201100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>19948300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>19032800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>18040300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>17443200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>16664700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>15909000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>15530900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>15048500</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6929,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7033,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7137,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>42543600</v>
+        <v>38400200</v>
       </c>
       <c r="E76" s="3">
-        <v>40496300</v>
+        <v>37248700</v>
       </c>
       <c r="F76" s="3">
-        <v>37478500</v>
+        <v>37709200</v>
       </c>
       <c r="G76" s="3">
-        <v>38452300</v>
+        <v>37447400</v>
       </c>
       <c r="H76" s="3">
-        <v>37240300</v>
+        <v>36259600</v>
       </c>
       <c r="I76" s="3">
-        <v>35094300</v>
+        <v>36277000</v>
       </c>
       <c r="J76" s="3">
+        <v>37182800</v>
+      </c>
+      <c r="K76" s="3">
         <v>32121600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>30949900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>31126700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>28829800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>27137600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>27577500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>26415900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>24995800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>21464600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>22715300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>25901600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>27839500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>29420500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>30705700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>30120900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>31353600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>29663100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>32043600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>30517000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>29633300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>29113400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>28434800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>27238300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>26318000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>25587900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>23277400</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7345,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>1244800</v>
-      </c>
-      <c r="E81" s="3">
-        <v>1028100</v>
-      </c>
-      <c r="F81" s="3">
-        <v>1675500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>987500</v>
-      </c>
-      <c r="H81" s="3">
-        <v>497100</v>
-      </c>
-      <c r="I81" s="3">
-        <v>2533900</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>850000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>863600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>250400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>881000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>881700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1443500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>898400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1373600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>418700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>214300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1904300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>285900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1222100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>634000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1102000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1344600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1041900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>815200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>956700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>943800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>885600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>773300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>678600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>354800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>689800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7598,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>746300</v>
+        <v>841200</v>
       </c>
       <c r="E83" s="3">
-        <v>717100</v>
+        <v>839300</v>
       </c>
       <c r="F83" s="3">
-        <v>735000</v>
+        <v>905200</v>
       </c>
       <c r="G83" s="3">
-        <v>892100</v>
+        <v>937000</v>
       </c>
       <c r="H83" s="3">
-        <v>861600</v>
+        <v>972000</v>
       </c>
       <c r="I83" s="3">
-        <v>854400</v>
+        <v>1043300</v>
       </c>
       <c r="J83" s="3">
+        <v>605400</v>
+      </c>
+      <c r="K83" s="3">
         <v>877300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>897300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>955600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>945700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>926000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>952600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>962300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>996500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>918100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>992500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>839800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1027900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>989800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>959000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>947800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>934400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>863000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>828800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>819700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>836100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>833100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>836900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>788400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>836200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>793900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1019900</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7804,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7908,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8012,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8116,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8220,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1016200</v>
+        <v>1257900</v>
       </c>
       <c r="E89" s="3">
-        <v>2937600</v>
+        <v>889700</v>
       </c>
       <c r="F89" s="3">
-        <v>1604200</v>
+        <v>2735400</v>
       </c>
       <c r="G89" s="3">
-        <v>1411200</v>
+        <v>1602800</v>
       </c>
       <c r="H89" s="3">
-        <v>838900</v>
+        <v>1330800</v>
       </c>
       <c r="I89" s="3">
-        <v>3173400</v>
+        <v>817200</v>
       </c>
       <c r="J89" s="3">
+        <v>3362200</v>
+      </c>
+      <c r="K89" s="3">
         <v>1039700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>813400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>715500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3139300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>657400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>175900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1007500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2600100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1553300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>472800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1311900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2229600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>930700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1165500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>722400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3917700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-91000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>721300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1221300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2295800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1760400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1369900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1147500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2221100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>835800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1773600</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8364,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-72192000</v>
+        <v>-348900</v>
       </c>
       <c r="E91" s="3">
-        <v>-110861000</v>
+        <v>-254400</v>
       </c>
       <c r="F91" s="3">
-        <v>-78532000</v>
+        <v>-476000</v>
       </c>
       <c r="G91" s="3">
-        <v>-106661000</v>
+        <v>-314200</v>
       </c>
       <c r="H91" s="3">
-        <v>-89091000</v>
+        <v>-420500</v>
       </c>
       <c r="I91" s="3">
-        <v>-105408000</v>
+        <v>-372000</v>
       </c>
       <c r="J91" s="3">
+        <v>-421200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-96150000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-108272000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100755000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-134149000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100626000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-107573000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-488900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-628300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-384800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-471300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-453200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-794100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-595900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-811800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-723700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-857900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-898800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-883000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-934700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-11900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1277100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-889100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2139000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8570,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8674,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1664200</v>
+        <v>-540900</v>
       </c>
       <c r="E94" s="3">
-        <v>287300</v>
+        <v>-1457100</v>
       </c>
       <c r="F94" s="3">
-        <v>-438200</v>
+        <v>267500</v>
       </c>
       <c r="G94" s="3">
-        <v>-500000</v>
+        <v>-437800</v>
       </c>
       <c r="H94" s="3">
-        <v>-283000</v>
+        <v>-471500</v>
       </c>
       <c r="I94" s="3">
-        <v>2104000</v>
+        <v>-275700</v>
       </c>
       <c r="J94" s="3">
+        <v>2229200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-517900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-485400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-140400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-524200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6808900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-51800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>2178300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-455900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-8267800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>3049100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-297800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2595800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-937000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-962900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>121300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-311700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-357900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-944800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1447200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-721200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1173700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-945800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1217900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>141000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1198700</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,109 +8818,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>-658200</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E96" s="3">
+        <v>576300</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
+        <v>-471300</v>
+      </c>
+      <c r="L96" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M96" s="3">
+        <v>-424400</v>
+      </c>
+      <c r="N96" s="3">
+        <v>600</v>
+      </c>
+      <c r="O96" s="3">
+        <v>-399200</v>
+      </c>
+      <c r="P96" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>-391300</v>
+      </c>
+      <c r="R96" s="3">
+        <v>600</v>
+      </c>
+      <c r="S96" s="3">
+        <v>-355300</v>
+      </c>
+      <c r="T96" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U96" s="3">
+        <v>-412600</v>
+      </c>
+      <c r="V96" s="3">
+        <v>600</v>
+      </c>
+      <c r="W96" s="3">
+        <v>-397200</v>
+      </c>
+      <c r="X96" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>-442700</v>
+      </c>
+      <c r="Z96" s="3">
         <v>700</v>
       </c>
-      <c r="F96" s="3">
-        <v>-526900</v>
-      </c>
-      <c r="G96" s="3">
-        <v>900</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-499600</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="AA96" s="3">
+        <v>-365100</v>
+      </c>
+      <c r="AB96" s="3">
         <v>700</v>
       </c>
-      <c r="J96" s="3">
-        <v>-471300</v>
-      </c>
-      <c r="K96" s="3">
-        <v>1600</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-424400</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="AC96" s="3">
+        <v>-351500</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>-305900</v>
+      </c>
+      <c r="AF96" s="3">
         <v>600</v>
       </c>
-      <c r="N96" s="3">
-        <v>-399200</v>
-      </c>
-      <c r="O96" s="3">
-        <v>800</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-391300</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>600</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-355300</v>
-      </c>
-      <c r="S96" s="3">
-        <v>1100</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-412600</v>
-      </c>
-      <c r="U96" s="3">
-        <v>600</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-397200</v>
-      </c>
-      <c r="W96" s="3">
-        <v>1500</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-442700</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>700</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-365100</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>700</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-351500</v>
-      </c>
-      <c r="AC96" s="3">
+      <c r="AG96" s="3">
+        <v>-305900</v>
+      </c>
+      <c r="AH96" s="3">
         <v>400</v>
       </c>
-      <c r="AD96" s="3">
-        <v>-305900</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>600</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-305900</v>
-      </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
+        <v>-257400</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>400</v>
       </c>
-      <c r="AH96" s="3">
-        <v>-257400</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>400</v>
-      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9024,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9128,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9232,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1377000</v>
+        <v>-662500</v>
       </c>
       <c r="E100" s="3">
-        <v>-4608900</v>
+        <v>1205700</v>
       </c>
       <c r="F100" s="3">
-        <v>-1288200</v>
+        <v>-4291700</v>
       </c>
       <c r="G100" s="3">
-        <v>-1183300</v>
+        <v>-1287100</v>
       </c>
       <c r="H100" s="3">
-        <v>-196400</v>
+        <v>-1115800</v>
       </c>
       <c r="I100" s="3">
-        <v>-6263000</v>
+        <v>-191300</v>
       </c>
       <c r="J100" s="3">
+        <v>-6635700</v>
+      </c>
+      <c r="K100" s="3">
         <v>551100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2261600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>107900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3369100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>436900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4584400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>78600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4395900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>9900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-723400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4492600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-740400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>152600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-25700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>668100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3116400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-529700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-258300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>797900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1618500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-748700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-709100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>170400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-864900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2288400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>989900</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>264000</v>
+        <v>125300</v>
       </c>
       <c r="E101" s="3">
-        <v>255600</v>
+        <v>287200</v>
       </c>
       <c r="F101" s="3">
-        <v>-172800</v>
+        <v>96300</v>
       </c>
       <c r="G101" s="3">
-        <v>132900</v>
+        <v>-438600</v>
       </c>
       <c r="H101" s="3">
-        <v>294900</v>
+        <v>97000</v>
       </c>
       <c r="I101" s="3">
-        <v>90900</v>
+        <v>443900</v>
       </c>
       <c r="J101" s="3">
+        <v>283000</v>
+      </c>
+      <c r="K101" s="3">
         <v>-410600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>89500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>406600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>228200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>180400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>22500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>39600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>316900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>46100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>18000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>7000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-152900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>171200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-128000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-189700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>27200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-170600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-254800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>99500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>107600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>59800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-122100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>530100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-69300</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>993000</v>
+        <v>-355700</v>
       </c>
       <c r="E102" s="3">
-        <v>-1128400</v>
+        <v>869400</v>
       </c>
       <c r="F102" s="3">
-        <v>-294900</v>
+        <v>-1050800</v>
       </c>
       <c r="G102" s="3">
-        <v>-139200</v>
+        <v>-294700</v>
       </c>
       <c r="H102" s="3">
-        <v>654400</v>
+        <v>-131300</v>
       </c>
       <c r="I102" s="3">
-        <v>-894700</v>
+        <v>637400</v>
       </c>
       <c r="J102" s="3">
+        <v>-948000</v>
+      </c>
+      <c r="K102" s="3">
         <v>662300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1360700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>744500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-141900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>750500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2026200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1073900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>699400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1153400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-8500500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8860600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1038400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1341400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>74800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>237900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>949900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1103100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>104000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1058400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1024800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>390000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-405400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>431900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>16200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-781600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1495500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HTHIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HTHIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
   <si>
     <t>HTHIY</t>
   </si>
@@ -656,154 +656,157 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -828,86 +831,89 @@
       <c r="J8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3">
         <v>19113300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18163600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17320600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19375100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17271200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17774300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>17400700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>19498900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16264900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>16871400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>13599200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>21347400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>19339200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>20114600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>18618500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>25924400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>21628300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>21607900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>19688000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>24359100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>20770000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>20681700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>18881600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>23443000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>19208300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>19720700</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -932,86 +938,89 @@
       <c r="J9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3">
         <v>14358800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13699200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13172300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14433800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12948800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13386900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13161400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>14759900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12099600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12635200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>10060500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>15555900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>14178700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>14579000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>13633700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>19379600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>15751100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>15728800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>14420300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>17804700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>15290000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>15148400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>13830300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>17433900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>14170500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>14505800</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1036,86 +1045,89 @@
       <c r="J10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="3">
         <v>4754500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4464400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4148300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4941300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4322400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4387400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4239200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4739000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4165300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4236200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3538700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5791400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5160500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5535500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4984800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>6544800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5877200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>5879200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5267700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>6554300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5479900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5533300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>5051300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>6009100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>5037800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>5214900</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1152,8 +1164,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1256,8 +1269,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1360,8 +1376,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1386,44 +1405,44 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>47900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-13000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>28300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>176000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>55000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-428000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-245700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-853500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>256500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>325700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-2389500</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1464,8 +1483,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1490,8 +1512,8 @@
       <c r="J15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1568,8 +1590,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1603,8 +1628,9 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1629,86 +1655,89 @@
       <c r="J17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3">
         <v>17720900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16855000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16529600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17866000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16128100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16051500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16195900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>17381500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15523600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>16243500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10711800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>19442200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>17987000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>18526400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>17479100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>23806000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>19835200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>19783000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>18341400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>22188700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>19221300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>19132200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>17689700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>21707800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>18186600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>18780900</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1733,86 +1762,89 @@
       <c r="J18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="3">
         <v>1392400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1308600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>791000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1509100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1143100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1722800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1204700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2117400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>741300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>628000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2887400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1905200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1352200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1588200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1139400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2118400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1793100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1824900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1346700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2170300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1548600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1549500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1191800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1735100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1021800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>939800</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1849,8 +1881,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1875,86 +1908,89 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>-53700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>80400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-212100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>175400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>91000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>150500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>69100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>373000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>149700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-235800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>47600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-725600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3452500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-545700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>577900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-53600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2174600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-175700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>335400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-583700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>82700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-132600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>132400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-702400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>286900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1979,86 +2015,89 @@
       <c r="J21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="3">
         <v>2216000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2286300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1534400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2630100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2160100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2825900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2236100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3486900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1809100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1384600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3774700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2207500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1110500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2001500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2665100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2999300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>481600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2478000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2501800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2422700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2464400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2253700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2112600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1868900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2102600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1987900</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2083,86 +2122,89 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
         <v>98600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>77700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>62500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>50500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>44600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>47300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>47400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>40900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>50200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>45100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>37200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>50600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>57400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>58200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>51300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>49200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>54300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>47100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>41700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>45400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>48500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>47200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>44600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>38100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>42000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>41800</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2187,86 +2229,89 @@
       <c r="J23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="3">
         <v>1240200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1311300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>516300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1634000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1189500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1825900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1226400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2449500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>840800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>347000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2897700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1129000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2157700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>984300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1665900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2015600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-435700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1602100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1640400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1541300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1582800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1369600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1279600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>994600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1266600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>926100</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2291,86 +2336,89 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3">
         <v>295800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>330100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>199200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>580700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>174000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>185900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>219800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1000000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>347100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>186800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>962900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>762200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1147100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>454200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>377600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>469000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>422800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>407300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>444600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>137800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>394200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>340500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>318200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>339400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>295300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>179000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2473,8 +2521,11 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2499,86 +2550,89 @@
       <c r="J26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="3">
         <v>944400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>981200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>317100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1053300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1015600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1640000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1006600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1449500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>493700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>160200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1934800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>366800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1010700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>530100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1288300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1546600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-858600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1194900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1195800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1403500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1188600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1029200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>961500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>655200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>971300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>747200</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2603,86 +2657,89 @@
       <c r="J27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3">
         <v>850000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>863600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>250400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>881000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>881700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1443500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>898400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1373600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>418700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>217000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1907200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>291100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1218500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>637600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1105700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1390100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1038100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>907000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>903300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1089500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>873200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>784200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>679200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>399800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>697700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>509700</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2785,8 +2842,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2811,8 +2871,8 @@
       <c r="J29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2839,58 +2899,61 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>-2700</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-2900</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-5200</v>
-      </c>
-      <c r="W29" s="3">
-        <v>-3600</v>
       </c>
       <c r="X29" s="3">
         <v>-3600</v>
       </c>
       <c r="Y29" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-45500</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-91800</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>53400</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-145700</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>12400</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-10900</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-600</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-45100</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-7900</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2993,8 +3056,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3097,8 +3163,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3123,86 +3192,89 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>53700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-80400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>212100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-175400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-91000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-150500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-69100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-373000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-149700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>235800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-47600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>725600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3452500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>545700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-577900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>53600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2174600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>175700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-335400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>583700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-82700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>132600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-132400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>702400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-286900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-28100</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3227,86 +3299,89 @@
       <c r="J33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3">
         <v>850000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>863600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>250400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>881000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>881700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1443500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>898400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1373600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>418700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>214300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1904300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>285900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1222100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>634000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1102000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1344600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1041900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>815200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>956700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>943800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>885600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>773300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>678600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>354800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>689800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3409,8 +3484,11 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3435,195 +3513,201 @@
       <c r="J35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="3">
         <v>850000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>863600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>250400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>881000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>881700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1443500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>898400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1373600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>418700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>214300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1904300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>285900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1222100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>634000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1102000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1344600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1041900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>815200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>956700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>943800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>885600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>773300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>678600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>354800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>689800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3660,8 +3744,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3698,944 +3783,972 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6419600</v>
+      </c>
+      <c r="E41" s="3">
         <v>5544100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5254200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4663400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6131400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6064700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6400700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6268400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5961200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5525200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7274400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6433000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6802700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6351800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8540600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7202600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6723400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5919500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>15789700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7156600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6326500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7735200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7635500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7761000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6690600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7669800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>7402900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6309600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>7334400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6944300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>7349700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6787700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>6771500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>7553100</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2055600</v>
+      </c>
+      <c r="E42" s="3">
         <v>2132100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2041900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2190200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2076500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2173600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2782200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2609700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1934400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2124500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2780300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2498700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2058500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2439100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2416300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2326600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2238300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2240900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2179300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2466400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2925600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2532000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2600300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2731800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>3037900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2792200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>3453500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>3374800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2939900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2708500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>3501600</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI42" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ42" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK42" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>20901000</v>
+      </c>
+      <c r="E43" s="3">
         <v>21499500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>19625100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>19776600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>19301700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>20051500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>18958000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>21627200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>18238600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>17864700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>18629400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>19774900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>18424400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>18472800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>18322300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>19387400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>17315500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>17898000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>14873600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>19912400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>19995800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>19820500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>19347400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>23063400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>20887500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>20792200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>19477900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>22612800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>20017900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>21216900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>19871600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>21957800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>19728100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>25974400</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10979900</v>
+      </c>
+      <c r="E44" s="3">
         <v>11216400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10637800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>9987400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>11355000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>12479600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12652100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12383500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12515200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12670200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>15703200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>13561700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>13883600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>13376400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>13211400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>11722600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>12228700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>12212600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>12348200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>12412700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>14707900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>13615300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>13569800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>13038500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>14975900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>13820200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>13141900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>12432100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>14097600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>12782800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>12369500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>10873800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>12655400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>11737600</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2714200</v>
+      </c>
+      <c r="E45" s="3">
         <v>2523100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2600200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2089100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2521500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2297100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2444000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1708800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10609100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1898400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2040100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1551800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2556900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2070600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1818300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1498800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1681100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1832800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4113500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4018800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6546100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2042700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2117200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1799400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2361700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2166700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2156900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1842900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2258300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2187200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2212300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4753800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>4708100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>4654500</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>43070200</v>
+      </c>
+      <c r="E46" s="3">
         <v>42915100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>40159200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>38706800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>41386200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>43066500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>43236900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>44597600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>49258500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>40083000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>46427400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>43820200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>43726000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>42710700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>44308900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>42138000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>40187000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>40103800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>49304300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>45967000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>50502000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>45745800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>45270100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>48394000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>47953500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>47241100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>45633100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>46572300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>46648100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>45839800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>45304800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>44373100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>43863100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>49919500</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7486300</v>
+      </c>
+      <c r="E47" s="3">
         <v>11077300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7423800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8654800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>11988300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>10202700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10289700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8957900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6823800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7123800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6934300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6613500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6824000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7105800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7097900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7135600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>6667500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7063000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7699800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8113000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>9074100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12086600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>11909900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12423900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12268900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>12733300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>12636400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>13196900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>13425300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>13164700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>12783700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>12515200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>13097300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>16937400</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8169700</v>
+      </c>
+      <c r="E48" s="3">
         <v>8514000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7963900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8078000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8325500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11872500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12155500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12791800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12067500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13491700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17274800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>16459900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16629700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17237600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17652400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17079000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>15682000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>16694300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>16517900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19076400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20106600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19703700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19759100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>18803700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>18389900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20003800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19357100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>19208400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>19232200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>18881700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>18246800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>17725900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>17662900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>20069600</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>25198800</v>
+      </c>
+      <c r="E49" s="3">
         <v>25224100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>24923100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>23473100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>23948700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>25076700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>25305000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>25652100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>23738800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>23826100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>25113500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>22647900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>22308700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>23106900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>15617200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>15073600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>14192100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>15141300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9038200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9829500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10478300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8381100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8770800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9225800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>9348100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9968300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9621800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>9531500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>10139000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>10111900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>8483100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>8153300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>8193600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>8309100</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4738,8 +4851,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4842,20 +4958,23 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3">
+        <v>3001600</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3">
         <v>2857700</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4868,86 +4987,89 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3">
         <v>2406600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2354000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2667900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2671500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2733700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2700300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2786600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2610500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3472000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3696300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4109000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4498100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3502200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3405900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3442200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3664200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3546200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3512500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3057200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2854500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2728600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2784700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2792500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2951400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2691400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>9247200</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5050,112 +5172,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>86926700</v>
+      </c>
+      <c r="E54" s="3">
         <v>87730500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>83327700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>80799200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>85648700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>90218400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>90987100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>94042300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>94295100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>86878700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>98418000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>92213000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>92222000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>92861400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>87463100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>84036700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>80200700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>82698800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>86669200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>87484000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>93663200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>89323100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>89152000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>92511500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>91506600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>93459000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>90305500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>91363700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>92173200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>90782700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>87610900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>85718900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>85508400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>104482800</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5192,8 +5320,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5230,632 +5359,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9868700</v>
+      </c>
+      <c r="E57" s="3">
         <v>10207600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9432200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9253900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9523100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10553000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10855800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11648600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10499200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10878200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12105000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11650800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10957900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10787600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11144000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10748100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9809900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9797100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9368400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11194600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11828400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11275400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>11927900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>13511800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12785400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12738900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12718200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>13894300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>13397100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>12889700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>12346100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>12437800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>11908500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>11654900</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6567900</v>
+      </c>
+      <c r="E58" s="3">
         <v>3935800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3847100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1489600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4160100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6929500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7514300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6917000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12408500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8625500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12483000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10428400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>13041400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>12086700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6548900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4899400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>9077200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>12284200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>12318200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3652100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>6529700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5029300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4536800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2847300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5429700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4508500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4229900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2157200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3742700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3865500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>4202800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3429100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3937900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>12512300</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>19451800</v>
+      </c>
+      <c r="E59" s="3">
         <v>18753000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>18295400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16396900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16765700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15008200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15378500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14873600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>20275000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17563000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17017900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>16791900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15810000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16046600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16697900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16944700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15956700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>16120700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>17854300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>18042600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>19847800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>16505800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>16298200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>18290400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>17134300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>17568000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>16763300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>18258800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>17693700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>17628000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>16719600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>17137200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>16265100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>16240700</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>39848400</v>
+      </c>
+      <c r="E60" s="3">
         <v>37169400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>35000400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>31751700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>34400400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>37330200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>37806500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>38862700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>43182600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>37066800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>41605900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>38871000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>39809300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>38920800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>34390800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>32592200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>34843800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>38202100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>39540800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>32889300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>38205800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>32810500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>32762900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>34649400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>35349400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>34815400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>33711400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>34310400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>34833500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>34383200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>33268500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>33004000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>32111400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>40407900</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4829600</v>
+      </c>
+      <c r="E61" s="3">
         <v>6737400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6196700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6311900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8287000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8977200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9217300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9732900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9280200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9269000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10837200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10333000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11118900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11804800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12061200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12097900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9983800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7275300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8505400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9431100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7705500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7720200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8081000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6808600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7076600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6652500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6755400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7337400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7529400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7629600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7261000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7007400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7631500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>19851800</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2344700</v>
+      </c>
+      <c r="E62" s="3">
         <v>2470900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2306900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1626500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2488200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2715000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2701400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1710500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5121100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5332800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7899900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7450000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7621300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7886600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7913300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7737800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8641200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>9389500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7054800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7573600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8011800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7935100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7819600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8631100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8503900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8634300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8575800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>8930400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>9587400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9519400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9427600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9367200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9692000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>9942400</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5958,8 +6106,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6062,8 +6213,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6166,112 +6320,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>48639600</v>
+      </c>
+      <c r="E66" s="3">
         <v>48253800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>45155800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>42059300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>47174600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>51214100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>51988900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>53905300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>62173500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>55928700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>67291300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>63383200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>65084500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>65283900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>61047200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>59040900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>58736000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>59983500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>60767600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>59644500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>64242700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>58617400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>59031200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>61157900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>61843400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>61415400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>59788500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>61730400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>63059800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>62347900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>60372500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>59400900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>59920500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>81205500</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6308,8 +6468,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6412,8 +6573,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6516,8 +6680,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6620,8 +6787,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6724,112 +6894,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>27507600</v>
+      </c>
+      <c r="E72" s="3">
         <v>29895400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>25894400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>27005600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>27270100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>25325900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>25192600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>27360800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>23149500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>21426100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>21664600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>21232900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>20987100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>21520400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>20473000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>19218200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>18264800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>19425200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>21120100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>20229600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>20621300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>22424100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>21711000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>21983700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>20149100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>21201100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>19948300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>19032800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>18040300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>17443200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>16664700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>15909000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>15530900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>15048500</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6932,8 +7108,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7036,8 +7215,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7140,112 +7322,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>37201300</v>
+      </c>
+      <c r="E76" s="3">
         <v>38400200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>37248700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>37709200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>37447400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>36259600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>36277000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>37182800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>32121600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>30949900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>31126700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>28829800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>27137600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>27577500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>26415900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>24995800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>21464600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>22715300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>25901600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>27839500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>29420500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>30705700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>30120900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>31353600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>29663100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>32043600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>30517000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>29633300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>29113400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>28434800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>27238300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>26318000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>25587900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>23277400</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7348,117 +7536,123 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7483,86 +7677,89 @@
       <c r="J81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L81" s="3">
         <v>850000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>863600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>250400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>881000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>881700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1443500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>898400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1373600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>418700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>214300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1904300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>285900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1222100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>634000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1102000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1344600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1041900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>815200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>956700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>943800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>885600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>773300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>678600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>354800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>689800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7599,112 +7796,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>734300</v>
+      </c>
+      <c r="E83" s="3">
         <v>841200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>839300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>905200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>937000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>972000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1043300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>605400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>877300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>897300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>955600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>945700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>926000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>952600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>962300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>996500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>918100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>992500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>839800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1027900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>989800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>959000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>947800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>934400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>863000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>828800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>819700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>836100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>833100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>836900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>788400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>836200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>793900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1019900</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7807,8 +8008,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7911,8 +8115,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8015,8 +8222,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8119,8 +8329,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8223,112 +8436,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1875200</v>
+      </c>
+      <c r="E89" s="3">
         <v>1257900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>889700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2735400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1602800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1330800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>817200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3362200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1039700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>813400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>715500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3139300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>657400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>175900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1007500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2600100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1553300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>472800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1311900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2229600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>930700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1165500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>722400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3917700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-91000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>721300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1221300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2295800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1760400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1369900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1147500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2221100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>835800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1773600</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8365,112 +8584,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-328500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-348900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-254400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-476000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-314200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-420500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-372000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-421200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-96150000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-108272000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100755000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-134149000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100626000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-107573000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-488900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-628300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-384800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-471300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-453200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-794100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-595900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-811800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-723700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-857900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-898800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-883000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-934700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-5500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-11900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1277100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-889100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2139000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8573,8 +8796,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8677,112 +8903,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-697800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-540900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1457100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>267500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-437800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-471500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-275700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2229200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-517900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-485400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-140400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-524200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6808900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-51800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>2178300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-455900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-8267800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>3049100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-297800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2595800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-937000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-962900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>121300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-311700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-357900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-944800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1447200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-721200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1173700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-945800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1217900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>141000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1198700</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8819,20 +9051,21 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
+        <v>615100</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
         <v>576300</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G96" s="3" t="s">
         <v>8</v>
       </c>
@@ -8845,86 +9078,89 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>-471300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>1600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-424400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-399200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-391300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-355300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>1100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-412600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-397200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>1500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-442700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-365100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-351500</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>400</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-305900</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-305900</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>400</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-257400</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9027,8 +9263,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9131,8 +9370,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9235,316 +9477,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-115700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-662500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1205700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4291700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1287100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1115800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-191300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6635700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>551100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2261600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>107900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3369100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>436900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4584400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>78600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4395900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>9900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-723400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4492600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-740400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>152600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-25700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>668100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-3116400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-529700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-258300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>797900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1618500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-748700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-709100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>170400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-864900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2288400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>989900</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-172600</v>
+      </c>
+      <c r="E101" s="3">
         <v>125300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>287200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>96300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-438600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>97000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>443900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>283000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-410600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>89500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>406600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>228200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>180400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>22500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>39600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>316900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>46100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>18000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>7000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-152900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>171200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-128000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-189700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>27200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-170600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-254800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>99500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>107600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>59800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-122100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>530100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-69300</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1367700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-355700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>869400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1050800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-294700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-131300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>637400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-948000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>662300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1360700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>744500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-141900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>750500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2026200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1073900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>699400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1153400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-8500500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>8860600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1038400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1341400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>74800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>237900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>949900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1103100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>104000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1058400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1024800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>390000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-405400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>431900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>16200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-781600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1495500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HTHIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HTHIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
   <si>
     <t>HTHIY</t>
   </si>
@@ -656,157 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -834,86 +838,89 @@
       <c r="K8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="3">
         <v>19113300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18163600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17320600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19375100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17271200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>17774300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>17400700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>19498900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>16264900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16871400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>13599200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>21347400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>19339200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>20114600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>18618500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>25924400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>21628300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>21607900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>19688000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>24359100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>20770000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>20681700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>18881600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>23443000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>19208300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>19720700</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -941,86 +948,89 @@
       <c r="K9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3">
         <v>14358800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13699200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13172300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14433800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12948800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13386900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13161400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>14759900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12099600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>12635200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>10060500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>15555900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>14178700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>14579000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>13633700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>19379600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>15751100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>15728800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>14420300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>17804700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>15290000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>15148400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>13830300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>17433900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>14170500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>14505800</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1048,86 +1058,89 @@
       <c r="K10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="3">
         <v>4754500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4464400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4148300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4941300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4322400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4387400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4239200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4739000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4165300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4236200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3538700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5791400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5160500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5535500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4984800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>6544800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>5877200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5879200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5267700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>6554300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5479900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>5533300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>5051300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>6009100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>5037800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>5214900</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1165,8 +1178,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1272,8 +1286,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1379,8 +1396,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1408,44 +1428,44 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>47900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-13000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>28300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>176000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>55000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-428000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-245700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-853500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>256500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>325700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-2389500</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1486,8 +1506,11 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1515,8 +1538,8 @@
       <c r="K15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1593,8 +1616,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1629,8 +1655,9 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1658,86 +1685,89 @@
       <c r="K17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="3">
         <v>17720900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16855000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16529600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17866000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16128100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16051500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>16195900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>17381500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15523600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>16243500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10711800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>19442200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>17987000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>18526400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>17479100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>23806000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>19835200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>19783000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>18341400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>22188700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>19221300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>19132200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>17689700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>21707800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>18186600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>18780900</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1765,86 +1795,89 @@
       <c r="K18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="3">
         <v>1392400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1308600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>791000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1509100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1143100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1722800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1204700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2117400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>741300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>628000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2887400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1905200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1352200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1588200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1139400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2118400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1793100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1824900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1346700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2170300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1548600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1549500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1191800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1735100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1021800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>939800</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1882,8 +1915,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1911,86 +1945,89 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>-53700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>80400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-212100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>175400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>91000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>150500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>69100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>373000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>149700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-235800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>47600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-725600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3452500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-545700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>577900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-53600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2174600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-175700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>335400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-583700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>82700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-132600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>132400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-702400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>286900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2018,86 +2055,89 @@
       <c r="K21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="3">
         <v>2216000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2286300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1534400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2630100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2160100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2825900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2236100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3486900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1809100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1384600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3774700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2207500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1110500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2001500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2665100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2999300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>481600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2478000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2501800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2422700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2464400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2253700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2112600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1868900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2102600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1987900</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2125,86 +2165,89 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
         <v>98600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>77700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>62500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>50500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>44600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>47300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>47400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>40900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>50200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>45100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>37200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>50600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>57400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>58200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>51300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>49200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>54300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>47100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>41700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>45400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>48500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>47200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>44600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>38100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>42000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>41800</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2232,86 +2275,89 @@
       <c r="K23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="3">
         <v>1240200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1311300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>516300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1634000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1189500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1825900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1226400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2449500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>840800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>347000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2897700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1129000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2157700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>984300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1665900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2015600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-435700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1602100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1640400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1541300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1582800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1369600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1279600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>994600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1266600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>926100</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2339,86 +2385,89 @@
       <c r="K24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3">
         <v>295800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>330100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>199200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>580700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>174000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>185900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>219800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1000000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>347100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>186800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>962900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>762200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-1147100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>454200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>377600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>469000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>422800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>407300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>444600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>137800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>394200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>340500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>318200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>339400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>295300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>179000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2524,8 +2573,11 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2553,86 +2605,89 @@
       <c r="K26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="3">
         <v>944400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>981200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>317100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1053300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1015600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1640000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1006600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1449500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>493700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>160200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1934800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>366800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1010700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>530100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1288300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1546600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-858600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1194900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1195800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1403500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1188600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1029200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>961500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>655200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>971300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>747200</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2660,86 +2715,89 @@
       <c r="K27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="3">
         <v>850000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>863600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>250400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>881000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>881700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1443500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>898400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1373600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>418700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>217000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1907200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>291100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1218500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>637600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1105700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1390100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1038100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>907000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>903300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1089500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>873200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>784200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>679200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>399800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>697700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>509700</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2845,8 +2903,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2874,8 +2935,8 @@
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2902,58 +2963,61 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-2700</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-2900</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-5200</v>
-      </c>
-      <c r="X29" s="3">
-        <v>-3600</v>
       </c>
       <c r="Y29" s="3">
         <v>-3600</v>
       </c>
       <c r="Z29" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-45500</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-91800</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>53400</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-145700</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>12400</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-10900</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-600</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-45100</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-7900</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3059,8 +3123,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3166,8 +3233,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3195,86 +3265,89 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>53700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-80400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>212100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-175400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-91000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-150500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-69100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-373000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-149700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>235800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-47600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>725600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3452500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>545700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-577900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>53600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2174600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>175700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-335400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>583700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-82700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>132600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-132400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>702400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-286900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-28100</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3302,86 +3375,89 @@
       <c r="K33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M33" s="3">
         <v>850000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>863600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>250400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>881000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>881700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1443500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>898400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1373600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>418700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>214300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1904300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>285900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1222100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>634000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1102000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1344600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1041900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>815200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>956700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>943800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>885600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>773300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>678600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>354800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>689800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3487,8 +3563,11 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3516,198 +3595,204 @@
       <c r="K35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="3">
         <v>850000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>863600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>250400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>881000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>881700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1443500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>898400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1373600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>418700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>214300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1904300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>285900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1222100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>634000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1102000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1344600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1041900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>815200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>956700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>943800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>885600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>773300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>678600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>354800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>689800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3745,8 +3830,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3784,971 +3870,999 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5784700</v>
+      </c>
+      <c r="E41" s="3">
         <v>6419600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5544100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5254200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4663400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6131400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6064700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6400700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6268400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5961200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5525200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7274400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6433000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6802700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6351800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8540600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7202600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6723400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5919500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>15789700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7156600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6326500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7735200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7635500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7761000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6690600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>7669800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>7402900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6309600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7334400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6944300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>7349700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>6787700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>6771500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>7553100</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2126400</v>
+      </c>
+      <c r="E42" s="3">
         <v>2055600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2132100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2041900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2190200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2076500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2173600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2782200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2609700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1934400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2124500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2780300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2498700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2058500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2439100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2416300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2326600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2238300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2240900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2179300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2466400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2925600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2532000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2600300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2731800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>3037900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2792200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>3453500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>3374800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2939900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>2708500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>3501600</v>
       </c>
-      <c r="AI42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ42" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK42" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL42" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>23348200</v>
+      </c>
+      <c r="E43" s="3">
         <v>20901000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>21499500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>19625100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>19776600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>19301700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>20051500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>18958000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>21627200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>18238600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>17864700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>18629400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>19774900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>18424400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>18472800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>18322300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>19387400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>17315500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>17898000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>14873600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>19912400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>19995800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>19820500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>19347400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>23063400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>20887500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>20792200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>19477900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>22612800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>20017900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>21216900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>19871600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>21957800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>19728100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>25974400</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10459500</v>
+      </c>
+      <c r="E44" s="3">
         <v>10979900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>11216400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>10637800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>9987400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>11355000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12479600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12652100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12383500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12515200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>12670200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>15703200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>13561700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>13883600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>13376400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>13211400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>11722600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>12228700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>12212600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>12348200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>12412700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>14707900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>13615300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>13569800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>13038500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>14975900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>13820200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>13141900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>12432100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>14097600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>12782800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>12369500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>10873800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>12655400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>11737600</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2341000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2714200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2523100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2600200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2089100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2521500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2297100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2444000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1708800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10609100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1898400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2040100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1551800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2556900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2070600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1818300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1498800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1681100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1832800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4113500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4018800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6546100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2042700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2117200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1799400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2361700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2166700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2156900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1842900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2258300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2187200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2212300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>4753800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>4708100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>4654500</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>44059600</v>
+      </c>
+      <c r="E46" s="3">
         <v>43070200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>42915100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>40159200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>38706800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>41386200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>43066500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>43236900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>44597600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>49258500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>40083000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>46427400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>43820200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>43726000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>42710700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>44308900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>42138000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>40187000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>40103800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>49304300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>45967000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>50502000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>45745800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>45270100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>48394000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>47953500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>47241100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>45633100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>46572300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>46648100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>45839800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>45304800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>44373100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>43863100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>49919500</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7918600</v>
+      </c>
+      <c r="E47" s="3">
         <v>7486300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>11077300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7423800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8654800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>11988300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10202700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10289700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8957900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6823800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7123800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6934300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6613500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6824000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7105800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7097900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7135600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>6667500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7063000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7699800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8113000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>9074100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12086600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>11909900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12423900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>12268900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>12733300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>12636400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>13196900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>13425300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>13164700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>12783700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>12515200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>13097300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>16937400</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8958600</v>
+      </c>
+      <c r="E48" s="3">
         <v>8169700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8514000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7963900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8078000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8325500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11872500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12155500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12791800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12067500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13491700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17274800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16459900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16629700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17237600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17652400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>17079000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>15682000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>16694300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>16517900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19076400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20106600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19703700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19759100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>18803700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>18389900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>20003800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>19357100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>19208400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>19232200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>18881700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>18246800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>17725900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>17662900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>20069600</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>24620200</v>
+      </c>
+      <c r="E49" s="3">
         <v>25198800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>25224100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>24923100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>23473100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>23948700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>25076700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>25305000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>25652100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>23738800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>23826100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>25113500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>22647900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>22308700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>23106900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>15617200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>15073600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>14192100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>15141300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9038200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9829500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10478300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8381100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8770800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>9225800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9348100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9968300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>9621800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>9531500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>10139000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>10111900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>8483100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>8153300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>8193600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>8309100</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4854,8 +4968,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4961,23 +5078,26 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3157400</v>
+      </c>
+      <c r="E52" s="3">
         <v>3001600</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3">
         <v>2857700</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4990,86 +5110,89 @@
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="3">
         <v>2406600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2354000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2667900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2671500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2733700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2700300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2786600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2610500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3472000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3696300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4109000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4498100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3502200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3405900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3442200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3664200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3546200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3512500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3057200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2854500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2728600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2784700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2792500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2951400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2691400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>9247200</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5175,115 +5298,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>88714500</v>
+      </c>
+      <c r="E54" s="3">
         <v>86926700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>87730500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>83327700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>80799200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>85648700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>90218400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>90987100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>94042300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>94295100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>86878700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>98418000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>92213000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>92222000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>92861400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>87463100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>84036700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>80200700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>82698800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>86669200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>87484000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>93663200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>89323100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>89152000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>92511500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>91506600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>93459000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>90305500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>91363700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>92173200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>90782700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>87610900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>85718900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>85508400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>104482800</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5321,8 +5450,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5360,650 +5490,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10502700</v>
+      </c>
+      <c r="E57" s="3">
         <v>9868700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10207600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9432200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9253900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9523100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10553000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10855800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11648600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10499200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10878200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12105000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11650800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10957900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10787600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>11144000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10748100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9809900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9797100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9368400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11194600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11828400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>11275400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11927900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>13511800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12785400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12738900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12718200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>13894300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>13397100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>12889700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>12346100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>12437800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>11908500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>11654900</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2951400</v>
+      </c>
+      <c r="E58" s="3">
         <v>6567900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3935800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3847100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1489600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4160100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6929500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7514300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6917000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12408500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8625500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12483000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10428400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>13041400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>12086700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6548900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4899400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>9077200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>12284200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>12318200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3652100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>6529700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5029300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4536800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2847300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>5429700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4508500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4229900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2157200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3742700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3865500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>4202800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3429100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3937900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>12512300</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>21081000</v>
+      </c>
+      <c r="E59" s="3">
         <v>19451800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>18753000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>18295400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16396900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16765700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15008200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15378500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14873600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>20275000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17563000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17017900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16791900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15810000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16046600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16697900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>16944700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>15956700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>16120700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>17854300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>18042600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>19847800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>16505800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>16298200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>18290400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>17134300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>17568000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>16763300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>18258800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>17693700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>17628000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>16719600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>17137200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>16265100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>16240700</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>39451900</v>
+      </c>
+      <c r="E60" s="3">
         <v>39848400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>37169400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>35000400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>31751700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34400400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>37330200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>37806500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>38862700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>43182600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>37066800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>41605900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>38871000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>39809300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>38920800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>34390800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>32592200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>34843800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>38202100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>39540800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>32889300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>38205800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>32810500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>32762900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>34649400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>35349400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>34815400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>33711400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>34310400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>34833500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>34383200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>33268500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>33004000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>32111400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>40407900</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5102900</v>
+      </c>
+      <c r="E61" s="3">
         <v>4829600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6737400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6196700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6311900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8287000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8977200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9217300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9732900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9280200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9269000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10837200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10333000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11118900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11804800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12061200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>12097900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9983800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7275300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8505400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9431100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7705500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7720200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8081000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6808600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7076600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6652500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6755400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7337400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7529400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7629600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7261000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7007400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>7631500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>19851800</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2229800</v>
+      </c>
+      <c r="E62" s="3">
         <v>2344700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2470900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2306900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1626500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2488200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2715000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2701400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1710500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5121100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5332800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7899900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7450000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7621300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7886600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7913300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7737800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8641200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>9389500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7054800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7573600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8011800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7935100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7819600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8631100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8503900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8634300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>8575800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>8930400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9587400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9519400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9427600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9367200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>9692000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>9942400</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6109,8 +6258,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6216,8 +6368,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6323,115 +6478,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>48437300</v>
+      </c>
+      <c r="E66" s="3">
         <v>48639600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>48253800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>45155800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>42059300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>47174600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>51214100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>51988900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>53905300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>62173500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>55928700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>67291300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>63383200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>65084500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>65283900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>61047200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>59040900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>58736000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>59983500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>60767600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>59644500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>64242700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>58617400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>59031200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>61157900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>61843400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>61415400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>59788500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>61730400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>63059800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>62347900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>60372500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>59400900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>59920500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>81205500</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6469,8 +6630,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6576,8 +6738,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6683,8 +6848,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6790,8 +6958,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6897,115 +7068,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>29052200</v>
+      </c>
+      <c r="E72" s="3">
         <v>27507600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>29895400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>25894400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>27005600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>27270100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>25325900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>25192600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>27360800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>23149500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>21426100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>21664600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>21232900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>20987100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>21520400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>20473000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>19218200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>18264800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>19425200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>21120100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>20229600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>20621300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>22424100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>21711000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>21983700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>20149100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>21201100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>19948300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>19032800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>18040300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>17443200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>16664700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>15909000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>15530900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>15048500</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7111,8 +7288,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7218,8 +7398,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7325,115 +7508,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>39046200</v>
+      </c>
+      <c r="E76" s="3">
         <v>37201300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>38400200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>37248700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>37709200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>37447400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>36259600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>36277000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>37182800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>32121600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>30949900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>31126700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>28829800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>27137600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>27577500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>26415900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>24995800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>21464600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>22715300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>25901600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>27839500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>29420500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>30705700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>30120900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>31353600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>29663100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>32043600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>30517000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>29633300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>29113400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>28434800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>27238300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>26318000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>25587900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>23277400</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7539,120 +7728,126 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7680,86 +7875,89 @@
       <c r="K81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M81" s="3">
         <v>850000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>863600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>250400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>881000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>881700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1443500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>898400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1373600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>418700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>214300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1904300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>285900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1222100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>634000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1102000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1344600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1041900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>815200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>956700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>943800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>885600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>773300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>678600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>354800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>689800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7797,115 +7995,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>667800</v>
+      </c>
+      <c r="E83" s="3">
         <v>734300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>841200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>839300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>905200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>937000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>972000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1043300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>605400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>877300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>897300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>955600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>945700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>926000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>952600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>962300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>996500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>918100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>992500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>839800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1027900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>989800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>959000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>947800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>934400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>863000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>828800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>819700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>836100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>833100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>836900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>788400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>836200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>793900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1019900</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8011,8 +8213,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8118,8 +8323,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8225,8 +8433,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8332,8 +8543,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8439,115 +8653,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3700100</v>
+      </c>
+      <c r="E89" s="3">
         <v>1875200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1257900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>889700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2735400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1602800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1330800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>817200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3362200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1039700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>813400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>715500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3139300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>657400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>175900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1007500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2600100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1553300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>472800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1311900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2229600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>930700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1165500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>722400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3917700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-91000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>721300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1221300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2295800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1760400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1369900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1147500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2221100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>835800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1773600</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8585,115 +8805,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-696300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-328500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-348900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-254400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-476000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-314200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-420500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-372000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-421200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-96150000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-108272000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100755000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-134149000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100626000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-107573000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-488900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-628300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-384800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-471300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-453200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-794100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-595900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-811800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-723700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-857900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-898800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-883000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-934700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-11900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1277100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-889100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2139000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8799,8 +9023,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8906,115 +9133,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1015500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-697800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-540900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1457100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>267500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-437800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-471500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-275700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2229200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-517900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-485400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-140400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-524200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6808900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-51800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>2178300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-455900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-8267800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>3049100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-297800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2595800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-937000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-962900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>121300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-311700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-357900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-944800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1447200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-721200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1173700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-945800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1217900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>141000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1198700</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9052,23 +9285,24 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3">
         <v>615100</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3">
         <v>576300</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H96" s="3" t="s">
         <v>8</v>
       </c>
@@ -9081,86 +9315,89 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3">
         <v>-471300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>1600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-424400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-399200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-391300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-355300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>1100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-412600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-397200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>1500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-442700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>700</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-365100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-351500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-305900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-305900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>400</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-257400</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9266,8 +9503,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9373,8 +9613,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9480,325 +9723,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3372100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-115700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-662500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1205700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4291700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1287100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1115800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-191300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6635700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>551100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2261600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>107900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3369100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>436900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4584400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>78600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4395900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>9900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-723400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4492600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-740400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>152600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-25700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>668100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3116400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-529700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-258300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>797900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1618500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-748700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-709100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>170400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-864900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2288400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>989900</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>238000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-172600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>125300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>287200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>96300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-438600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>97000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>443900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>283000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-410600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>89500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>406600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>228200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>180400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>22500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>39600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>316900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>46100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>18000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>7000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-152900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>171200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-128000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-189700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>27200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-170600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-254800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>99500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>107600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>59800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-122100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>530100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-69300</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-955200</v>
+      </c>
+      <c r="E102" s="3">
         <v>1367700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-355700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>869400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1050800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-294700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-131300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>637400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-948000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>662300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1360700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>744500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-141900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>750500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2026200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1073900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>699400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1153400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-8500500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>8860600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1038400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1341400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>74800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>237900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>949900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1103100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>104000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1058400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1024800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>390000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-405400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>431900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>16200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-781600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1495500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HTHIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HTHIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="92">
   <si>
     <t>HTHIY</t>
   </si>
@@ -656,161 +656,165 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="19" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -841,86 +845,89 @@
       <c r="L8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="3">
         <v>19113300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18163600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17320600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19375100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>17271200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>17774300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>17400700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>19498900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16264900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16871400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>13599200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>21347400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>19339200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>20114600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>18618500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>25924400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>21628300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>21607900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>19688000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>24359100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>20770000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>20681700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>18881600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>23443000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>19208300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>19720700</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -951,86 +958,89 @@
       <c r="L9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="3">
         <v>14358800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13699200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13172300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>14433800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12948800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13386900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13161400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14759900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>12099600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>12635200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>10060500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>15555900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>14178700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>14579000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>13633700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>19379600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>15751100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>15728800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>14420300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>17804700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>15290000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>15148400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>13830300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>17433900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>14170500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>14505800</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1061,86 +1071,89 @@
       <c r="L10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="3">
         <v>4754500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4464400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4148300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4941300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4322400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4387400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4239200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4739000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4165300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4236200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3538700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5791400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5160500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5535500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4984800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>6544800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5877200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5879200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5267700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>6554300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>5479900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>5533300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>5051300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>6009100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>5037800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>5214900</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1179,8 +1192,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1289,8 +1303,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1399,8 +1416,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1431,44 +1451,44 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>47900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-13000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>28300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>176000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>55000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-428000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-245700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-853500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>256500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>325700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-2389500</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1509,8 +1529,11 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1541,8 +1564,8 @@
       <c r="L15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1619,8 +1642,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1656,8 +1682,9 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1688,86 +1715,89 @@
       <c r="L17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="3">
         <v>17720900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16855000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16529600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17866000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16128100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>16051500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>16195900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>17381500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15523600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>16243500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10711800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>19442200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>17987000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>18526400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>17479100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>23806000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>19835200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>19783000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>18341400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>22188700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>19221300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>19132200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>17689700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>21707800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>18186600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>18780900</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1798,86 +1828,89 @@
       <c r="L18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="3">
         <v>1392400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1308600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>791000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1509100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1143100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1722800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1204700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2117400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>741300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>628000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2887400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1905200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1352200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1588200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1139400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2118400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1793100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1824900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1346700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2170300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1548600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1549500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1191800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1735100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1021800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>939800</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1916,8 +1949,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1948,86 +1982,89 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>-53700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>80400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-212100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>175400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>91000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>150500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>69100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>373000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>149700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-235800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>47600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-725600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3452500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-545700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>577900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-53600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2174600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-175700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>335400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-583700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>82700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-132600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>132400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-702400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>286900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2058,86 +2095,89 @@
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3">
         <v>2216000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2286300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1534400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2630100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2160100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2825900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2236100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3486900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1809100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1384600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3774700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2207500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1110500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2001500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2665100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2999300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>481600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2478000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2501800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2422700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2464400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2253700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2112600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1868900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2102600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1987900</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2168,86 +2208,89 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
         <v>98600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>77700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>62500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>50500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>44600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>47300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>47400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>40900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>50200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>45100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>37200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>50600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>57400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>58200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>51300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>49200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>54300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>47100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>41700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>45400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>48500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>47200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>44600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>38100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>42000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>41800</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2278,86 +2321,89 @@
       <c r="L23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="3">
         <v>1240200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1311300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>516300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1634000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1189500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1825900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1226400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2449500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>840800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>347000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2897700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1129000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2157700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>984300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1665900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2015600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-435700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1602100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1640400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1541300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1582800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1369600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1279600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>994600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1266600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>926100</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2388,86 +2434,89 @@
       <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="3">
         <v>295800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>330100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>199200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>580700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>174000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>185900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>219800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1000000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>347100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>186800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>962900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>762200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1147100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>454200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>377600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>469000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>422800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>407300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>444600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>137800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>394200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>340500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>318200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>339400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>295300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>179000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2576,8 +2625,11 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2608,86 +2660,89 @@
       <c r="L26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="3">
         <v>944400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>981200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>317100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1053300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1015600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1640000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1006600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1449500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>493700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>160200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1934800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>366800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1010700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>530100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1288300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1546600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-858600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1194900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1195800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1403500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1188600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1029200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>961500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>655200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>971300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>747200</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2718,86 +2773,89 @@
       <c r="L27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="3">
         <v>850000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>863600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>250400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>881000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>881700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1443500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>898400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1373600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>418700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>217000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1907200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>291100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1218500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>637600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1105700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1390100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1038100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>907000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>903300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1089500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>873200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>784200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>679200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>399800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>697700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>509700</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2906,8 +2964,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2938,8 +2999,8 @@
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -2966,58 +3027,61 @@
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>-2700</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-2900</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-5200</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>-3600</v>
       </c>
       <c r="Z29" s="3">
         <v>-3600</v>
       </c>
       <c r="AA29" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-45500</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-91800</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>53400</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-145700</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>12400</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-10900</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-45100</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-7900</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3126,8 +3190,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3236,8 +3303,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3268,86 +3338,89 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>53700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-80400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>212100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-175400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-91000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-150500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-69100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-373000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-149700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>235800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-47600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>725600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3452500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>545700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-577900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>53600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2174600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>175700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-335400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>583700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-82700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>132600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-132400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>702400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-286900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-28100</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3378,86 +3451,89 @@
       <c r="L33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N33" s="3">
         <v>850000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>863600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>250400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>881000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>881700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1443500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>898400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1373600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>418700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>214300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1904300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>285900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1222100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>634000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1102000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1344600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1041900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>815200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>956700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>943800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>885600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>773300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>678600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>354800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>689800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3566,8 +3642,11 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3598,201 +3677,207 @@
       <c r="L35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N35" s="3">
         <v>850000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>863600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>250400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>881000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>881700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1443500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>898400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1373600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>418700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>214300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1904300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>285900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1222100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>634000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1102000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1344600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1041900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>815200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>956700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>943800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>885600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>773300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>678600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>354800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>689800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3831,8 +3916,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3871,998 +3957,1026 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3">
         <v>5784700</v>
       </c>
-      <c r="E41" s="3">
-        <v>6419600</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="F41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" s="3">
         <v>5544100</v>
       </c>
-      <c r="G41" s="3">
-        <v>5254200</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="3">
         <v>4663400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6131400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6064700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6400700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6268400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5961200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5525200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7274400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6433000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6802700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6351800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8540600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7202600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6723400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5919500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>15789700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7156600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6326500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7735200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7635500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7761000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6690600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>7669800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>7402900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6309600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>7334400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6944300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>7349700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>6787700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>6771500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>7553100</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>2126400</v>
       </c>
-      <c r="E42" s="3">
-        <v>2055600</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>2132100</v>
       </c>
-      <c r="G42" s="3">
-        <v>2041900</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>2190200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2076500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2173600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2782200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2609700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1934400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2124500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2780300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2498700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2058500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2439100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2416300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2326600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2238300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2240900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2179300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2466400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2925600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2532000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2600300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2731800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>3037900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2792200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>3453500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>3374800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>2939900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>2708500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>3501600</v>
       </c>
-      <c r="AJ42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK42" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL42" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM42" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
         <v>23348200</v>
       </c>
-      <c r="E43" s="3">
-        <v>20901000</v>
-      </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="3">
         <v>21499500</v>
       </c>
-      <c r="G43" s="3">
-        <v>19625100</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3">
         <v>19776600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>19301700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>20051500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>18958000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>21627200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>18238600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>17864700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>18629400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>19774900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>18424400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>18472800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>18322300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>19387400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>17315500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>17898000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>14873600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>19912400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>19995800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>19820500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>19347400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>23063400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>20887500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>20792200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>19477900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>22612800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>20017900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>21216900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>19871600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>21957800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>19728100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>25974400</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3">
         <v>10459500</v>
       </c>
-      <c r="E44" s="3">
-        <v>10979900</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3">
         <v>11216400</v>
       </c>
-      <c r="G44" s="3">
-        <v>10637800</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3">
         <v>9987400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>11355000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12479600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12652100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12383500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>12515200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>12670200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>15703200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>13561700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>13883600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>13376400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>13211400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>11722600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>12228700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>12212600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>12348200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>12412700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>14707900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>13615300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>13569800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>13038500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>14975900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>13820200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>13141900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>12432100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>14097600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>12782800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>12369500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>10873800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>12655400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>11737600</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>2341000</v>
       </c>
-      <c r="E45" s="3">
-        <v>2714200</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>2523100</v>
       </c>
-      <c r="G45" s="3">
-        <v>2600200</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3">
         <v>2089100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2521500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2297100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2444000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1708800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10609100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1898400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2040100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1551800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2556900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2070600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1818300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1498800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1681100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1832800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4113500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4018800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6546100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2042700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2117200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1799400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2361700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2166700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2156900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1842900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2258300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2187200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2212300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>4753800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>4708100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>4654500</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3">
         <v>44059600</v>
       </c>
-      <c r="E46" s="3">
-        <v>43070200</v>
-      </c>
-      <c r="F46" s="3">
+      <c r="F46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="3">
         <v>42915100</v>
       </c>
-      <c r="G46" s="3">
-        <v>40159200</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" s="3">
         <v>38706800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>41386200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>43066500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>43236900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>44597600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>49258500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>40083000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>46427400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>43820200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>43726000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>42710700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>44308900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>42138000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>40187000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>40103800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>49304300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>45967000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>50502000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>45745800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>45270100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>48394000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>47953500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>47241100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>45633100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>46572300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>46648100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>45839800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>45304800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>44373100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>43863100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>49919500</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>7918600</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E47" s="3">
-        <v>7486300</v>
-      </c>
-      <c r="F47" s="3">
+        <v>9189400</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>11077300</v>
       </c>
-      <c r="G47" s="3">
-        <v>7423800</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>8654800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>11988300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10202700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10289700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8957900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6823800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7123800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6934300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6613500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6824000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7105800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7097900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7135600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>6667500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7063000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7699800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8113000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>9074100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12086600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>11909900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>12423900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>12268900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>12733300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>12636400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>13196900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>13425300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>13164700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>12783700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>12515200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>13097300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>16937400</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3">
         <v>8958600</v>
       </c>
-      <c r="E48" s="3">
-        <v>8169700</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="F48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="3">
         <v>8514000</v>
       </c>
-      <c r="G48" s="3">
-        <v>7963900</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3">
         <v>8078000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8325500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>11872500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12155500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12791800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12067500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13491700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17274800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16459900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>16629700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17237600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>17652400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>17079000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>15682000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>16694300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>16517900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19076400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20106600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19703700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19759100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>18803700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>18389900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>20003800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>19357100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>19208400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>19232200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>18881700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>18246800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>17725900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>17662900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>20069600</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="3">
         <v>24620200</v>
       </c>
-      <c r="E49" s="3">
-        <v>25198800</v>
-      </c>
-      <c r="F49" s="3">
+      <c r="F49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="3">
         <v>25224100</v>
       </c>
-      <c r="G49" s="3">
-        <v>24923100</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I49" s="3">
         <v>23473100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>23948700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>25076700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>25305000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>25652100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>23738800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>23826100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>25113500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>22647900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>22308700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>23106900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>15617200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>15073600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>14192100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>15141300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9038200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9829500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>10478300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8381100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8770800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9225800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9348100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>9968300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>9621800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>9531500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>10139000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>10111900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>8483100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>8153300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>8193600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>8309100</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4971,8 +5085,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5081,22 +5198,25 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>3157400</v>
-      </c>
-      <c r="E52" s="3">
-        <v>3001600</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G52" s="3">
-        <v>2857700</v>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>8</v>
@@ -5113,86 +5233,89 @@
       <c r="L52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="3">
         <v>2406600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2354000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2667900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2671500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2733700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2700300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2786600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2610500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3472000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3696300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4109000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4498100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3502200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3405900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3442200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3664200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3546200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3512500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3057200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2854500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2728600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2784700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2792500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2951400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>2691400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>9247200</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5301,118 +5424,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="3">
         <v>88714500</v>
       </c>
-      <c r="E54" s="3">
-        <v>86926700</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="F54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" s="3">
         <v>87730500</v>
       </c>
-      <c r="G54" s="3">
-        <v>83327700</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I54" s="3">
         <v>80799200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>85648700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>90218400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>90987100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>94042300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>94295100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>86878700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>98418000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>92213000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>92222000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>92861400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>87463100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>84036700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>80200700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>82698800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>86669200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>87484000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>93663200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>89323100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>89152000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>92511500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>91506600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>93459000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>90305500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>91363700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>92173200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>90782700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>87610900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>85718900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>85508400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>104482800</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5451,8 +5580,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5491,668 +5621,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
         <v>10502700</v>
       </c>
-      <c r="E57" s="3">
-        <v>9868700</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3">
         <v>10207600</v>
       </c>
-      <c r="G57" s="3">
-        <v>9432200</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3">
         <v>9253900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9523100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10553000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10855800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11648600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10499200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10878200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12105000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11650800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10957900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10787600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11144000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10748100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9809900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9797100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9368400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11194600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>11828400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11275400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>11927900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>13511800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12785400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12738900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12718200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>13894300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>13397100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>12889700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>12346100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>12437800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>11908500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>11654900</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="3">
         <v>2951400</v>
       </c>
-      <c r="E58" s="3">
-        <v>6567900</v>
-      </c>
-      <c r="F58" s="3">
+      <c r="F58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="3">
         <v>3935800</v>
       </c>
-      <c r="G58" s="3">
-        <v>3847100</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I58" s="3">
         <v>1489600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4160100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6929500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7514300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6917000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12408500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8625500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12483000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>10428400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>13041400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>12086700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6548900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4899400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>9077200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>12284200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>12318200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3652100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>6529700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5029300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4536800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2847300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>5429700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4508500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4229900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2157200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3742700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3865500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>4202800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3429100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3937900</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>12512300</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
         <v>21081000</v>
       </c>
-      <c r="E59" s="3">
-        <v>19451800</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3">
         <v>18753000</v>
       </c>
-      <c r="G59" s="3">
-        <v>18295400</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3">
         <v>16396900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16765700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15008200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15378500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14873600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20275000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17563000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17017900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16791900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15810000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16046600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>16697900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>16944700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>15956700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>16120700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>17854300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>18042600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>19847800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>16505800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>16298200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>18290400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>17134300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>17568000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>16763300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>18258800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>17693700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>17628000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>16719600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>17137200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>16265100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>16240700</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="3">
         <v>39451900</v>
       </c>
-      <c r="E60" s="3">
-        <v>39848400</v>
-      </c>
-      <c r="F60" s="3">
+      <c r="F60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" s="3">
         <v>37169400</v>
       </c>
-      <c r="G60" s="3">
-        <v>35000400</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I60" s="3">
         <v>31751700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>34400400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>37330200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>37806500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>38862700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>43182600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>37066800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>41605900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>38871000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>39809300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>38920800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>34390800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>32592200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>34843800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>38202100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>39540800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>32889300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>38205800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>32810500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>32762900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>34649400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>35349400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>34815400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>33711400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>34310400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>34833500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>34383200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>33268500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>33004000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>32111400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>40407900</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>5102900</v>
       </c>
-      <c r="E61" s="3">
-        <v>4829600</v>
-      </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>6737400</v>
       </c>
-      <c r="G61" s="3">
-        <v>6196700</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>6311900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8287000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8977200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9217300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9732900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9280200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9269000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10837200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10333000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11118900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11804800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>12061200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>12097900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9983800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7275300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8505400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9431100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7705500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7720200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8081000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6808600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7076600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6652500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6755400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7337400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7529400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7629600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7261000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>7007400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>7631500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>19851800</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>2229800</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E62" s="3">
-        <v>2344700</v>
-      </c>
-      <c r="F62" s="3">
+        <v>1546600</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3">
         <v>2470900</v>
       </c>
-      <c r="G62" s="3">
-        <v>2306900</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3">
         <v>1626500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2488200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2715000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2701400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1710500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5121100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5332800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7899900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7450000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7621300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7886600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7913300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7737800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8641200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>9389500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7054800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7573600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8011800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7935100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7819600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8631100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8503900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>8634300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>8575800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>8930400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9587400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9519400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9427600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>9367200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>9692000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>9942400</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6261,8 +6410,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6371,8 +6523,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6481,118 +6636,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="3">
         <v>48437300</v>
       </c>
-      <c r="E66" s="3">
-        <v>48639600</v>
-      </c>
-      <c r="F66" s="3">
+      <c r="F66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66" s="3">
         <v>48253800</v>
       </c>
-      <c r="G66" s="3">
-        <v>45155800</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I66" s="3">
         <v>42059300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>47174600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>51214100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>51988900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>53905300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>62173500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>55928700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>67291300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>63383200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>65084500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>65283900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>61047200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>59040900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>58736000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>59983500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>60767600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>59644500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>64242700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>58617400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>59031200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>61157900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>61843400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>61415400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>59788500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>61730400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>63059800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>62347900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>60372500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>59400900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>59920500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>81205500</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6631,8 +6792,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6741,8 +6903,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6851,8 +7016,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6961,8 +7129,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7071,118 +7242,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
         <v>29052200</v>
       </c>
-      <c r="E72" s="3">
-        <v>27507600</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3">
         <v>29895400</v>
       </c>
-      <c r="G72" s="3">
-        <v>25894400</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3">
         <v>27005600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>27270100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>25325900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>25192600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>27360800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>23149500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>21426100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>21664600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>21232900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>20987100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>21520400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>20473000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>19218200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>18264800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>19425200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>21120100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>20229600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>20621300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>22424100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>21711000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>21983700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>20149100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>21201100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>19948300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>19032800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>18040300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>17443200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>16664700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>15909000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>15530900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>15048500</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7291,8 +7468,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7401,8 +7581,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7511,118 +7694,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="3">
         <v>39046200</v>
       </c>
-      <c r="E76" s="3">
-        <v>37201300</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="F76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76" s="3">
         <v>38400200</v>
       </c>
-      <c r="G76" s="3">
-        <v>37248700</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I76" s="3">
         <v>37709200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>37447400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>36259600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>36277000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>37182800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>32121600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>30949900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>31126700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>28829800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>27137600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>27577500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>26415900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>24995800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>21464600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>22715300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>25901600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>27839500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>29420500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>30705700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>30120900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>31353600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>29663100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>32043600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>30517000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>29633300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>29113400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>28434800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>27238300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>26318000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>25587900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>23277400</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7731,123 +7920,129 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7878,86 +8073,89 @@
       <c r="L81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N81" s="3">
         <v>850000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>863600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>250400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>881000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>881700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1443500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>898400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1373600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>418700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>214300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1904300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>285900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1222100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>634000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1102000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1344600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1041900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>815200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>956700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>943800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>885600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>773300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>678600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>354800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>689800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>506000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7996,118 +8194,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
         <v>667800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>734300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>841200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>839300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>905200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>937000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>972000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1043300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>605400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>877300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>897300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>955600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>945700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>926000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>952600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>962300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>996500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>918100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>992500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>839800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1027900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>989800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>959000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>947800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>934400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>863000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>828800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>819700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>836100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>833100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>836900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>788400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>836200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>793900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1019900</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8216,8 +8418,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8326,8 +8531,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8436,8 +8644,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8546,8 +8757,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8656,118 +8870,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>3700100</v>
       </c>
-      <c r="E89" s="3">
-        <v>1875200</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3">
         <v>1257900</v>
       </c>
-      <c r="G89" s="3">
-        <v>889700</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3">
         <v>2735400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1602800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1330800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>817200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3362200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1039700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>813400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>715500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3139300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>657400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>175900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1007500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2600100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1553300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>472800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1311900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2229600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>930700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1165500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>722400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3917700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-91000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>721300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1221300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2295800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1760400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1369900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1147500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2221100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>835800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1773600</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8806,118 +9026,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
         <v>-696300</v>
       </c>
-      <c r="E91" s="3">
-        <v>-328500</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3">
         <v>-348900</v>
       </c>
-      <c r="G91" s="3">
-        <v>-254400</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
         <v>-476000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-314200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-420500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-372000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-421200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-96150000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-108272000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100755000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-134149000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100626000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-107573000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-488900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-628300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-384800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-471300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-453200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-794100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-595900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-811800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-723700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-857900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-898800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-883000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-934700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-11900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1277100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-889100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-2139000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9026,8 +9250,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9136,118 +9363,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1015500</v>
       </c>
-      <c r="E94" s="3">
-        <v>-697800</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3">
         <v>-540900</v>
       </c>
-      <c r="G94" s="3">
-        <v>-1457100</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3">
         <v>267500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-437800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-471500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-275700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2229200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-517900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-485400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-140400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-524200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6808900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-51800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>2178300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-455900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-8267800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>3049100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-297800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2595800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-937000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-962900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>121300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-311700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-357900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-944800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1447200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-721200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1173700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-945800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1217900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>141000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1198700</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9286,22 +9519,23 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="3">
-        <v>615100</v>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="3">
-        <v>576300</v>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>8</v>
@@ -9318,86 +9552,89 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3">
         <v>-471300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>1600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-424400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-399200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-391300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-355300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>1100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-412600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-397200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>1500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-442700</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-365100</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-351500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>400</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-305900</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-305900</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>400</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-257400</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9506,8 +9743,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9616,8 +9856,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9726,334 +9969,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3372100</v>
       </c>
-      <c r="E100" s="3">
-        <v>-115700</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3">
         <v>-662500</v>
       </c>
-      <c r="G100" s="3">
-        <v>1205700</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3">
         <v>-4291700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1287100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1115800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-191300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6635700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>551100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2261600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>107900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3369100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>436900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4584400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>78600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4395900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>9900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-723400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>4492600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-740400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>152600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-25700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>668100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-3116400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-529700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-258300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>797900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1618500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-748700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-709100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>170400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-864900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2288400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>989900</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
         <v>238000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-172600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>125300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>287200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>96300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-438600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>97000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>443900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>283000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-410600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>89500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>406600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>228200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>180400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>22500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>39600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>316900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>46100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>18000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>7000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-152900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>171200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-128000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-189700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>27200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-170600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-254800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>99500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>107600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>59800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-122100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>530100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-69300</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-955200</v>
       </c>
-      <c r="E102" s="3">
-        <v>1367700</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-355700</v>
       </c>
-      <c r="G102" s="3">
-        <v>869400</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1050800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-294700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-131300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>637400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-948000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>662300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1360700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>744500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-141900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>750500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2026200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1073900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>699400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1153400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-8500500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>8860600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1038400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1341400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>74800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>237900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>949900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1103100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>104000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1058400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1024800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>390000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-405400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>431900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>16200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-781600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1495500</v>
       </c>
     </row>
